--- a/data_kkp/KKP_MASTER.xlsx
+++ b/data_kkp/KKP_MASTER.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F108"/>
+  <dimension ref="A1:F156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,22 +466,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>007130</t>
+          <t>665307</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+          <t>POLRES OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>770670</v>
+        <v>59780000</v>
       </c>
     </row>
     <row r="3">
@@ -490,22 +490,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>007130</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>2025</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>160005</v>
+        <v>46960000</v>
       </c>
     </row>
     <row r="4">
@@ -514,22 +514,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>007130</t>
+          <t>641681</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+          <t>POLRES OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1160190</v>
+        <v>38610000</v>
       </c>
     </row>
     <row r="5">
@@ -538,22 +538,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>2025</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>9180565</v>
+        <v>37740000</v>
       </c>
     </row>
     <row r="6">
@@ -562,22 +562,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2025</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>8752087</v>
+        <v>28612620</v>
       </c>
     </row>
     <row r="7">
@@ -593,7 +593,7 @@
         <v>2025</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>16690098</v>
+        <v>26763409</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>665307</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>POLRES OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>26763409</v>
+        <v>24770827</v>
       </c>
     </row>
     <row r="9">
@@ -634,22 +634,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>665307</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>POLRES OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>22446603</v>
+        <v>24183457</v>
       </c>
     </row>
     <row r="10">
@@ -658,22 +658,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>641681</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>POLRES OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>11321000</v>
+        <v>23405000</v>
       </c>
     </row>
     <row r="11">
@@ -682,22 +682,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>2025</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>17922000</v>
+        <v>22446603</v>
       </c>
     </row>
     <row r="12">
@@ -706,22 +706,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>2025</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2650000</v>
+        <v>22314667</v>
       </c>
     </row>
     <row r="13">
@@ -730,22 +730,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>2025</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3905000</v>
+        <v>19651577</v>
       </c>
     </row>
     <row r="14">
@@ -761,7 +761,7 @@
         <v>2025</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3500000</v>
+        <v>17922000</v>
       </c>
     </row>
     <row r="15">
@@ -778,22 +778,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>2025</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>13874500</v>
+        <v>17770000</v>
       </c>
     </row>
     <row r="16">
@@ -802,7 +802,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -813,11 +813,11 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3897000</v>
+        <v>17150045</v>
       </c>
     </row>
     <row r="17">
@@ -826,7 +826,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -837,11 +837,11 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>13995500</v>
+        <v>17095326</v>
       </c>
     </row>
     <row r="18">
@@ -850,22 +850,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>2025</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>9151500</v>
+        <v>16690098</v>
       </c>
     </row>
     <row r="19">
@@ -874,22 +874,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>665292</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D19" t="n">
         <v>2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>POLRES OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4043518</v>
+        <v>16512000</v>
       </c>
     </row>
     <row r="20">
@@ -898,22 +898,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>665292</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>POLRES OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>37740000</v>
+        <v>16512000</v>
       </c>
     </row>
     <row r="21">
@@ -922,22 +922,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>2025</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>12365000</v>
+        <v>15951110</v>
       </c>
     </row>
     <row r="22">
@@ -946,22 +946,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>2025</v>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>9286864</v>
+        <v>14785443</v>
       </c>
     </row>
     <row r="23">
@@ -970,22 +970,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>2025</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2793700</v>
+        <v>13995500</v>
       </c>
     </row>
     <row r="24">
@@ -994,22 +994,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>2025</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>212017</v>
+        <v>13874500</v>
       </c>
     </row>
     <row r="25">
@@ -1018,22 +1018,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>2025</v>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>885100</v>
+        <v>12365000</v>
       </c>
     </row>
     <row r="26">
@@ -1042,22 +1042,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1496500</v>
+        <v>12334663</v>
       </c>
     </row>
     <row r="27">
@@ -1066,22 +1066,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>668529</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>2025</v>
       </c>
       <c r="D27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2316253</v>
+        <v>11419000</v>
       </c>
     </row>
     <row r="28">
@@ -1090,22 +1090,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>2025</v>
       </c>
       <c r="D28" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2625670</v>
+        <v>11321000</v>
       </c>
     </row>
     <row r="29">
@@ -1114,22 +1114,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>2025</v>
       </c>
       <c r="D29" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1933320</v>
+        <v>9978760</v>
       </c>
     </row>
     <row r="30">
@@ -1138,22 +1138,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D30" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4885170</v>
+        <v>9749809</v>
       </c>
     </row>
     <row r="31">
@@ -1162,22 +1162,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>2025</v>
       </c>
       <c r="D31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>5818770</v>
+        <v>9670989</v>
       </c>
     </row>
     <row r="32">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1197,11 +1197,11 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>6652559</v>
+        <v>9286864</v>
       </c>
     </row>
     <row r="33">
@@ -1210,22 +1210,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D33" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3348270</v>
+        <v>9264940</v>
       </c>
     </row>
     <row r="34">
@@ -1234,22 +1234,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>2025</v>
       </c>
       <c r="D34" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1168200</v>
+        <v>9180565</v>
       </c>
     </row>
     <row r="35">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>2025</v>
       </c>
       <c r="D35" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>9026788</v>
+        <v>9151500</v>
       </c>
     </row>
     <row r="36">
@@ -1289,7 +1289,7 @@
         <v>2025</v>
       </c>
       <c r="D36" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1068054</v>
+        <v>9026788</v>
       </c>
     </row>
     <row r="37">
@@ -1306,22 +1306,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>2025</v>
       </c>
       <c r="D37" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>7992275</v>
+        <v>8875815</v>
       </c>
     </row>
     <row r="38">
@@ -1330,22 +1330,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D38" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>8596433</v>
+        <v>8771468</v>
       </c>
     </row>
     <row r="39">
@@ -1354,22 +1354,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>2025</v>
       </c>
       <c r="D39" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>10000</v>
+        <v>8752087</v>
       </c>
     </row>
     <row r="40">
@@ -1385,7 +1385,7 @@
         <v>2025</v>
       </c>
       <c r="D40" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>14785443</v>
+        <v>8596433</v>
       </c>
     </row>
     <row r="41">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1413,11 +1413,11 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>10000</v>
+        <v>8400111</v>
       </c>
     </row>
     <row r="42">
@@ -1426,22 +1426,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>2025</v>
       </c>
       <c r="D42" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>19651577</v>
+        <v>7992275</v>
       </c>
     </row>
     <row r="43">
@@ -1450,22 +1450,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D43" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>9670989</v>
+        <v>7855000</v>
       </c>
     </row>
     <row r="44">
@@ -1474,22 +1474,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>2025</v>
       </c>
       <c r="D44" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>6743111</v>
+        <v>7744485</v>
       </c>
     </row>
     <row r="45">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1509,11 +1509,11 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>9978760</v>
+        <v>7326664</v>
       </c>
     </row>
     <row r="46">
@@ -1529,7 +1529,7 @@
         <v>2025</v>
       </c>
       <c r="D46" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>22314667</v>
+        <v>6743111</v>
       </c>
     </row>
     <row r="47">
@@ -1546,22 +1546,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>692339</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D47" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>8400111</v>
+        <v>6727500</v>
       </c>
     </row>
     <row r="48">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>424245</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1581,11 +1581,11 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>568000</v>
+        <v>6652559</v>
       </c>
     </row>
     <row r="49">
@@ -1601,7 +1601,7 @@
         <v>2025</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>17770000</v>
+        <v>6523503</v>
       </c>
     </row>
     <row r="50">
@@ -1618,22 +1618,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="C50" t="n">
         <v>2025</v>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>6523503</v>
+        <v>6438360</v>
       </c>
     </row>
     <row r="51">
@@ -1642,22 +1642,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>692339</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D51" t="n">
         <v>3</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>905070</v>
+        <v>6331240</v>
       </c>
     </row>
     <row r="52">
@@ -1666,22 +1666,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="C52" t="n">
         <v>2025</v>
       </c>
       <c r="D52" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>3822990</v>
+        <v>6077473</v>
       </c>
     </row>
     <row r="53">
@@ -1690,22 +1690,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>2025</v>
       </c>
       <c r="D53" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1290545</v>
+        <v>5939307</v>
       </c>
     </row>
     <row r="54">
@@ -1714,22 +1714,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>2025</v>
       </c>
       <c r="D54" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1517640</v>
+        <v>5902139</v>
       </c>
     </row>
     <row r="55">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>2025</v>
       </c>
       <c r="D55" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>8875815</v>
+        <v>5818770</v>
       </c>
     </row>
     <row r="56">
@@ -1762,22 +1762,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>2025</v>
       </c>
       <c r="D56" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>15951110</v>
+        <v>5716521</v>
       </c>
     </row>
     <row r="57">
@@ -1786,22 +1786,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>2025</v>
       </c>
       <c r="D57" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>17150045</v>
+        <v>5489670</v>
       </c>
     </row>
     <row r="58">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D58" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>17095326</v>
+        <v>4924945</v>
       </c>
     </row>
     <row r="59">
@@ -1834,22 +1834,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D59" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1074070</v>
+        <v>4910000</v>
       </c>
     </row>
     <row r="60">
@@ -1858,22 +1858,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="C60" t="n">
         <v>2025</v>
       </c>
       <c r="D60" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1489998</v>
+        <v>4885170</v>
       </c>
     </row>
     <row r="61">
@@ -1882,22 +1882,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D61" t="n">
         <v>4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>3211146</v>
+        <v>4849486</v>
       </c>
     </row>
     <row r="62">
@@ -1906,22 +1906,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D62" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>5902139</v>
+        <v>4663299</v>
       </c>
     </row>
     <row r="63">
@@ -1930,22 +1930,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D63" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>6077473</v>
+        <v>4395000</v>
       </c>
     </row>
     <row r="64">
@@ -1954,22 +1954,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="C64" t="n">
         <v>2025</v>
       </c>
       <c r="D64" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>7744485</v>
+        <v>4298266</v>
       </c>
     </row>
     <row r="65">
@@ -1978,22 +1978,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>692339</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D65" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>2241786</v>
+        <v>4225000</v>
       </c>
     </row>
     <row r="66">
@@ -2002,22 +2002,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="C66" t="n">
         <v>2025</v>
       </c>
       <c r="D66" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>3557090</v>
+        <v>4151070</v>
       </c>
     </row>
     <row r="67">
@@ -2026,22 +2026,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="C67" t="n">
         <v>2025</v>
       </c>
       <c r="D67" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>46960000</v>
+        <v>4043518</v>
       </c>
     </row>
     <row r="68">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>28612620</v>
+        <v>4002352</v>
       </c>
     </row>
     <row r="69">
@@ -2074,22 +2074,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="C69" t="n">
         <v>2025</v>
       </c>
       <c r="D69" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>259000</v>
+        <v>3960692</v>
       </c>
     </row>
     <row r="70">
@@ -2098,22 +2098,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>553099</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="C70" t="n">
         <v>2025</v>
       </c>
       <c r="D70" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2911500</v>
+        <v>3905000</v>
       </c>
     </row>
     <row r="71">
@@ -2122,22 +2122,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>656553</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="C71" t="n">
         <v>2025</v>
       </c>
       <c r="D71" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>775000</v>
+        <v>3897000</v>
       </c>
     </row>
     <row r="72">
@@ -2146,22 +2146,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="C72" t="n">
         <v>2025</v>
       </c>
       <c r="D72" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>2289406</v>
+        <v>3822990</v>
       </c>
     </row>
     <row r="73">
@@ -2194,22 +2194,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D74" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>2283305</v>
+        <v>3632700</v>
       </c>
     </row>
     <row r="75">
@@ -2218,22 +2218,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="C75" t="n">
         <v>2025</v>
       </c>
       <c r="D75" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>5489670</v>
+        <v>3557090</v>
       </c>
     </row>
     <row r="76">
@@ -2242,22 +2242,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D76" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>2257445</v>
+        <v>3512800</v>
       </c>
     </row>
     <row r="77">
@@ -2266,22 +2266,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="C77" t="n">
         <v>2025</v>
       </c>
       <c r="D77" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>7326664</v>
+        <v>3500000</v>
       </c>
     </row>
     <row r="78">
@@ -2290,22 +2290,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>692339</t>
         </is>
       </c>
       <c r="C78" t="n">
         <v>2025</v>
       </c>
       <c r="D78" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>3185388</v>
+        <v>3465000</v>
       </c>
     </row>
     <row r="79">
@@ -2318,10 +2318,10 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D79" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>4151070</v>
+        <v>3429000</v>
       </c>
     </row>
     <row r="80">
@@ -2338,22 +2338,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1904397</v>
+        <v>3417810</v>
       </c>
     </row>
     <row r="81">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="C81" t="n">
         <v>2025</v>
       </c>
       <c r="D81" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>640133</v>
+        <v>3348270</v>
       </c>
     </row>
     <row r="82">
@@ -2386,22 +2386,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D82" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1720000</v>
+        <v>3277136</v>
       </c>
     </row>
     <row r="83">
@@ -2410,22 +2410,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="C83" t="n">
         <v>2025</v>
       </c>
       <c r="D83" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>128530</v>
+        <v>3240885</v>
       </c>
     </row>
     <row r="84">
@@ -2434,22 +2434,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="C84" t="n">
         <v>2025</v>
       </c>
       <c r="D84" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>401000</v>
+        <v>3211146</v>
       </c>
     </row>
     <row r="85">
@@ -2458,22 +2458,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="C85" t="n">
         <v>2025</v>
       </c>
       <c r="D85" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>1826019</v>
+        <v>3185388</v>
       </c>
     </row>
     <row r="86">
@@ -2482,22 +2482,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D86" t="n">
         <v>3</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>2115768</v>
+        <v>3082879</v>
       </c>
     </row>
     <row r="87">
@@ -2506,22 +2506,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D87" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>2111897</v>
+        <v>3050000</v>
       </c>
     </row>
     <row r="88">
@@ -2537,7 +2537,7 @@
         <v>2025</v>
       </c>
       <c r="D88" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>4298266</v>
+        <v>3017400</v>
       </c>
     </row>
     <row r="89">
@@ -2554,22 +2554,22 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>553099</t>
         </is>
       </c>
       <c r="C89" t="n">
         <v>2025</v>
       </c>
       <c r="D89" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>3017400</v>
+        <v>2911500</v>
       </c>
     </row>
     <row r="90">
@@ -2578,22 +2578,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>692334</t>
         </is>
       </c>
       <c r="C90" t="n">
         <v>2025</v>
       </c>
       <c r="D90" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>LAPAS KELAS II B MUARA DUA</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>5939307</v>
+        <v>2806886</v>
       </c>
     </row>
     <row r="91">
@@ -2602,22 +2602,22 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="C91" t="n">
         <v>2025</v>
       </c>
       <c r="D91" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>3240885</v>
+        <v>2793700</v>
       </c>
     </row>
     <row r="92">
@@ -2626,22 +2626,22 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>690801</t>
         </is>
       </c>
       <c r="C92" t="n">
         <v>2025</v>
       </c>
       <c r="D92" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>6438360</v>
+        <v>2717905</v>
       </c>
     </row>
     <row r="93">
@@ -2650,22 +2650,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D93" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>3960692</v>
+        <v>2695000</v>
       </c>
     </row>
     <row r="94">
@@ -2674,22 +2674,22 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="C94" t="n">
         <v>2025</v>
       </c>
       <c r="D94" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>4002352</v>
+        <v>2650000</v>
       </c>
     </row>
     <row r="95">
@@ -2698,22 +2698,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="C95" t="n">
         <v>2025</v>
       </c>
       <c r="D95" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>5716521</v>
+        <v>2625670</v>
       </c>
     </row>
     <row r="96">
@@ -2722,22 +2722,22 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D96" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>11419000</v>
+        <v>2574000</v>
       </c>
     </row>
     <row r="97">
@@ -2746,22 +2746,22 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>692625</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D97" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>BAPAS KELAS II OKU INDUK</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>1392000</v>
+        <v>2550000</v>
       </c>
     </row>
     <row r="98">
@@ -2770,22 +2770,22 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>692625</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D98" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>BAPAS KELAS II OKU INDUK</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>1722276</v>
+        <v>2500000</v>
       </c>
     </row>
     <row r="99">
@@ -2794,22 +2794,22 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D99" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>689000</v>
+        <v>2483040</v>
       </c>
     </row>
     <row r="100">
@@ -2818,22 +2818,22 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>685001</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D100" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>PUSLATPUR KODIKLATAD</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>1500000</v>
+        <v>2420890</v>
       </c>
     </row>
     <row r="101">
@@ -2842,22 +2842,22 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>690801</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D101" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>1865319</v>
+        <v>2410602</v>
       </c>
     </row>
     <row r="102">
@@ -2866,22 +2866,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>690801</t>
+          <t>685001</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D102" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
+          <t>PUSLATPUR KODIKLATAD</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>2717905</v>
+        <v>2400000</v>
       </c>
     </row>
     <row r="103">
@@ -2890,22 +2890,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>685001</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D103" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA</t>
+          <t>PUSLATPUR KODIKLATAD</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>1082700</v>
+        <v>2400000</v>
       </c>
     </row>
     <row r="104">
@@ -2914,22 +2914,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="C104" t="n">
         <v>2025</v>
       </c>
       <c r="D104" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>2260122</v>
+        <v>2316253</v>
       </c>
     </row>
     <row r="105">
@@ -2938,22 +2938,22 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="C105" t="n">
         <v>2025</v>
       </c>
       <c r="D105" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>2806886</v>
+        <v>2289406</v>
       </c>
     </row>
     <row r="106">
@@ -2962,22 +2962,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="C106" t="n">
         <v>2025</v>
       </c>
       <c r="D106" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>1082700</v>
+        <v>2283305</v>
       </c>
     </row>
     <row r="107">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>692339</t>
+          <t>692334</t>
         </is>
       </c>
       <c r="C107" t="n">
         <v>2025</v>
       </c>
       <c r="D107" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RUTAN KELAS II B BATURAJA</t>
+          <t>LAPAS KELAS II B MUARA DUA</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>1386000</v>
+        <v>2260122</v>
       </c>
     </row>
     <row r="108">
@@ -3010,22 +3010,1174 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
+          <t>656560</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D108" t="n">
+        <v>9</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>2257445</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>656560</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D109" t="n">
+        <v>4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>2256300</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>527975</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D110" t="n">
+        <v>8</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>2241786</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>424245</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D111" t="n">
+        <v>3</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>2223600</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D112" t="n">
+        <v>3</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>2115768</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D113" t="n">
+        <v>4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>2111897</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>656553</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D114" t="n">
+        <v>3</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>1995000</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>656553</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D115" t="n">
+        <v>4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>656553</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D116" t="n">
+        <v>2</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>401944</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D117" t="n">
+        <v>7</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>1933320</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>656574</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D118" t="n">
+        <v>2</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>1904397</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>690801</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D119" t="n">
+        <v>11</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>1865319</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D120" t="n">
+        <v>2</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>1826019</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>424245</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D121" t="n">
+        <v>1</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>1725950</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>668529</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D122" t="n">
+        <v>9</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>1722276</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>656553</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D123" t="n">
+        <v>1</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>1721500</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>656574</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D124" t="n">
+        <v>5</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>1720000</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D125" t="n">
+        <v>6</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>1517640</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>685001</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D126" t="n">
+        <v>11</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>PUSLATPUR KODIKLATAD</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>401944</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D127" t="n">
+        <v>4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>1496500</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>527975</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D128" t="n">
+        <v>2</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>1489998</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>668529</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D129" t="n">
+        <v>8</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>1392000</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
           <t>692339</t>
         </is>
       </c>
-      <c r="C108" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D108" t="n">
+      <c r="C130" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D130" t="n">
+        <v>11</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>RUTAN KELAS II B BATURAJA</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>1386000</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D131" t="n">
+        <v>5</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>1290545</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>402267</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D132" t="n">
+        <v>5</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>1168200</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>007130</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D133" t="n">
         <v>12</v>
       </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>RUTAN KELAS II B BATURAJA</t>
-        </is>
-      </c>
-      <c r="F108" t="n">
-        <v>3465000</v>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>1160190</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>692334</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D134" t="n">
+        <v>8</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>LAPAS KELAS II B MUARA DUA</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>1082700</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>692334</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D135" t="n">
+        <v>12</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>LAPAS KELAS II B MUARA DUA</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>1082700</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D136" t="n">
+        <v>11</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>1074070</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>402267</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D137" t="n">
+        <v>7</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>1068054</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>424245</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D138" t="n">
+        <v>4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>1067000</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D139" t="n">
+        <v>3</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>905070</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>401944</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D140" t="n">
+        <v>3</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>885100</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>656553</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D141" t="n">
+        <v>10</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>775000</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>007130</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D142" t="n">
+        <v>10</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>770670</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>668529</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D143" t="n">
+        <v>10</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>689000</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>656574</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D144" t="n">
+        <v>2</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>647750</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>656574</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D145" t="n">
+        <v>3</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>640133</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>424245</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D146" t="n">
+        <v>10</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>568000</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>656574</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D147" t="n">
+        <v>11</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>401000</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>656574</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D148" t="n">
+        <v>3</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>283500</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>527975</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D149" t="n">
+        <v>12</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>259000</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>401944</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D150" t="n">
+        <v>2</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>212017</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>007130</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D151" t="n">
+        <v>3</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>198180</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>007130</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D152" t="n">
+        <v>11</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>160005</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>007130</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D153" t="n">
+        <v>2</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>145429</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>656574</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D154" t="n">
+        <v>10</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>128530</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>402267</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D155" t="n">
+        <v>12</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>402267</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D156" t="n">
+        <v>10</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>10000</v>
       </c>
     </row>
   </sheetData>

--- a/data_kkp/KKP_MASTER.xlsx
+++ b/data_kkp/KKP_MASTER.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F108"/>
+  <dimension ref="A1:F156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,22 +466,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>007130</t>
+          <t>665307</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+          <t>POLRES OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>770670</v>
+        <v>59780000</v>
       </c>
     </row>
     <row r="3">
@@ -490,22 +490,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>007130</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>2025</v>
       </c>
       <c r="E3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>160005</v>
+        <v>46960000</v>
       </c>
     </row>
     <row r="4">
@@ -514,22 +514,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>007130</t>
+          <t>641681</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+          <t>POLRES OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>1160190</v>
+        <v>38610000</v>
       </c>
     </row>
     <row r="5">
@@ -538,22 +538,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>2025</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>9180565</v>
+        <v>37740000</v>
       </c>
     </row>
     <row r="6">
@@ -562,22 +562,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>2025</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F6" t="n">
-        <v>8752087</v>
+        <v>28612620</v>
       </c>
     </row>
     <row r="7">
@@ -598,10 +598,10 @@
         <v>2025</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F7" t="n">
-        <v>16690098</v>
+        <v>26763409</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>665307</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>POLRES OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>26763409</v>
+        <v>24770827</v>
       </c>
     </row>
     <row r="9">
@@ -634,22 +634,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>665307</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>POLRES OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E9" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>22446603</v>
+        <v>24183457</v>
       </c>
     </row>
     <row r="10">
@@ -658,22 +658,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>641681</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>POLRES OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>11321000</v>
+        <v>23405000</v>
       </c>
     </row>
     <row r="11">
@@ -682,22 +682,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>2025</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F11" t="n">
-        <v>17922000</v>
+        <v>22446603</v>
       </c>
     </row>
     <row r="12">
@@ -706,22 +706,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>2025</v>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F12" t="n">
-        <v>2650000</v>
+        <v>22314667</v>
       </c>
     </row>
     <row r="13">
@@ -730,22 +730,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>2025</v>
       </c>
       <c r="E13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F13" t="n">
-        <v>3905000</v>
+        <v>19651577</v>
       </c>
     </row>
     <row r="14">
@@ -766,10 +766,10 @@
         <v>2025</v>
       </c>
       <c r="E14" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>3500000</v>
+        <v>17922000</v>
       </c>
     </row>
     <row r="15">
@@ -778,22 +778,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>2025</v>
       </c>
       <c r="E15" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>13874500</v>
+        <v>17770000</v>
       </c>
     </row>
     <row r="16">
@@ -802,12 +802,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -817,7 +817,7 @@
         <v>9</v>
       </c>
       <c r="F16" t="n">
-        <v>3897000</v>
+        <v>17150045</v>
       </c>
     </row>
     <row r="17">
@@ -826,12 +826,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -841,7 +841,7 @@
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>13995500</v>
+        <v>17095326</v>
       </c>
     </row>
     <row r="18">
@@ -850,22 +850,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>2025</v>
       </c>
       <c r="E18" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F18" t="n">
-        <v>9151500</v>
+        <v>16690098</v>
       </c>
     </row>
     <row r="19">
@@ -874,22 +874,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>665292</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>POLRES OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E19" t="n">
         <v>2</v>
       </c>
       <c r="F19" t="n">
-        <v>4043518</v>
+        <v>16512000</v>
       </c>
     </row>
     <row r="20">
@@ -898,22 +898,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>665292</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>POLRES OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F20" t="n">
-        <v>37740000</v>
+        <v>16512000</v>
       </c>
     </row>
     <row r="21">
@@ -922,22 +922,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>2025</v>
       </c>
       <c r="E21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F21" t="n">
-        <v>12365000</v>
+        <v>15951110</v>
       </c>
     </row>
     <row r="22">
@@ -946,22 +946,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>2025</v>
       </c>
       <c r="E22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F22" t="n">
-        <v>9286864</v>
+        <v>14785443</v>
       </c>
     </row>
     <row r="23">
@@ -970,22 +970,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>2025</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F23" t="n">
-        <v>2793700</v>
+        <v>13995500</v>
       </c>
     </row>
     <row r="24">
@@ -994,22 +994,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>2025</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F24" t="n">
-        <v>212017</v>
+        <v>13874500</v>
       </c>
     </row>
     <row r="25">
@@ -1018,22 +1018,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>2025</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F25" t="n">
-        <v>885100</v>
+        <v>12365000</v>
       </c>
     </row>
     <row r="26">
@@ -1042,22 +1042,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F26" t="n">
-        <v>1496500</v>
+        <v>12334663</v>
       </c>
     </row>
     <row r="27">
@@ -1066,22 +1066,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>668529</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>2025</v>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F27" t="n">
-        <v>2316253</v>
+        <v>11419000</v>
       </c>
     </row>
     <row r="28">
@@ -1090,22 +1090,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>2025</v>
       </c>
       <c r="E28" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>2625670</v>
+        <v>11321000</v>
       </c>
     </row>
     <row r="29">
@@ -1114,22 +1114,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>2025</v>
       </c>
       <c r="E29" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F29" t="n">
-        <v>1933320</v>
+        <v>9978760</v>
       </c>
     </row>
     <row r="30">
@@ -1138,22 +1138,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E30" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F30" t="n">
-        <v>4885170</v>
+        <v>9749809</v>
       </c>
     </row>
     <row r="31">
@@ -1162,22 +1162,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="D31" t="n">
         <v>2025</v>
       </c>
       <c r="E31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F31" t="n">
-        <v>5818770</v>
+        <v>9670989</v>
       </c>
     </row>
     <row r="32">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1201,7 +1201,7 @@
         <v>10</v>
       </c>
       <c r="F32" t="n">
-        <v>6652559</v>
+        <v>9286864</v>
       </c>
     </row>
     <row r="33">
@@ -1210,22 +1210,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E33" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F33" t="n">
-        <v>3348270</v>
+        <v>9264940</v>
       </c>
     </row>
     <row r="34">
@@ -1234,22 +1234,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="D34" t="n">
         <v>2025</v>
       </c>
       <c r="E34" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F34" t="n">
-        <v>1168200</v>
+        <v>9180565</v>
       </c>
     </row>
     <row r="35">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="D35" t="n">
         <v>2025</v>
       </c>
       <c r="E35" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F35" t="n">
-        <v>9026788</v>
+        <v>9151500</v>
       </c>
     </row>
     <row r="36">
@@ -1294,10 +1294,10 @@
         <v>2025</v>
       </c>
       <c r="E36" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F36" t="n">
-        <v>1068054</v>
+        <v>9026788</v>
       </c>
     </row>
     <row r="37">
@@ -1306,22 +1306,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D37" t="n">
         <v>2025</v>
       </c>
       <c r="E37" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F37" t="n">
-        <v>7992275</v>
+        <v>8875815</v>
       </c>
     </row>
     <row r="38">
@@ -1330,22 +1330,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E38" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F38" t="n">
-        <v>8596433</v>
+        <v>8771468</v>
       </c>
     </row>
     <row r="39">
@@ -1354,22 +1354,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="D39" t="n">
         <v>2025</v>
       </c>
       <c r="E39" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F39" t="n">
-        <v>10000</v>
+        <v>8752087</v>
       </c>
     </row>
     <row r="40">
@@ -1390,10 +1390,10 @@
         <v>2025</v>
       </c>
       <c r="E40" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F40" t="n">
-        <v>14785443</v>
+        <v>8596433</v>
       </c>
     </row>
     <row r="41">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1417,7 +1417,7 @@
         <v>12</v>
       </c>
       <c r="F41" t="n">
-        <v>10000</v>
+        <v>8400111</v>
       </c>
     </row>
     <row r="42">
@@ -1426,22 +1426,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="D42" t="n">
         <v>2025</v>
       </c>
       <c r="E42" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F42" t="n">
-        <v>19651577</v>
+        <v>7992275</v>
       </c>
     </row>
     <row r="43">
@@ -1450,22 +1450,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E43" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F43" t="n">
-        <v>9670989</v>
+        <v>7855000</v>
       </c>
     </row>
     <row r="44">
@@ -1474,22 +1474,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="D44" t="n">
         <v>2025</v>
       </c>
       <c r="E44" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F44" t="n">
-        <v>6743111</v>
+        <v>7744485</v>
       </c>
     </row>
     <row r="45">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1513,7 +1513,7 @@
         <v>10</v>
       </c>
       <c r="F45" t="n">
-        <v>9978760</v>
+        <v>7326664</v>
       </c>
     </row>
     <row r="46">
@@ -1534,10 +1534,10 @@
         <v>2025</v>
       </c>
       <c r="E46" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F46" t="n">
-        <v>22314667</v>
+        <v>6743111</v>
       </c>
     </row>
     <row r="47">
@@ -1546,22 +1546,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>692339</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E47" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F47" t="n">
-        <v>8400111</v>
+        <v>6727500</v>
       </c>
     </row>
     <row r="48">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>424245</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -1585,7 +1585,7 @@
         <v>10</v>
       </c>
       <c r="F48" t="n">
-        <v>568000</v>
+        <v>6652559</v>
       </c>
     </row>
     <row r="49">
@@ -1606,10 +1606,10 @@
         <v>2025</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" t="n">
-        <v>17770000</v>
+        <v>6523503</v>
       </c>
     </row>
     <row r="50">
@@ -1618,22 +1618,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="D50" t="n">
         <v>2025</v>
       </c>
       <c r="E50" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F50" t="n">
-        <v>6523503</v>
+        <v>6438360</v>
       </c>
     </row>
     <row r="51">
@@ -1642,22 +1642,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>692339</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E51" t="n">
         <v>3</v>
       </c>
       <c r="F51" t="n">
-        <v>905070</v>
+        <v>6331240</v>
       </c>
     </row>
     <row r="52">
@@ -1666,22 +1666,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="D52" t="n">
         <v>2025</v>
       </c>
       <c r="E52" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F52" t="n">
-        <v>3822990</v>
+        <v>6077473</v>
       </c>
     </row>
     <row r="53">
@@ -1690,22 +1690,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="D53" t="n">
         <v>2025</v>
       </c>
       <c r="E53" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F53" t="n">
-        <v>1290545</v>
+        <v>5939307</v>
       </c>
     </row>
     <row r="54">
@@ -1714,22 +1714,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="D54" t="n">
         <v>2025</v>
       </c>
       <c r="E54" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F54" t="n">
-        <v>1517640</v>
+        <v>5902139</v>
       </c>
     </row>
     <row r="55">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="D55" t="n">
         <v>2025</v>
       </c>
       <c r="E55" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F55" t="n">
-        <v>8875815</v>
+        <v>5818770</v>
       </c>
     </row>
     <row r="56">
@@ -1762,22 +1762,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="D56" t="n">
         <v>2025</v>
       </c>
       <c r="E56" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F56" t="n">
-        <v>15951110</v>
+        <v>5716521</v>
       </c>
     </row>
     <row r="57">
@@ -1786,22 +1786,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="D57" t="n">
         <v>2025</v>
       </c>
       <c r="E57" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F57" t="n">
-        <v>17150045</v>
+        <v>5489670</v>
       </c>
     </row>
     <row r="58">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E58" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F58" t="n">
-        <v>17095326</v>
+        <v>4924945</v>
       </c>
     </row>
     <row r="59">
@@ -1834,22 +1834,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E59" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F59" t="n">
-        <v>1074070</v>
+        <v>4910000</v>
       </c>
     </row>
     <row r="60">
@@ -1858,22 +1858,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="D60" t="n">
         <v>2025</v>
       </c>
       <c r="E60" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F60" t="n">
-        <v>1489998</v>
+        <v>4885170</v>
       </c>
     </row>
     <row r="61">
@@ -1882,22 +1882,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E61" t="n">
         <v>4</v>
       </c>
       <c r="F61" t="n">
-        <v>3211146</v>
+        <v>4849486</v>
       </c>
     </row>
     <row r="62">
@@ -1906,22 +1906,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E62" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F62" t="n">
-        <v>5902139</v>
+        <v>4663299</v>
       </c>
     </row>
     <row r="63">
@@ -1930,22 +1930,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E63" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F63" t="n">
-        <v>6077473</v>
+        <v>4395000</v>
       </c>
     </row>
     <row r="64">
@@ -1954,22 +1954,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="D64" t="n">
         <v>2025</v>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F64" t="n">
-        <v>7744485</v>
+        <v>4298266</v>
       </c>
     </row>
     <row r="65">
@@ -1978,22 +1978,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>692339</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E65" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F65" t="n">
-        <v>2241786</v>
+        <v>4225000</v>
       </c>
     </row>
     <row r="66">
@@ -2002,22 +2002,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="D66" t="n">
         <v>2025</v>
       </c>
       <c r="E66" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F66" t="n">
-        <v>3557090</v>
+        <v>4151070</v>
       </c>
     </row>
     <row r="67">
@@ -2026,22 +2026,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="D67" t="n">
         <v>2025</v>
       </c>
       <c r="E67" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F67" t="n">
-        <v>46960000</v>
+        <v>4043518</v>
       </c>
     </row>
     <row r="68">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2065,7 +2065,7 @@
         <v>11</v>
       </c>
       <c r="F68" t="n">
-        <v>28612620</v>
+        <v>4002352</v>
       </c>
     </row>
     <row r="69">
@@ -2074,22 +2074,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="D69" t="n">
         <v>2025</v>
       </c>
       <c r="E69" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F69" t="n">
-        <v>259000</v>
+        <v>3960692</v>
       </c>
     </row>
     <row r="70">
@@ -2098,22 +2098,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>553099</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="D70" t="n">
         <v>2025</v>
       </c>
       <c r="E70" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F70" t="n">
-        <v>2911500</v>
+        <v>3905000</v>
       </c>
     </row>
     <row r="71">
@@ -2122,22 +2122,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>656553</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="D71" t="n">
         <v>2025</v>
       </c>
       <c r="E71" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F71" t="n">
-        <v>775000</v>
+        <v>3897000</v>
       </c>
     </row>
     <row r="72">
@@ -2146,22 +2146,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D72" t="n">
         <v>2025</v>
       </c>
       <c r="E72" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F72" t="n">
-        <v>2289406</v>
+        <v>3822990</v>
       </c>
     </row>
     <row r="73">
@@ -2194,22 +2194,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E74" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F74" t="n">
-        <v>2283305</v>
+        <v>3632700</v>
       </c>
     </row>
     <row r="75">
@@ -2218,22 +2218,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="D75" t="n">
         <v>2025</v>
       </c>
       <c r="E75" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F75" t="n">
-        <v>5489670</v>
+        <v>3557090</v>
       </c>
     </row>
     <row r="76">
@@ -2242,22 +2242,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E76" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F76" t="n">
-        <v>2257445</v>
+        <v>3512800</v>
       </c>
     </row>
     <row r="77">
@@ -2266,22 +2266,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="D77" t="n">
         <v>2025</v>
       </c>
       <c r="E77" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F77" t="n">
-        <v>7326664</v>
+        <v>3500000</v>
       </c>
     </row>
     <row r="78">
@@ -2290,22 +2290,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>692339</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
       <c r="D78" t="n">
         <v>2025</v>
       </c>
       <c r="E78" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F78" t="n">
-        <v>3185388</v>
+        <v>3465000</v>
       </c>
     </row>
     <row r="79">
@@ -2323,13 +2323,13 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E79" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F79" t="n">
-        <v>4151070</v>
+        <v>3429000</v>
       </c>
     </row>
     <row r="80">
@@ -2338,22 +2338,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F80" t="n">
-        <v>1904397</v>
+        <v>3417810</v>
       </c>
     </row>
     <row r="81">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="D81" t="n">
         <v>2025</v>
       </c>
       <c r="E81" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F81" t="n">
-        <v>640133</v>
+        <v>3348270</v>
       </c>
     </row>
     <row r="82">
@@ -2386,22 +2386,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
-        <v>1720000</v>
+        <v>3277136</v>
       </c>
     </row>
     <row r="83">
@@ -2410,22 +2410,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="D83" t="n">
         <v>2025</v>
       </c>
       <c r="E83" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F83" t="n">
-        <v>128530</v>
+        <v>3240885</v>
       </c>
     </row>
     <row r="84">
@@ -2434,22 +2434,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="D84" t="n">
         <v>2025</v>
       </c>
       <c r="E84" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F84" t="n">
-        <v>401000</v>
+        <v>3211146</v>
       </c>
     </row>
     <row r="85">
@@ -2458,22 +2458,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="D85" t="n">
         <v>2025</v>
       </c>
       <c r="E85" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F85" t="n">
-        <v>1826019</v>
+        <v>3185388</v>
       </c>
     </row>
     <row r="86">
@@ -2482,22 +2482,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E86" t="n">
         <v>3</v>
       </c>
       <c r="F86" t="n">
-        <v>2115768</v>
+        <v>3082879</v>
       </c>
     </row>
     <row r="87">
@@ -2506,22 +2506,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E87" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F87" t="n">
-        <v>2111897</v>
+        <v>3050000</v>
       </c>
     </row>
     <row r="88">
@@ -2542,10 +2542,10 @@
         <v>2025</v>
       </c>
       <c r="E88" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F88" t="n">
-        <v>4298266</v>
+        <v>3017400</v>
       </c>
     </row>
     <row r="89">
@@ -2554,22 +2554,22 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>553099</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="D89" t="n">
         <v>2025</v>
       </c>
       <c r="E89" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F89" t="n">
-        <v>3017400</v>
+        <v>2911500</v>
       </c>
     </row>
     <row r="90">
@@ -2578,22 +2578,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>692334</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>LAPAS KELAS II B MUARA DUA</t>
         </is>
       </c>
       <c r="D90" t="n">
         <v>2025</v>
       </c>
       <c r="E90" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F90" t="n">
-        <v>5939307</v>
+        <v>2806886</v>
       </c>
     </row>
     <row r="91">
@@ -2602,22 +2602,22 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="D91" t="n">
         <v>2025</v>
       </c>
       <c r="E91" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F91" t="n">
-        <v>3240885</v>
+        <v>2793700</v>
       </c>
     </row>
     <row r="92">
@@ -2626,22 +2626,22 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>690801</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
         </is>
       </c>
       <c r="D92" t="n">
         <v>2025</v>
       </c>
       <c r="E92" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F92" t="n">
-        <v>6438360</v>
+        <v>2717905</v>
       </c>
     </row>
     <row r="93">
@@ -2650,22 +2650,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E93" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F93" t="n">
-        <v>3960692</v>
+        <v>2695000</v>
       </c>
     </row>
     <row r="94">
@@ -2674,22 +2674,22 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="D94" t="n">
         <v>2025</v>
       </c>
       <c r="E94" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F94" t="n">
-        <v>4002352</v>
+        <v>2650000</v>
       </c>
     </row>
     <row r="95">
@@ -2698,22 +2698,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="D95" t="n">
         <v>2025</v>
       </c>
       <c r="E95" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F95" t="n">
-        <v>5716521</v>
+        <v>2625670</v>
       </c>
     </row>
     <row r="96">
@@ -2722,22 +2722,22 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E96" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F96" t="n">
-        <v>11419000</v>
+        <v>2574000</v>
       </c>
     </row>
     <row r="97">
@@ -2746,22 +2746,22 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>692625</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>BAPAS KELAS II OKU INDUK</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E97" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F97" t="n">
-        <v>1392000</v>
+        <v>2550000</v>
       </c>
     </row>
     <row r="98">
@@ -2770,22 +2770,22 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>692625</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>BAPAS KELAS II OKU INDUK</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E98" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F98" t="n">
-        <v>1722276</v>
+        <v>2500000</v>
       </c>
     </row>
     <row r="99">
@@ -2794,22 +2794,22 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E99" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F99" t="n">
-        <v>689000</v>
+        <v>2483040</v>
       </c>
     </row>
     <row r="100">
@@ -2818,22 +2818,22 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>685001</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>PUSLATPUR KODIKLATAD</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E100" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F100" t="n">
-        <v>1500000</v>
+        <v>2420890</v>
       </c>
     </row>
     <row r="101">
@@ -2842,22 +2842,22 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>690801</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E101" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F101" t="n">
-        <v>1865319</v>
+        <v>2410602</v>
       </c>
     </row>
     <row r="102">
@@ -2866,22 +2866,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>690801</t>
+          <t>685001</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
+          <t>PUSLATPUR KODIKLATAD</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E102" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F102" t="n">
-        <v>2717905</v>
+        <v>2400000</v>
       </c>
     </row>
     <row r="103">
@@ -2890,22 +2890,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>685001</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA</t>
+          <t>PUSLATPUR KODIKLATAD</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E103" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F103" t="n">
-        <v>1082700</v>
+        <v>2400000</v>
       </c>
     </row>
     <row r="104">
@@ -2914,22 +2914,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="D104" t="n">
         <v>2025</v>
       </c>
       <c r="E104" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F104" t="n">
-        <v>2260122</v>
+        <v>2316253</v>
       </c>
     </row>
     <row r="105">
@@ -2938,22 +2938,22 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="D105" t="n">
         <v>2025</v>
       </c>
       <c r="E105" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F105" t="n">
-        <v>2806886</v>
+        <v>2289406</v>
       </c>
     </row>
     <row r="106">
@@ -2962,22 +2962,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="D106" t="n">
         <v>2025</v>
       </c>
       <c r="E106" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F106" t="n">
-        <v>1082700</v>
+        <v>2283305</v>
       </c>
     </row>
     <row r="107">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>692339</t>
+          <t>692334</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>RUTAN KELAS II B BATURAJA</t>
+          <t>LAPAS KELAS II B MUARA DUA</t>
         </is>
       </c>
       <c r="D107" t="n">
         <v>2025</v>
       </c>
       <c r="E107" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F107" t="n">
-        <v>1386000</v>
+        <v>2260122</v>
       </c>
     </row>
     <row r="108">
@@ -3010,22 +3010,1174 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
+          <t>656560</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E108" t="n">
+        <v>9</v>
+      </c>
+      <c r="F108" t="n">
+        <v>2257445</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>656560</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E109" t="n">
+        <v>4</v>
+      </c>
+      <c r="F109" t="n">
+        <v>2256300</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>527975</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E110" t="n">
+        <v>8</v>
+      </c>
+      <c r="F110" t="n">
+        <v>2241786</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>424245</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E111" t="n">
+        <v>3</v>
+      </c>
+      <c r="F111" t="n">
+        <v>2223600</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E112" t="n">
+        <v>3</v>
+      </c>
+      <c r="F112" t="n">
+        <v>2115768</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E113" t="n">
+        <v>4</v>
+      </c>
+      <c r="F113" t="n">
+        <v>2111897</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>656553</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E114" t="n">
+        <v>3</v>
+      </c>
+      <c r="F114" t="n">
+        <v>1995000</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>656553</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E115" t="n">
+        <v>4</v>
+      </c>
+      <c r="F115" t="n">
+        <v>1990000</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>656553</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E116" t="n">
+        <v>2</v>
+      </c>
+      <c r="F116" t="n">
+        <v>1980000</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>401944</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E117" t="n">
+        <v>7</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1933320</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>656574</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E118" t="n">
+        <v>2</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1904397</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>690801</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E119" t="n">
+        <v>11</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1865319</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E120" t="n">
+        <v>2</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1826019</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>424245</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E121" t="n">
+        <v>1</v>
+      </c>
+      <c r="F121" t="n">
+        <v>1725950</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>668529</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E122" t="n">
+        <v>9</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1722276</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>656553</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E123" t="n">
+        <v>1</v>
+      </c>
+      <c r="F123" t="n">
+        <v>1721500</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>656574</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E124" t="n">
+        <v>5</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1720000</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E125" t="n">
+        <v>6</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1517640</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>685001</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>PUSLATPUR KODIKLATAD</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E126" t="n">
+        <v>11</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>401944</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E127" t="n">
+        <v>4</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1496500</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>527975</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E128" t="n">
+        <v>2</v>
+      </c>
+      <c r="F128" t="n">
+        <v>1489998</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>668529</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E129" t="n">
+        <v>8</v>
+      </c>
+      <c r="F129" t="n">
+        <v>1392000</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
           <t>692339</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C130" t="inlineStr">
         <is>
           <t>RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
-      <c r="D108" t="n">
-        <v>2025</v>
-      </c>
-      <c r="E108" t="n">
+      <c r="D130" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E130" t="n">
+        <v>11</v>
+      </c>
+      <c r="F130" t="n">
+        <v>1386000</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E131" t="n">
+        <v>5</v>
+      </c>
+      <c r="F131" t="n">
+        <v>1290545</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>402267</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E132" t="n">
+        <v>5</v>
+      </c>
+      <c r="F132" t="n">
+        <v>1168200</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>007130</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E133" t="n">
         <v>12</v>
       </c>
-      <c r="F108" t="n">
-        <v>3465000</v>
+      <c r="F133" t="n">
+        <v>1160190</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>692334</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>LAPAS KELAS II B MUARA DUA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E134" t="n">
+        <v>8</v>
+      </c>
+      <c r="F134" t="n">
+        <v>1082700</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>692334</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>LAPAS KELAS II B MUARA DUA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E135" t="n">
+        <v>12</v>
+      </c>
+      <c r="F135" t="n">
+        <v>1082700</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E136" t="n">
+        <v>11</v>
+      </c>
+      <c r="F136" t="n">
+        <v>1074070</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>402267</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E137" t="n">
+        <v>7</v>
+      </c>
+      <c r="F137" t="n">
+        <v>1068054</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>424245</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E138" t="n">
+        <v>4</v>
+      </c>
+      <c r="F138" t="n">
+        <v>1067000</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E139" t="n">
+        <v>3</v>
+      </c>
+      <c r="F139" t="n">
+        <v>905070</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>401944</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E140" t="n">
+        <v>3</v>
+      </c>
+      <c r="F140" t="n">
+        <v>885100</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>656553</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E141" t="n">
+        <v>10</v>
+      </c>
+      <c r="F141" t="n">
+        <v>775000</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>007130</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E142" t="n">
+        <v>10</v>
+      </c>
+      <c r="F142" t="n">
+        <v>770670</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>668529</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E143" t="n">
+        <v>10</v>
+      </c>
+      <c r="F143" t="n">
+        <v>689000</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>656574</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E144" t="n">
+        <v>2</v>
+      </c>
+      <c r="F144" t="n">
+        <v>647750</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>656574</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E145" t="n">
+        <v>3</v>
+      </c>
+      <c r="F145" t="n">
+        <v>640133</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>424245</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E146" t="n">
+        <v>10</v>
+      </c>
+      <c r="F146" t="n">
+        <v>568000</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>656574</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E147" t="n">
+        <v>11</v>
+      </c>
+      <c r="F147" t="n">
+        <v>401000</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>656574</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E148" t="n">
+        <v>3</v>
+      </c>
+      <c r="F148" t="n">
+        <v>283500</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>527975</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E149" t="n">
+        <v>12</v>
+      </c>
+      <c r="F149" t="n">
+        <v>259000</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>401944</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E150" t="n">
+        <v>2</v>
+      </c>
+      <c r="F150" t="n">
+        <v>212017</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>007130</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E151" t="n">
+        <v>3</v>
+      </c>
+      <c r="F151" t="n">
+        <v>198180</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>007130</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E152" t="n">
+        <v>11</v>
+      </c>
+      <c r="F152" t="n">
+        <v>160005</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>007130</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E153" t="n">
+        <v>2</v>
+      </c>
+      <c r="F153" t="n">
+        <v>145429</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>656574</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E154" t="n">
+        <v>10</v>
+      </c>
+      <c r="F154" t="n">
+        <v>128530</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>402267</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E155" t="n">
+        <v>12</v>
+      </c>
+      <c r="F155" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>402267</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E156" t="n">
+        <v>10</v>
+      </c>
+      <c r="F156" t="n">
+        <v>10000</v>
       </c>
     </row>
   </sheetData>

--- a/data_kkp/KKP_MASTER.xlsx
+++ b/data_kkp/KKP_MASTER.xlsx
@@ -534,7 +534,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>120000000</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -585,7 +585,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -636,7 +636,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>8800000</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>8800000</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>40000000</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>12000000</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>12000000</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>20000000</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>20000000</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>6000000</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>80000000</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>14400000</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>14400000</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>14400000</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>6000000</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>6000000</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>6000000</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>120000000</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>120000000</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>2400000</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>120000000</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>12000000</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>6000000</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>6000000</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>6000000</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>120000000</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>12000000</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>2400000</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>6000000</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>80000000</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>10000000</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>10000000</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>10000000</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>6000000</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>8800000</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>12000000</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>40000000</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>40000000</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>40000000</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>6000000</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>2400000</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4665,7 +4665,7 @@
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>120000000</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -4767,7 +4767,7 @@
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>120000000</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -5124,7 +5124,7 @@
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>120000000</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>20000000</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>20000000</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -5328,7 +5328,7 @@
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>20000000</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>20000000</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
-        <v>0</v>
+        <v>20000000</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
-        <v>0</v>
+        <v>2400000</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
-        <v>0</v>
+        <v>120000000</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
-        <v>0</v>
+        <v>14400000</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
-        <v>0</v>
+        <v>14400000</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -5685,7 +5685,7 @@
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
-        <v>0</v>
+        <v>14400000</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
-        <v>0</v>
+        <v>6000000</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
-        <v>0</v>
+        <v>120000000</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
-        <v>0</v>
+        <v>6000000</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
-        <v>0</v>
+        <v>6000000</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -6246,7 +6246,7 @@
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -6552,7 +6552,7 @@
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
-        <v>0</v>
+        <v>10000000</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
-        <v>0</v>
+        <v>10000000</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
-        <v>0</v>
+        <v>8800000</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
-        <v>0</v>
+        <v>20000000</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
-        <v>0</v>
+        <v>20000000</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
-        <v>0</v>
+        <v>20000000</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
-        <v>0</v>
+        <v>20000000</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
-        <v>0</v>
+        <v>20000000</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
-        <v>0</v>
+        <v>20000000</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
-        <v>0</v>
+        <v>40000000</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
-        <v>0</v>
+        <v>8000000</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>

--- a/data_kkp/KKP_MASTER.xlsx
+++ b/data_kkp/KKP_MASTER.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q128"/>
+  <dimension ref="A1:Q262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,8 +567,10 @@
           <t>2025-01</t>
         </is>
       </c>
-      <c r="L2" t="n">
-        <v>824300</v>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>824300</t>
+        </is>
       </c>
       <c r="M2" t="n">
         <v>824300</v>
@@ -640,8 +642,10 @@
           <t>2025-01</t>
         </is>
       </c>
-      <c r="L3" t="n">
-        <v>11321000</v>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>11321000</t>
+        </is>
       </c>
       <c r="M3" t="n">
         <v>11321000</v>
@@ -713,8 +717,10 @@
           <t>2025-01</t>
         </is>
       </c>
-      <c r="L4" t="n">
-        <v>2793700</v>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2793700</t>
+        </is>
       </c>
       <c r="M4" t="n">
         <v>2793700</v>
@@ -786,8 +792,10 @@
           <t>2025-02</t>
         </is>
       </c>
-      <c r="L5" t="n">
-        <v>17922000</v>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>17922000</t>
+        </is>
       </c>
       <c r="M5" t="n">
         <v>17922000</v>
@@ -859,8 +867,10 @@
           <t>2025-02</t>
         </is>
       </c>
-      <c r="L6" t="n">
-        <v>212017</v>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>212017</t>
+        </is>
       </c>
       <c r="M6" t="n">
         <v>212017</v>
@@ -932,8 +942,10 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="L7" t="n">
-        <v>476970</v>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>476970</t>
+        </is>
       </c>
       <c r="M7" t="n">
         <v>476970</v>
@@ -1005,8 +1017,10 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="L8" t="n">
-        <v>885100</v>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>885100</t>
+        </is>
       </c>
       <c r="M8" t="n">
         <v>885100</v>
@@ -1078,8 +1092,10 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="L9" t="n">
-        <v>1304070</v>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>1304070</t>
+        </is>
       </c>
       <c r="M9" t="n">
         <v>1304070</v>
@@ -1151,8 +1167,10 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="L10" t="n">
-        <v>2650000</v>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2650000</t>
+        </is>
       </c>
       <c r="M10" t="n">
         <v>2650000</v>
@@ -1224,8 +1242,10 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="L11" t="n">
-        <v>1496500</v>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>1496500</t>
+        </is>
       </c>
       <c r="M11" t="n">
         <v>1496500</v>
@@ -1297,8 +1317,10 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="L12" t="n">
-        <v>2316253</v>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2316253</t>
+        </is>
       </c>
       <c r="M12" t="n">
         <v>2316253</v>
@@ -1370,8 +1392,10 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="L13" t="n">
-        <v>1168200</v>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>1168200</t>
+        </is>
       </c>
       <c r="M13" t="n">
         <v>1168200</v>
@@ -1443,8 +1467,10 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="L14" t="n">
-        <v>1905600</v>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1905600</t>
+        </is>
       </c>
       <c r="M14" t="n">
         <v>1905600</v>
@@ -1516,8 +1542,10 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="L15" t="n">
-        <v>1745800</v>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1745800</t>
+        </is>
       </c>
       <c r="M15" t="n">
         <v>1745800</v>
@@ -1589,8 +1617,10 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="L16" t="n">
-        <v>2625670</v>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2625670</t>
+        </is>
       </c>
       <c r="M16" t="n">
         <v>2625670</v>
@@ -1662,8 +1692,10 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="L17" t="n">
-        <v>3905000</v>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>3905000</t>
+        </is>
       </c>
       <c r="M17" t="n">
         <v>3905000</v>
@@ -1735,8 +1767,10 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="L18" t="n">
-        <v>9026788</v>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>9026788</t>
+        </is>
       </c>
       <c r="M18" t="n">
         <v>9026788</v>
@@ -1808,8 +1842,10 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="L19" t="n">
-        <v>3500000</v>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>3500000</t>
+        </is>
       </c>
       <c r="M19" t="n">
         <v>3500000</v>
@@ -1881,8 +1917,10 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="L20" t="n">
-        <v>1933320</v>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1933320</t>
+        </is>
       </c>
       <c r="M20" t="n">
         <v>1933320</v>
@@ -1954,8 +1992,10 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="L21" t="n">
-        <v>1068054</v>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>1068054</t>
+        </is>
       </c>
       <c r="M21" t="n">
         <v>1068054</v>
@@ -2027,8 +2067,10 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="L22" t="n">
-        <v>4885170</v>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>4885170</t>
+        </is>
       </c>
       <c r="M22" t="n">
         <v>4885170</v>
@@ -2100,8 +2142,10 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="L23" t="n">
-        <v>400000</v>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>400000</t>
+        </is>
       </c>
       <c r="M23" t="n">
         <v>400000</v>
@@ -2173,8 +2217,10 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="L24" t="n">
-        <v>13874500</v>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>13874500</t>
+        </is>
       </c>
       <c r="M24" t="n">
         <v>13874500</v>
@@ -2246,8 +2292,10 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="L25" t="n">
-        <v>7992275</v>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>7992275</t>
+        </is>
       </c>
       <c r="M25" t="n">
         <v>7992275</v>
@@ -2319,8 +2367,10 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="L26" t="n">
-        <v>3897000</v>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>3897000</t>
+        </is>
       </c>
       <c r="M26" t="n">
         <v>3897000</v>
@@ -2392,8 +2442,10 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="L27" t="n">
-        <v>5818770</v>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>5818770</t>
+        </is>
       </c>
       <c r="M27" t="n">
         <v>5818770</v>
@@ -2465,8 +2517,10 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="L28" t="n">
-        <v>1935940</v>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>1935940</t>
+        </is>
       </c>
       <c r="M28" t="n">
         <v>1935940</v>
@@ -2538,8 +2592,10 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="L29" t="n">
-        <v>8596433</v>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>8596433</t>
+        </is>
       </c>
       <c r="M29" t="n">
         <v>8596433</v>
@@ -2611,8 +2667,10 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="L30" t="n">
-        <v>3471500</v>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>3471500</t>
+        </is>
       </c>
       <c r="M30" t="n">
         <v>3471500</v>
@@ -2684,8 +2742,10 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="L31" t="n">
-        <v>13995500</v>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>13995500</t>
+        </is>
       </c>
       <c r="M31" t="n">
         <v>13995500</v>
@@ -2757,8 +2817,10 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="L32" t="n">
-        <v>10000</v>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
       </c>
       <c r="M32" t="n">
         <v>10000</v>
@@ -2830,8 +2892,10 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="L33" t="n">
-        <v>6652559</v>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>6652559</t>
+        </is>
       </c>
       <c r="M33" t="n">
         <v>6652559</v>
@@ -2903,8 +2967,10 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="L34" t="n">
-        <v>3348270</v>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>3348270</t>
+        </is>
       </c>
       <c r="M34" t="n">
         <v>3348270</v>
@@ -2976,8 +3042,10 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="L35" t="n">
-        <v>14785443</v>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>14785443</t>
+        </is>
       </c>
       <c r="M35" t="n">
         <v>14785443</v>
@@ -3049,8 +3117,10 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="L36" t="n">
-        <v>9151500</v>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>9151500</t>
+        </is>
       </c>
       <c r="M36" t="n">
         <v>9151500</v>
@@ -3122,8 +3192,10 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="L37" t="n">
-        <v>10000</v>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
       </c>
       <c r="M37" t="n">
         <v>10000</v>
@@ -3195,8 +3267,10 @@
           <t>2025-02</t>
         </is>
       </c>
-      <c r="L38" t="n">
-        <v>9180565</v>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>9180565</t>
+        </is>
       </c>
       <c r="M38" t="n">
         <v>9180565</v>
@@ -3268,8 +3342,10 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="L39" t="n">
-        <v>8752087</v>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>8752087</t>
+        </is>
       </c>
       <c r="M39" t="n">
         <v>8752087</v>
@@ -3341,8 +3417,10 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="L40" t="n">
-        <v>16690098</v>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>16690098</t>
+        </is>
       </c>
       <c r="M40" t="n">
         <v>16690098</v>
@@ -3414,8 +3492,10 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="L41" t="n">
-        <v>26763409</v>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>26763409</t>
+        </is>
       </c>
       <c r="M41" t="n">
         <v>26763409</v>
@@ -3487,8 +3567,10 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="L42" t="n">
-        <v>770670</v>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>770670</t>
+        </is>
       </c>
       <c r="M42" t="n">
         <v>770670</v>
@@ -3560,8 +3642,10 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="L43" t="n">
-        <v>160005</v>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>160005</t>
+        </is>
       </c>
       <c r="M43" t="n">
         <v>160005</v>
@@ -3633,8 +3717,10 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="L44" t="n">
-        <v>1160190</v>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>1160190</t>
+        </is>
       </c>
       <c r="M44" t="n">
         <v>1160190</v>
@@ -3706,8 +3792,10 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="L45" t="n">
-        <v>22446603</v>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>22446603</t>
+        </is>
       </c>
       <c r="M45" t="n">
         <v>22446603</v>
@@ -3779,8 +3867,10 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="L46" t="n">
-        <v>1500000</v>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
       </c>
       <c r="M46" t="n">
         <v>1500000</v>
@@ -3852,8 +3942,10 @@
           <t>2025-02</t>
         </is>
       </c>
-      <c r="L47" t="n">
-        <v>1489998</v>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>1489998</t>
+        </is>
       </c>
       <c r="M47" t="n">
         <v>1489998</v>
@@ -3925,8 +4017,10 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="L48" t="n">
-        <v>3211146</v>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>3211146</t>
+        </is>
       </c>
       <c r="M48" t="n">
         <v>3211146</v>
@@ -3998,8 +4092,10 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="L49" t="n">
-        <v>5902139</v>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>5902139</t>
+        </is>
       </c>
       <c r="M49" t="n">
         <v>5902139</v>
@@ -4071,8 +4167,10 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="L50" t="n">
-        <v>6077473</v>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>6077473</t>
+        </is>
       </c>
       <c r="M50" t="n">
         <v>6077473</v>
@@ -4144,8 +4242,10 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="L51" t="n">
-        <v>19651577</v>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>19651577</t>
+        </is>
       </c>
       <c r="M51" t="n">
         <v>19651577</v>
@@ -4217,8 +4317,10 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="L52" t="n">
-        <v>7744485</v>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>7744485</t>
+        </is>
       </c>
       <c r="M52" t="n">
         <v>7744485</v>
@@ -4290,8 +4392,10 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="L53" t="n">
-        <v>9670989</v>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>9670989</t>
+        </is>
       </c>
       <c r="M53" t="n">
         <v>9670989</v>
@@ -4363,8 +4467,10 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="L54" t="n">
-        <v>2241786</v>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2241786</t>
+        </is>
       </c>
       <c r="M54" t="n">
         <v>2241786</v>
@@ -4436,8 +4542,10 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="L55" t="n">
-        <v>6743111</v>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>6743111</t>
+        </is>
       </c>
       <c r="M55" t="n">
         <v>6743111</v>
@@ -4509,8 +4617,10 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="L56" t="n">
-        <v>3557090</v>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>3557090</t>
+        </is>
       </c>
       <c r="M56" t="n">
         <v>3557090</v>
@@ -4582,8 +4692,10 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="L57" t="n">
-        <v>332500</v>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>332500</t>
+        </is>
       </c>
       <c r="M57" t="n">
         <v>332500</v>
@@ -4655,8 +4767,10 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="L58" t="n">
-        <v>21740000</v>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>21740000</t>
+        </is>
       </c>
       <c r="M58" t="n">
         <v>21740000</v>
@@ -4728,8 +4842,10 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="L59" t="n">
-        <v>46960000</v>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>46960000</t>
+        </is>
       </c>
       <c r="M59" t="n">
         <v>46960000</v>
@@ -4801,8 +4917,10 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="L60" t="n">
-        <v>9978760</v>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>9978760</t>
+        </is>
       </c>
       <c r="M60" t="n">
         <v>9978760</v>
@@ -4874,8 +4992,10 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="L61" t="n">
-        <v>4695000</v>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>4695000</t>
+        </is>
       </c>
       <c r="M61" t="n">
         <v>4695000</v>
@@ -4947,8 +5067,10 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="L62" t="n">
-        <v>22314667</v>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>22314667</t>
+        </is>
       </c>
       <c r="M62" t="n">
         <v>22314667</v>
@@ -5020,8 +5142,10 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="L63" t="n">
-        <v>28612620</v>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>28612620</t>
+        </is>
       </c>
       <c r="M63" t="n">
         <v>28612620</v>
@@ -5093,8 +5217,10 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="L64" t="n">
-        <v>8400111</v>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>8400111</t>
+        </is>
       </c>
       <c r="M64" t="n">
         <v>8400111</v>
@@ -5166,8 +5292,10 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="L65" t="n">
-        <v>259000</v>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>259000</t>
+        </is>
       </c>
       <c r="M65" t="n">
         <v>259000</v>
@@ -5239,8 +5367,10 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="L66" t="n">
-        <v>1865319</v>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>1865319</t>
+        </is>
       </c>
       <c r="M66" t="n">
         <v>1865319</v>
@@ -5312,8 +5442,10 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="L67" t="n">
-        <v>2717905</v>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2717905</t>
+        </is>
       </c>
       <c r="M67" t="n">
         <v>2717905</v>
@@ -5385,8 +5517,10 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="L68" t="n">
-        <v>568000</v>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>568000</t>
+        </is>
       </c>
       <c r="M68" t="n">
         <v>568000</v>
@@ -5458,8 +5592,10 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="L69" t="n">
-        <v>2911500</v>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>2911500</t>
+        </is>
       </c>
       <c r="M69" t="n">
         <v>2911500</v>
@@ -5531,8 +5667,10 @@
           <t>2025-01</t>
         </is>
       </c>
-      <c r="L70" t="n">
-        <v>17770000</v>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>17770000</t>
+        </is>
       </c>
       <c r="M70" t="n">
         <v>17770000</v>
@@ -5604,8 +5742,10 @@
           <t>2025-01</t>
         </is>
       </c>
-      <c r="L71" t="n">
-        <v>1650000</v>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>1650000</t>
+        </is>
       </c>
       <c r="M71" t="n">
         <v>1650000</v>
@@ -5677,8 +5817,10 @@
           <t>2025-02</t>
         </is>
       </c>
-      <c r="L72" t="n">
-        <v>6523503</v>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>6523503</t>
+        </is>
       </c>
       <c r="M72" t="n">
         <v>6523503</v>
@@ -5750,8 +5892,10 @@
           <t>2025-02</t>
         </is>
       </c>
-      <c r="L73" t="n">
-        <v>1826019</v>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>1826019</t>
+        </is>
       </c>
       <c r="M73" t="n">
         <v>1826019</v>
@@ -5823,8 +5967,10 @@
           <t>2025-02</t>
         </is>
       </c>
-      <c r="L74" t="n">
-        <v>1042470</v>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>1042470</t>
+        </is>
       </c>
       <c r="M74" t="n">
         <v>1042470</v>
@@ -5896,8 +6042,10 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="L75" t="n">
-        <v>905070</v>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>905070</t>
+        </is>
       </c>
       <c r="M75" t="n">
         <v>905070</v>
@@ -5969,8 +6117,10 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="L76" t="n">
-        <v>2115768</v>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2115768</t>
+        </is>
       </c>
       <c r="M76" t="n">
         <v>2115768</v>
@@ -6042,8 +6192,10 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="L77" t="n">
-        <v>2111897</v>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2111897</t>
+        </is>
       </c>
       <c r="M77" t="n">
         <v>2111897</v>
@@ -6115,8 +6267,10 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="L78" t="n">
-        <v>3822990</v>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>3822990</t>
+        </is>
       </c>
       <c r="M78" t="n">
         <v>3822990</v>
@@ -6188,8 +6342,10 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="L79" t="n">
-        <v>1290545</v>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>1290545</t>
+        </is>
       </c>
       <c r="M79" t="n">
         <v>1290545</v>
@@ -6261,8 +6417,10 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="L80" t="n">
-        <v>616000</v>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>616000</t>
+        </is>
       </c>
       <c r="M80" t="n">
         <v>616000</v>
@@ -6334,8 +6492,10 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="L81" t="n">
-        <v>4298266</v>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>4298266</t>
+        </is>
       </c>
       <c r="M81" t="n">
         <v>4298266</v>
@@ -6407,8 +6567,10 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="L82" t="n">
-        <v>1517640</v>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>1517640</t>
+        </is>
       </c>
       <c r="M82" t="n">
         <v>1517640</v>
@@ -6480,8 +6642,10 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="L83" t="n">
-        <v>3017400</v>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>3017400</t>
+        </is>
       </c>
       <c r="M83" t="n">
         <v>3017400</v>
@@ -6553,8 +6717,10 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="L84" t="n">
-        <v>8875815</v>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>8875815</t>
+        </is>
       </c>
       <c r="M84" t="n">
         <v>8875815</v>
@@ -6626,8 +6792,10 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="L85" t="n">
-        <v>3440000</v>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>3440000</t>
+        </is>
       </c>
       <c r="M85" t="n">
         <v>3440000</v>
@@ -6699,8 +6867,10 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="L86" t="n">
-        <v>5939307</v>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>5939307</t>
+        </is>
       </c>
       <c r="M86" t="n">
         <v>5939307</v>
@@ -6772,8 +6942,10 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="L87" t="n">
-        <v>11419000</v>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>11419000</t>
+        </is>
       </c>
       <c r="M87" t="n">
         <v>11419000</v>
@@ -6845,8 +7017,10 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="L88" t="n">
-        <v>3240885</v>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>3240885</t>
+        </is>
       </c>
       <c r="M88" t="n">
         <v>3240885</v>
@@ -6918,8 +7092,10 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="L89" t="n">
-        <v>15951110</v>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>15951110</t>
+        </is>
       </c>
       <c r="M89" t="n">
         <v>15951110</v>
@@ -6991,8 +7167,10 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="L90" t="n">
-        <v>1392000</v>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>1392000</t>
+        </is>
       </c>
       <c r="M90" t="n">
         <v>1392000</v>
@@ -7064,8 +7242,10 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="L91" t="n">
-        <v>4242930</v>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>4242930</t>
+        </is>
       </c>
       <c r="M91" t="n">
         <v>4242930</v>
@@ -7137,8 +7317,10 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="L92" t="n">
-        <v>17150045</v>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>17150045</t>
+        </is>
       </c>
       <c r="M92" t="n">
         <v>17150045</v>
@@ -7210,8 +7392,10 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="L93" t="n">
-        <v>6438360</v>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>6438360</t>
+        </is>
       </c>
       <c r="M93" t="n">
         <v>6438360</v>
@@ -7283,8 +7467,10 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="L94" t="n">
-        <v>1722276</v>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>1722276</t>
+        </is>
       </c>
       <c r="M94" t="n">
         <v>1722276</v>
@@ -7356,8 +7542,10 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="L95" t="n">
-        <v>673574</v>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>673574</t>
+        </is>
       </c>
       <c r="M95" t="n">
         <v>673574</v>
@@ -7429,8 +7617,10 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="L96" t="n">
-        <v>3960692</v>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>3960692</t>
+        </is>
       </c>
       <c r="M96" t="n">
         <v>3960692</v>
@@ -7502,8 +7692,10 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="L97" t="n">
-        <v>17095326</v>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>17095326</t>
+        </is>
       </c>
       <c r="M97" t="n">
         <v>17095326</v>
@@ -7575,8 +7767,10 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="L98" t="n">
-        <v>689000</v>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>689000</t>
+        </is>
       </c>
       <c r="M98" t="n">
         <v>689000</v>
@@ -7648,8 +7842,10 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="L99" t="n">
-        <v>4002352</v>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>4002352</t>
+        </is>
       </c>
       <c r="M99" t="n">
         <v>4002352</v>
@@ -7721,8 +7917,10 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="L100" t="n">
-        <v>3205417</v>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>3205417</t>
+        </is>
       </c>
       <c r="M100" t="n">
         <v>3205417</v>
@@ -7794,8 +7992,10 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="L101" t="n">
-        <v>1074070</v>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>1074070</t>
+        </is>
       </c>
       <c r="M101" t="n">
         <v>1074070</v>
@@ -7867,8 +8067,10 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="L102" t="n">
-        <v>5716521</v>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>5716521</t>
+        </is>
       </c>
       <c r="M102" t="n">
         <v>5716521</v>
@@ -7940,8 +8142,10 @@
           <t>2025-02</t>
         </is>
       </c>
-      <c r="L103" t="n">
-        <v>4043518</v>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>4043518</t>
+        </is>
       </c>
       <c r="M103" t="n">
         <v>4043518</v>
@@ -8013,8 +8217,10 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="L104" t="n">
-        <v>37740000</v>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>37740000</t>
+        </is>
       </c>
       <c r="M104" t="n">
         <v>37740000</v>
@@ -8086,8 +8292,10 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="L105" t="n">
-        <v>12365000</v>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>12365000</t>
+        </is>
       </c>
       <c r="M105" t="n">
         <v>12365000</v>
@@ -8159,8 +8367,10 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="L106" t="n">
-        <v>9286864</v>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>9286864</t>
+        </is>
       </c>
       <c r="M106" t="n">
         <v>9286864</v>
@@ -8232,8 +8442,10 @@
           <t>2025-02</t>
         </is>
       </c>
-      <c r="L107" t="n">
-        <v>1904397</v>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>1904397</t>
+        </is>
       </c>
       <c r="M107" t="n">
         <v>1904397</v>
@@ -8305,8 +8517,10 @@
           <t>2025-02</t>
         </is>
       </c>
-      <c r="L108" t="n">
-        <v>2289406</v>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>2289406</t>
+        </is>
       </c>
       <c r="M108" t="n">
         <v>2289406</v>
@@ -8378,8 +8592,10 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="L109" t="n">
-        <v>640133</v>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>640133</t>
+        </is>
       </c>
       <c r="M109" t="n">
         <v>640133</v>
@@ -8451,8 +8667,10 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="L110" t="n">
-        <v>3668591</v>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>3668591</t>
+        </is>
       </c>
       <c r="M110" t="n">
         <v>3668591</v>
@@ -8524,8 +8742,10 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="L111" t="n">
-        <v>1720000</v>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>1720000</t>
+        </is>
       </c>
       <c r="M111" t="n">
         <v>1720000</v>
@@ -8597,8 +8817,10 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="L112" t="n">
-        <v>2283305</v>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>2283305</t>
+        </is>
       </c>
       <c r="M112" t="n">
         <v>2283305</v>
@@ -8670,8 +8892,10 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="L113" t="n">
-        <v>2065000</v>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>2065000</t>
+        </is>
       </c>
       <c r="M113" t="n">
         <v>2065000</v>
@@ -8743,8 +8967,10 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="L114" t="n">
-        <v>5489670</v>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>5489670</t>
+        </is>
       </c>
       <c r="M114" t="n">
         <v>5489670</v>
@@ -8816,8 +9042,10 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="L115" t="n">
-        <v>470000</v>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>470000</t>
+        </is>
       </c>
       <c r="M115" t="n">
         <v>470000</v>
@@ -8889,8 +9117,10 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="L116" t="n">
-        <v>2257445</v>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>2257445</t>
+        </is>
       </c>
       <c r="M116" t="n">
         <v>2257445</v>
@@ -8962,8 +9192,10 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="L117" t="n">
-        <v>128530</v>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>128530</t>
+        </is>
       </c>
       <c r="M117" t="n">
         <v>128530</v>
@@ -9035,8 +9267,10 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="L118" t="n">
-        <v>775000</v>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>775000</t>
+        </is>
       </c>
       <c r="M118" t="n">
         <v>775000</v>
@@ -9108,8 +9342,10 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="L119" t="n">
-        <v>7326664</v>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>7326664</t>
+        </is>
       </c>
       <c r="M119" t="n">
         <v>7326664</v>
@@ -9181,8 +9417,10 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="L120" t="n">
-        <v>401000</v>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>401000</t>
+        </is>
       </c>
       <c r="M120" t="n">
         <v>401000</v>
@@ -9254,8 +9492,10 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="L121" t="n">
-        <v>3185388</v>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>3185388</t>
+        </is>
       </c>
       <c r="M121" t="n">
         <v>3185388</v>
@@ -9327,8 +9567,10 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="L122" t="n">
-        <v>4151070</v>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>4151070</t>
+        </is>
       </c>
       <c r="M122" t="n">
         <v>4151070</v>
@@ -9400,8 +9642,10 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="L123" t="n">
-        <v>1082700</v>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>1082700</t>
+        </is>
       </c>
       <c r="M123" t="n">
         <v>1082700</v>
@@ -9473,8 +9717,10 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="L124" t="n">
-        <v>2260122</v>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2260122</t>
+        </is>
       </c>
       <c r="M124" t="n">
         <v>2260122</v>
@@ -9546,8 +9792,10 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="L125" t="n">
-        <v>2806886</v>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>2806886</t>
+        </is>
       </c>
       <c r="M125" t="n">
         <v>2806886</v>
@@ -9619,8 +9867,10 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="L126" t="n">
-        <v>1386000</v>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>1386000</t>
+        </is>
       </c>
       <c r="M126" t="n">
         <v>1386000</v>
@@ -9692,8 +9942,10 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="L127" t="n">
-        <v>3465000</v>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>3465000</t>
+        </is>
       </c>
       <c r="M127" t="n">
         <v>3465000</v>
@@ -9765,8 +10017,10 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="L128" t="n">
-        <v>1082700</v>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>1082700</t>
+        </is>
       </c>
       <c r="M128" t="n">
         <v>1082700</v>
@@ -9783,6 +10037,6840 @@
       <c r="Q128" t="inlineStr">
         <is>
           <t>LAMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="inlineStr"/>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>665307</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>POLRES OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="n">
+        <v>120000000</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="n">
+        <v>59780000</v>
+      </c>
+      <c r="N129" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O129" t="n">
+        <v>1</v>
+      </c>
+      <c r="P129" t="n">
+        <v>59780000</v>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="inlineStr"/>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>401944</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="n">
+        <v>677500</v>
+      </c>
+      <c r="N130" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O130" t="n">
+        <v>1</v>
+      </c>
+      <c r="P130" t="n">
+        <v>677500</v>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="inlineStr"/>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>401944</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="n">
+        <v>3277136</v>
+      </c>
+      <c r="N131" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O131" t="n">
+        <v>1</v>
+      </c>
+      <c r="P131" t="n">
+        <v>3277136</v>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="inlineStr"/>
+      <c r="C132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>401944</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="n">
+        <v>1971500</v>
+      </c>
+      <c r="N132" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O132" t="n">
+        <v>1</v>
+      </c>
+      <c r="P132" t="n">
+        <v>1971500</v>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="inlineStr"/>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>402267</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="n">
+        <v>1222740</v>
+      </c>
+      <c r="N133" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O133" t="n">
+        <v>1</v>
+      </c>
+      <c r="P133" t="n">
+        <v>1222740</v>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="inlineStr"/>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>402267</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="n">
+        <v>394160</v>
+      </c>
+      <c r="N134" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O134" t="n">
+        <v>1</v>
+      </c>
+      <c r="P134" t="n">
+        <v>394160</v>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="inlineStr"/>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>402267</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="n">
+        <v>1428480</v>
+      </c>
+      <c r="N135" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O135" t="n">
+        <v>1</v>
+      </c>
+      <c r="P135" t="n">
+        <v>1428480</v>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="inlineStr"/>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>402267</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="n">
+        <v>1589870</v>
+      </c>
+      <c r="N136" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O136" t="n">
+        <v>1</v>
+      </c>
+      <c r="P136" t="n">
+        <v>1589870</v>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="inlineStr"/>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>402267</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="n">
+        <v>216624</v>
+      </c>
+      <c r="N137" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O137" t="n">
+        <v>1</v>
+      </c>
+      <c r="P137" t="n">
+        <v>216624</v>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="inlineStr"/>
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>424245</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="n">
+        <v>8800000</v>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="n">
+        <v>1725950</v>
+      </c>
+      <c r="N138" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O138" t="n">
+        <v>1</v>
+      </c>
+      <c r="P138" t="n">
+        <v>1725950</v>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="inlineStr"/>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>424245</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="n">
+        <v>8800000</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="n">
+        <v>1548000</v>
+      </c>
+      <c r="N139" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O139" t="n">
+        <v>1</v>
+      </c>
+      <c r="P139" t="n">
+        <v>1548000</v>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>402267</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="n">
+        <v>1249250</v>
+      </c>
+      <c r="N140" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O140" t="n">
+        <v>1</v>
+      </c>
+      <c r="P140" t="n">
+        <v>1249250</v>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="inlineStr"/>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>402267</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="n">
+        <v>2420890</v>
+      </c>
+      <c r="N141" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O141" t="n">
+        <v>1</v>
+      </c>
+      <c r="P141" t="n">
+        <v>2420890</v>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>402267</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="n">
+        <v>25500</v>
+      </c>
+      <c r="N142" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O142" t="n">
+        <v>1</v>
+      </c>
+      <c r="P142" t="n">
+        <v>25500</v>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="inlineStr"/>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>402267</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="n">
+        <v>1269695</v>
+      </c>
+      <c r="N143" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O143" t="n">
+        <v>1</v>
+      </c>
+      <c r="P143" t="n">
+        <v>1269695</v>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="inlineStr"/>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>656553</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="n">
+        <v>1721500</v>
+      </c>
+      <c r="N144" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O144" t="n">
+        <v>1</v>
+      </c>
+      <c r="P144" t="n">
+        <v>1721500</v>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="inlineStr"/>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>656553</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="N145" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O145" t="n">
+        <v>2</v>
+      </c>
+      <c r="P145" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="inlineStr"/>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>410574</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="n">
+        <v>12334663</v>
+      </c>
+      <c r="N146" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O146" t="n">
+        <v>2</v>
+      </c>
+      <c r="P146" t="n">
+        <v>12334663</v>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>111079</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="n">
+        <v>7855000</v>
+      </c>
+      <c r="N147" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O147" t="n">
+        <v>2</v>
+      </c>
+      <c r="P147" t="n">
+        <v>7855000</v>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="inlineStr"/>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>111079</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="n">
+        <v>3176747</v>
+      </c>
+      <c r="N148" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O148" t="n">
+        <v>2</v>
+      </c>
+      <c r="P148" t="n">
+        <v>3176747</v>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>692339</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>RUTAN KELAS II B BATURAJA</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="n">
+        <v>6025000</v>
+      </c>
+      <c r="N149" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O149" t="n">
+        <v>2</v>
+      </c>
+      <c r="P149" t="n">
+        <v>6025000</v>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="inlineStr"/>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>401944</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="n">
+        <v>498320</v>
+      </c>
+      <c r="N150" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O150" t="n">
+        <v>2</v>
+      </c>
+      <c r="P150" t="n">
+        <v>498320</v>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>401944</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="n">
+        <v>2161600</v>
+      </c>
+      <c r="N151" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O151" t="n">
+        <v>2</v>
+      </c>
+      <c r="P151" t="n">
+        <v>2161600</v>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="inlineStr"/>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>401944</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="n">
+        <v>2483040</v>
+      </c>
+      <c r="N152" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O152" t="n">
+        <v>2</v>
+      </c>
+      <c r="P152" t="n">
+        <v>2483040</v>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="inlineStr"/>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>007130</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="n">
+        <v>145429</v>
+      </c>
+      <c r="N153" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O153" t="n">
+        <v>2</v>
+      </c>
+      <c r="P153" t="n">
+        <v>145429</v>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="inlineStr"/>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>656574</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="n">
+        <v>569120</v>
+      </c>
+      <c r="N154" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O154" t="n">
+        <v>2</v>
+      </c>
+      <c r="P154" t="n">
+        <v>569120</v>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="inlineStr"/>
+      <c r="C155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="n">
+        <v>3050000</v>
+      </c>
+      <c r="N155" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O155" t="n">
+        <v>2</v>
+      </c>
+      <c r="P155" t="n">
+        <v>3050000</v>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="inlineStr"/>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="n">
+        <v>2005500</v>
+      </c>
+      <c r="N156" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O156" t="n">
+        <v>2</v>
+      </c>
+      <c r="P156" t="n">
+        <v>2005500</v>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" t="inlineStr"/>
+      <c r="C157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>692625</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>BAPAS KELAS II OKU INDUK</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="n">
+        <v>2550000</v>
+      </c>
+      <c r="N157" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O157" t="n">
+        <v>2</v>
+      </c>
+      <c r="P157" t="n">
+        <v>2550000</v>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" t="inlineStr"/>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>402267</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="n">
+        <v>971725</v>
+      </c>
+      <c r="N158" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O158" t="n">
+        <v>2</v>
+      </c>
+      <c r="P158" t="n">
+        <v>971725</v>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" t="inlineStr"/>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>402267</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="n">
+        <v>243000</v>
+      </c>
+      <c r="N159" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O159" t="n">
+        <v>2</v>
+      </c>
+      <c r="P159" t="n">
+        <v>243000</v>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" t="inlineStr"/>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>402267</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="n">
+        <v>3036299</v>
+      </c>
+      <c r="N160" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O160" t="n">
+        <v>2</v>
+      </c>
+      <c r="P160" t="n">
+        <v>3036299</v>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" t="inlineStr"/>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>402267</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="n">
+        <v>3632700</v>
+      </c>
+      <c r="N161" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O161" t="n">
+        <v>2</v>
+      </c>
+      <c r="P161" t="n">
+        <v>3632700</v>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" t="inlineStr"/>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>665292</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>POLRES OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="n">
+        <v>80000000</v>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="n">
+        <v>16512000</v>
+      </c>
+      <c r="N162" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O162" t="n">
+        <v>2</v>
+      </c>
+      <c r="P162" t="n">
+        <v>16512000</v>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" t="inlineStr"/>
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>692339</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>RUTAN KELAS II B BATURAJA</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="n">
+        <v>5400000</v>
+      </c>
+      <c r="N163" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O163" t="n">
+        <v>2</v>
+      </c>
+      <c r="P163" t="n">
+        <v>5400000</v>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" t="inlineStr"/>
+      <c r="C164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>098963</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>PENGADILAN NEGERI BATURAJA</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="n">
+        <v>14400000</v>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="n">
+        <v>168435</v>
+      </c>
+      <c r="N164" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O164" t="n">
+        <v>2</v>
+      </c>
+      <c r="P164" t="n">
+        <v>168435</v>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" t="inlineStr"/>
+      <c r="C165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>098963</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>PENGADILAN NEGERI BATURAJA</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="n">
+        <v>14400000</v>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="n">
+        <v>9264940</v>
+      </c>
+      <c r="N165" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O165" t="n">
+        <v>2</v>
+      </c>
+      <c r="P165" t="n">
+        <v>9264940</v>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" t="inlineStr"/>
+      <c r="C166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>098963</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>PENGADILAN NEGERI BATURAJA</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="n">
+        <v>14400000</v>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="n">
+        <v>1428160</v>
+      </c>
+      <c r="N166" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O166" t="n">
+        <v>2</v>
+      </c>
+      <c r="P166" t="n">
+        <v>1428160</v>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" t="inlineStr"/>
+      <c r="C167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>656553</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="n">
+        <v>1975000</v>
+      </c>
+      <c r="N167" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O167" t="n">
+        <v>2</v>
+      </c>
+      <c r="P167" t="n">
+        <v>1975000</v>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" t="inlineStr"/>
+      <c r="C168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="n">
+        <v>485000</v>
+      </c>
+      <c r="N168" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O168" t="n">
+        <v>2</v>
+      </c>
+      <c r="P168" t="n">
+        <v>485000</v>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" t="inlineStr"/>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="n">
+        <v>620173</v>
+      </c>
+      <c r="N169" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O169" t="n">
+        <v>2</v>
+      </c>
+      <c r="P169" t="n">
+        <v>620173</v>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" t="inlineStr"/>
+      <c r="C170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="n">
+        <v>1358000</v>
+      </c>
+      <c r="N170" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O170" t="n">
+        <v>2</v>
+      </c>
+      <c r="P170" t="n">
+        <v>1358000</v>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" t="inlineStr"/>
+      <c r="C171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>656574</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="n">
+        <v>647750</v>
+      </c>
+      <c r="N171" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O171" t="n">
+        <v>2</v>
+      </c>
+      <c r="P171" t="n">
+        <v>647750</v>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" t="inlineStr"/>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>692339</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>RUTAN KELAS II B BATURAJA</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="n">
+        <v>5210000</v>
+      </c>
+      <c r="N172" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O172" t="n">
+        <v>2</v>
+      </c>
+      <c r="P172" t="n">
+        <v>5210000</v>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" t="inlineStr"/>
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>402267</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="n">
+        <v>2014580</v>
+      </c>
+      <c r="N173" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O173" t="n">
+        <v>2</v>
+      </c>
+      <c r="P173" t="n">
+        <v>2014580</v>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" t="inlineStr"/>
+      <c r="C174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>402267</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="n">
+        <v>680800</v>
+      </c>
+      <c r="N174" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O174" t="n">
+        <v>2</v>
+      </c>
+      <c r="P174" t="n">
+        <v>680800</v>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" t="inlineStr"/>
+      <c r="C175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>402267</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="n">
+        <v>3520000</v>
+      </c>
+      <c r="N175" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O175" t="n">
+        <v>2</v>
+      </c>
+      <c r="P175" t="n">
+        <v>3520000</v>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" t="inlineStr"/>
+      <c r="C176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>665307</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>POLRES OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="n">
+        <v>120000000</v>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="n">
+        <v>24770827</v>
+      </c>
+      <c r="N176" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O176" t="n">
+        <v>2</v>
+      </c>
+      <c r="P176" t="n">
+        <v>24770827</v>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" t="inlineStr"/>
+      <c r="C177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>692339</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>RUTAN KELAS II B BATURAJA</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="n">
+        <v>6727500</v>
+      </c>
+      <c r="N177" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O177" t="n">
+        <v>2</v>
+      </c>
+      <c r="P177" t="n">
+        <v>6727500</v>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" t="inlineStr"/>
+      <c r="C178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>641681</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>POLRES OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="n">
+        <v>120000000</v>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="n">
+        <v>11500000</v>
+      </c>
+      <c r="N178" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O178" t="n">
+        <v>2</v>
+      </c>
+      <c r="P178" t="n">
+        <v>11500000</v>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" t="inlineStr"/>
+      <c r="C179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>685001</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>PUSLATPUR KODIKLATAD</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="N179" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O179" t="n">
+        <v>2</v>
+      </c>
+      <c r="P179" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" t="inlineStr"/>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>641681</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>POLRES OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="n">
+        <v>120000000</v>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="n">
+        <v>11500000</v>
+      </c>
+      <c r="N180" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O180" t="n">
+        <v>2</v>
+      </c>
+      <c r="P180" t="n">
+        <v>11500000</v>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" t="inlineStr"/>
+      <c r="C181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>007208</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="n">
+        <v>9749809</v>
+      </c>
+      <c r="N181" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O181" t="n">
+        <v>2</v>
+      </c>
+      <c r="P181" t="n">
+        <v>9749809</v>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" t="inlineStr"/>
+      <c r="C182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="n">
+        <v>2410602</v>
+      </c>
+      <c r="N182" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O182" t="n">
+        <v>2</v>
+      </c>
+      <c r="P182" t="n">
+        <v>2410602</v>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" t="inlineStr"/>
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="n">
+        <v>2190000</v>
+      </c>
+      <c r="N183" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O183" t="n">
+        <v>2</v>
+      </c>
+      <c r="P183" t="n">
+        <v>2190000</v>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" t="inlineStr"/>
+      <c r="C184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>656553</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="n">
+        <v>1980000</v>
+      </c>
+      <c r="N184" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O184" t="n">
+        <v>2</v>
+      </c>
+      <c r="P184" t="n">
+        <v>1980000</v>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" t="inlineStr"/>
+      <c r="C185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="n">
+        <v>1575090</v>
+      </c>
+      <c r="N185" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O185" t="n">
+        <v>2</v>
+      </c>
+      <c r="P185" t="n">
+        <v>1575090</v>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" t="inlineStr"/>
+      <c r="C186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>641681</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>POLRES OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="n">
+        <v>120000000</v>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="n">
+        <v>38610000</v>
+      </c>
+      <c r="N186" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O186" t="n">
+        <v>2</v>
+      </c>
+      <c r="P186" t="n">
+        <v>38610000</v>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" t="inlineStr"/>
+      <c r="C187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>007208</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="n">
+        <v>9586654</v>
+      </c>
+      <c r="N187" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O187" t="n">
+        <v>2</v>
+      </c>
+      <c r="P187" t="n">
+        <v>9586654</v>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" t="inlineStr"/>
+      <c r="C188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>685001</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>PUSLATPUR KODIKLATAD</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" t="n">
+        <v>225000</v>
+      </c>
+      <c r="N188" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O188" t="n">
+        <v>3</v>
+      </c>
+      <c r="P188" t="n">
+        <v>225000</v>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" t="inlineStr"/>
+      <c r="C189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>692339</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>RUTAN KELAS II B BATURAJA</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="n">
+        <v>6727500</v>
+      </c>
+      <c r="N189" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O189" t="n">
+        <v>2</v>
+      </c>
+      <c r="P189" t="n">
+        <v>6727500</v>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" t="inlineStr"/>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>656574</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" t="n">
+        <v>67050</v>
+      </c>
+      <c r="N190" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O190" t="n">
+        <v>3</v>
+      </c>
+      <c r="P190" t="n">
+        <v>67050</v>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" t="inlineStr"/>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>692625</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>BAPAS KELAS II OKU INDUK</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="N191" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O191" t="n">
+        <v>3</v>
+      </c>
+      <c r="P191" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" t="inlineStr"/>
+      <c r="C192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>665292</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>POLRES OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="n">
+        <v>80000000</v>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" t="n">
+        <v>16512000</v>
+      </c>
+      <c r="N192" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O192" t="n">
+        <v>3</v>
+      </c>
+      <c r="P192" t="n">
+        <v>16512000</v>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" t="inlineStr"/>
+      <c r="C193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>656560</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" t="n">
+        <v>2258589</v>
+      </c>
+      <c r="N193" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O193" t="n">
+        <v>3</v>
+      </c>
+      <c r="P193" t="n">
+        <v>2258589</v>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" t="inlineStr"/>
+      <c r="C194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>656560</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="n">
+        <v>347200</v>
+      </c>
+      <c r="N194" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O194" t="n">
+        <v>3</v>
+      </c>
+      <c r="P194" t="n">
+        <v>347200</v>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" t="inlineStr"/>
+      <c r="C195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>656560</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="n">
+        <v>3429000</v>
+      </c>
+      <c r="N195" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O195" t="n">
+        <v>3</v>
+      </c>
+      <c r="P195" t="n">
+        <v>3429000</v>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" t="inlineStr"/>
+      <c r="C196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="n">
+        <v>4910000</v>
+      </c>
+      <c r="N196" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O196" t="n">
+        <v>3</v>
+      </c>
+      <c r="P196" t="n">
+        <v>4910000</v>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" t="inlineStr"/>
+      <c r="C197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>424245</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr"/>
+      <c r="H197" t="n">
+        <v>8800000</v>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" t="n">
+        <v>2223600</v>
+      </c>
+      <c r="N197" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O197" t="n">
+        <v>3</v>
+      </c>
+      <c r="P197" t="n">
+        <v>2223600</v>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" t="inlineStr"/>
+      <c r="C198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>111079</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" t="n">
+        <v>2695000</v>
+      </c>
+      <c r="N198" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O198" t="n">
+        <v>3</v>
+      </c>
+      <c r="P198" t="n">
+        <v>2695000</v>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" t="inlineStr"/>
+      <c r="C199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>410574</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="n">
+        <v>4924945</v>
+      </c>
+      <c r="N199" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O199" t="n">
+        <v>3</v>
+      </c>
+      <c r="P199" t="n">
+        <v>4924945</v>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" t="inlineStr"/>
+      <c r="C200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>410574</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="n">
+        <v>10000</v>
+      </c>
+      <c r="N200" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O200" t="n">
+        <v>3</v>
+      </c>
+      <c r="P200" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" t="inlineStr"/>
+      <c r="C201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>410574</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" t="n">
+        <v>3118829</v>
+      </c>
+      <c r="N201" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O201" t="n">
+        <v>3</v>
+      </c>
+      <c r="P201" t="n">
+        <v>3118829</v>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" t="inlineStr"/>
+      <c r="C202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="n">
+        <v>4130000</v>
+      </c>
+      <c r="N202" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O202" t="n">
+        <v>3</v>
+      </c>
+      <c r="P202" t="n">
+        <v>4130000</v>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" t="inlineStr"/>
+      <c r="C203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>402267</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr"/>
+      <c r="H203" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="n">
+        <v>10000</v>
+      </c>
+      <c r="N203" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O203" t="n">
+        <v>3</v>
+      </c>
+      <c r="P203" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" t="inlineStr"/>
+      <c r="C204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>402267</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr"/>
+      <c r="H204" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="n">
+        <v>1329550</v>
+      </c>
+      <c r="N204" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O204" t="n">
+        <v>3</v>
+      </c>
+      <c r="P204" t="n">
+        <v>1329550</v>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" t="inlineStr"/>
+      <c r="C205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>402267</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr"/>
+      <c r="H205" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" t="n">
+        <v>944800</v>
+      </c>
+      <c r="N205" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O205" t="n">
+        <v>3</v>
+      </c>
+      <c r="P205" t="n">
+        <v>944800</v>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" t="inlineStr"/>
+      <c r="C206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>402267</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr"/>
+      <c r="H206" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr"/>
+      <c r="M206" t="n">
+        <v>3398978</v>
+      </c>
+      <c r="N206" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O206" t="n">
+        <v>3</v>
+      </c>
+      <c r="P206" t="n">
+        <v>3398978</v>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" t="inlineStr"/>
+      <c r="C207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>402267</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr"/>
+      <c r="H207" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr"/>
+      <c r="M207" t="n">
+        <v>1818120</v>
+      </c>
+      <c r="N207" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O207" t="n">
+        <v>3</v>
+      </c>
+      <c r="P207" t="n">
+        <v>1818120</v>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" t="inlineStr"/>
+      <c r="C208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>685001</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>PUSLATPUR KODIKLATAD</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr"/>
+      <c r="H208" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr"/>
+      <c r="M208" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="N208" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O208" t="n">
+        <v>3</v>
+      </c>
+      <c r="P208" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" t="inlineStr"/>
+      <c r="C209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>656553</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr"/>
+      <c r="H209" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr"/>
+      <c r="M209" t="n">
+        <v>1995000</v>
+      </c>
+      <c r="N209" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O209" t="n">
+        <v>3</v>
+      </c>
+      <c r="P209" t="n">
+        <v>1995000</v>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" t="inlineStr"/>
+      <c r="C210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>641681</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>POLRES OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr"/>
+      <c r="H210" t="n">
+        <v>120000000</v>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr"/>
+      <c r="M210" t="n">
+        <v>11500000</v>
+      </c>
+      <c r="N210" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O210" t="n">
+        <v>3</v>
+      </c>
+      <c r="P210" t="n">
+        <v>11500000</v>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" t="inlineStr"/>
+      <c r="C211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>007130</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr"/>
+      <c r="H211" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr"/>
+      <c r="M211" t="n">
+        <v>198180</v>
+      </c>
+      <c r="N211" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O211" t="n">
+        <v>3</v>
+      </c>
+      <c r="P211" t="n">
+        <v>198180</v>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" t="inlineStr"/>
+      <c r="C212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>641681</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>POLRES OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr"/>
+      <c r="H212" t="n">
+        <v>120000000</v>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr"/>
+      <c r="M212" t="n">
+        <v>19305000</v>
+      </c>
+      <c r="N212" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O212" t="n">
+        <v>3</v>
+      </c>
+      <c r="P212" t="n">
+        <v>19305000</v>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" t="inlineStr"/>
+      <c r="C213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>401944</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr"/>
+      <c r="H213" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr"/>
+      <c r="M213" t="n">
+        <v>498320</v>
+      </c>
+      <c r="N213" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O213" t="n">
+        <v>3</v>
+      </c>
+      <c r="P213" t="n">
+        <v>498320</v>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" t="inlineStr"/>
+      <c r="C214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>401944</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr"/>
+      <c r="H214" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr"/>
+      <c r="M214" t="n">
+        <v>1590457</v>
+      </c>
+      <c r="N214" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O214" t="n">
+        <v>3</v>
+      </c>
+      <c r="P214" t="n">
+        <v>1590457</v>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" t="inlineStr"/>
+      <c r="C215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>401944</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr"/>
+      <c r="H215" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr"/>
+      <c r="M215" t="n">
+        <v>2239410</v>
+      </c>
+      <c r="N215" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O215" t="n">
+        <v>3</v>
+      </c>
+      <c r="P215" t="n">
+        <v>2239410</v>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" t="inlineStr"/>
+      <c r="C216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>401944</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" t="inlineStr"/>
+      <c r="H216" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr"/>
+      <c r="M216" t="n">
+        <v>3512800</v>
+      </c>
+      <c r="N216" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O216" t="n">
+        <v>3</v>
+      </c>
+      <c r="P216" t="n">
+        <v>3512800</v>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" t="inlineStr"/>
+      <c r="C217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>401944</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr"/>
+      <c r="H217" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr"/>
+      <c r="M217" t="n">
+        <v>10000</v>
+      </c>
+      <c r="N217" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O217" t="n">
+        <v>3</v>
+      </c>
+      <c r="P217" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" t="inlineStr"/>
+      <c r="C218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>692339</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>RUTAN KELAS II B BATURAJA</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr"/>
+      <c r="M218" t="n">
+        <v>6331240</v>
+      </c>
+      <c r="N218" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O218" t="n">
+        <v>3</v>
+      </c>
+      <c r="P218" t="n">
+        <v>6331240</v>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" t="inlineStr"/>
+      <c r="C219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>641681</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>POLRES OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr"/>
+      <c r="H219" t="n">
+        <v>120000000</v>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr"/>
+      <c r="M219" t="n">
+        <v>23405000</v>
+      </c>
+      <c r="N219" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O219" t="n">
+        <v>3</v>
+      </c>
+      <c r="P219" t="n">
+        <v>23405000</v>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" t="inlineStr"/>
+      <c r="C220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>402267</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr"/>
+      <c r="H220" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr"/>
+      <c r="M220" t="n">
+        <v>3417810</v>
+      </c>
+      <c r="N220" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O220" t="n">
+        <v>3</v>
+      </c>
+      <c r="P220" t="n">
+        <v>3417810</v>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" t="inlineStr"/>
+      <c r="C221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr"/>
+      <c r="H221" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr"/>
+      <c r="M221" t="n">
+        <v>1347500</v>
+      </c>
+      <c r="N221" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O221" t="n">
+        <v>3</v>
+      </c>
+      <c r="P221" t="n">
+        <v>1347500</v>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" t="inlineStr"/>
+      <c r="C222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr"/>
+      <c r="H222" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr"/>
+      <c r="M222" t="n">
+        <v>539000</v>
+      </c>
+      <c r="N222" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O222" t="n">
+        <v>3</v>
+      </c>
+      <c r="P222" t="n">
+        <v>539000</v>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" t="inlineStr"/>
+      <c r="C223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr"/>
+      <c r="H223" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr"/>
+      <c r="M223" t="n">
+        <v>8771468</v>
+      </c>
+      <c r="N223" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O223" t="n">
+        <v>3</v>
+      </c>
+      <c r="P223" t="n">
+        <v>8771468</v>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" t="inlineStr"/>
+      <c r="C224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr"/>
+      <c r="H224" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr"/>
+      <c r="M224" t="n">
+        <v>82960</v>
+      </c>
+      <c r="N224" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O224" t="n">
+        <v>3</v>
+      </c>
+      <c r="P224" t="n">
+        <v>82960</v>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" t="inlineStr"/>
+      <c r="C225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr"/>
+      <c r="H225" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr"/>
+      <c r="M225" t="n">
+        <v>1979500</v>
+      </c>
+      <c r="N225" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O225" t="n">
+        <v>3</v>
+      </c>
+      <c r="P225" t="n">
+        <v>1979500</v>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" t="inlineStr"/>
+      <c r="C226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>685001</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>PUSLATPUR KODIKLATAD</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr"/>
+      <c r="H226" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr"/>
+      <c r="M226" t="n">
+        <v>225000</v>
+      </c>
+      <c r="N226" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O226" t="n">
+        <v>3</v>
+      </c>
+      <c r="P226" t="n">
+        <v>225000</v>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" t="inlineStr"/>
+      <c r="C227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>665307</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>POLRES OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr"/>
+      <c r="H227" t="n">
+        <v>120000000</v>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr"/>
+      <c r="M227" t="n">
+        <v>24183457</v>
+      </c>
+      <c r="N227" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O227" t="n">
+        <v>3</v>
+      </c>
+      <c r="P227" t="n">
+        <v>24183457</v>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" t="inlineStr"/>
+      <c r="C228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>098963</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>PENGADILAN NEGERI BATURAJA</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr"/>
+      <c r="H228" t="n">
+        <v>14400000</v>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr"/>
+      <c r="M228" t="n">
+        <v>94000</v>
+      </c>
+      <c r="N228" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O228" t="n">
+        <v>3</v>
+      </c>
+      <c r="P228" t="n">
+        <v>94000</v>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" t="inlineStr"/>
+      <c r="C229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>098963</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>PENGADILAN NEGERI BATURAJA</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr"/>
+      <c r="H229" t="n">
+        <v>14400000</v>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr"/>
+      <c r="M229" t="n">
+        <v>804000</v>
+      </c>
+      <c r="N229" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O229" t="n">
+        <v>3</v>
+      </c>
+      <c r="P229" t="n">
+        <v>804000</v>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" t="inlineStr"/>
+      <c r="C230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>098963</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>PENGADILAN NEGERI BATURAJA</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="inlineStr"/>
+      <c r="H230" t="n">
+        <v>14400000</v>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr"/>
+      <c r="M230" t="n">
+        <v>3082879</v>
+      </c>
+      <c r="N230" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O230" t="n">
+        <v>3</v>
+      </c>
+      <c r="P230" t="n">
+        <v>3082879</v>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" t="inlineStr"/>
+      <c r="C231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr"/>
+      <c r="H231" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr"/>
+      <c r="M231" t="n">
+        <v>2516000</v>
+      </c>
+      <c r="N231" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O231" t="n">
+        <v>3</v>
+      </c>
+      <c r="P231" t="n">
+        <v>2516000</v>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" t="inlineStr"/>
+      <c r="C232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>692339</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>RUTAN KELAS II B BATURAJA</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr"/>
+      <c r="H232" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr"/>
+      <c r="M232" t="n">
+        <v>3035000</v>
+      </c>
+      <c r="N232" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O232" t="n">
+        <v>3</v>
+      </c>
+      <c r="P232" t="n">
+        <v>3035000</v>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" t="inlineStr"/>
+      <c r="C233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>692339</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>RUTAN KELAS II B BATURAJA</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="inlineStr"/>
+      <c r="H233" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr"/>
+      <c r="M233" t="n">
+        <v>496832</v>
+      </c>
+      <c r="N233" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O233" t="n">
+        <v>3</v>
+      </c>
+      <c r="P233" t="n">
+        <v>496832</v>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" t="inlineStr"/>
+      <c r="C234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>665307</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>POLRES OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr"/>
+      <c r="G234" t="inlineStr"/>
+      <c r="H234" t="n">
+        <v>120000000</v>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr"/>
+      <c r="M234" t="n">
+        <v>13214610</v>
+      </c>
+      <c r="N234" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O234" t="n">
+        <v>3</v>
+      </c>
+      <c r="P234" t="n">
+        <v>13214610</v>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>234</v>
+      </c>
+      <c r="B235" t="inlineStr"/>
+      <c r="C235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>692339</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>RUTAN KELAS II B BATURAJA</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr"/>
+      <c r="H235" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr"/>
+      <c r="M235" t="n">
+        <v>591000</v>
+      </c>
+      <c r="N235" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O235" t="n">
+        <v>3</v>
+      </c>
+      <c r="P235" t="n">
+        <v>591000</v>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" t="inlineStr"/>
+      <c r="C236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>692339</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>RUTAN KELAS II B BATURAJA</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="inlineStr"/>
+      <c r="H236" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr"/>
+      <c r="M236" t="n">
+        <v>6200000</v>
+      </c>
+      <c r="N236" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O236" t="n">
+        <v>3</v>
+      </c>
+      <c r="P236" t="n">
+        <v>6200000</v>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>236</v>
+      </c>
+      <c r="B237" t="inlineStr"/>
+      <c r="C237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr"/>
+      <c r="G237" t="inlineStr"/>
+      <c r="H237" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr"/>
+      <c r="M237" t="n">
+        <v>532532</v>
+      </c>
+      <c r="N237" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O237" t="n">
+        <v>3</v>
+      </c>
+      <c r="P237" t="n">
+        <v>532532</v>
+      </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>237</v>
+      </c>
+      <c r="B238" t="inlineStr"/>
+      <c r="C238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr"/>
+      <c r="G238" t="inlineStr"/>
+      <c r="H238" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr"/>
+      <c r="M238" t="n">
+        <v>1542000</v>
+      </c>
+      <c r="N238" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O238" t="n">
+        <v>3</v>
+      </c>
+      <c r="P238" t="n">
+        <v>1542000</v>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>238</v>
+      </c>
+      <c r="B239" t="inlineStr"/>
+      <c r="C239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>656574</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr"/>
+      <c r="H239" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr"/>
+      <c r="M239" t="n">
+        <v>283500</v>
+      </c>
+      <c r="N239" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O239" t="n">
+        <v>3</v>
+      </c>
+      <c r="P239" t="n">
+        <v>283500</v>
+      </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>239</v>
+      </c>
+      <c r="B240" t="inlineStr"/>
+      <c r="C240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>692339</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>RUTAN KELAS II B BATURAJA</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="inlineStr"/>
+      <c r="H240" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr"/>
+      <c r="M240" t="n">
+        <v>562005</v>
+      </c>
+      <c r="N240" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O240" t="n">
+        <v>4</v>
+      </c>
+      <c r="P240" t="n">
+        <v>562005</v>
+      </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>240</v>
+      </c>
+      <c r="B241" t="inlineStr"/>
+      <c r="C241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>692339</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>RUTAN KELAS II B BATURAJA</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="inlineStr"/>
+      <c r="H241" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr"/>
+      <c r="M241" t="n">
+        <v>1793912</v>
+      </c>
+      <c r="N241" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O241" t="n">
+        <v>4</v>
+      </c>
+      <c r="P241" t="n">
+        <v>1793912</v>
+      </c>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>241</v>
+      </c>
+      <c r="B242" t="inlineStr"/>
+      <c r="C242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>692339</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>RUTAN KELAS II B BATURAJA</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr"/>
+      <c r="G242" t="inlineStr"/>
+      <c r="H242" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr"/>
+      <c r="M242" t="n">
+        <v>3721000</v>
+      </c>
+      <c r="N242" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O242" t="n">
+        <v>4</v>
+      </c>
+      <c r="P242" t="n">
+        <v>3721000</v>
+      </c>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>242</v>
+      </c>
+      <c r="B243" t="inlineStr"/>
+      <c r="C243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>402267</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr"/>
+      <c r="G243" t="inlineStr"/>
+      <c r="H243" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr"/>
+      <c r="M243" t="n">
+        <v>4663299</v>
+      </c>
+      <c r="N243" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O243" t="n">
+        <v>4</v>
+      </c>
+      <c r="P243" t="n">
+        <v>4663299</v>
+      </c>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>243</v>
+      </c>
+      <c r="B244" t="inlineStr"/>
+      <c r="C244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>402267</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr"/>
+      <c r="G244" t="inlineStr"/>
+      <c r="H244" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr"/>
+      <c r="M244" t="n">
+        <v>72032</v>
+      </c>
+      <c r="N244" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O244" t="n">
+        <v>4</v>
+      </c>
+      <c r="P244" t="n">
+        <v>72032</v>
+      </c>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>244</v>
+      </c>
+      <c r="B245" t="inlineStr"/>
+      <c r="C245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>402267</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr"/>
+      <c r="G245" t="inlineStr"/>
+      <c r="H245" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr"/>
+      <c r="M245" t="n">
+        <v>2522000</v>
+      </c>
+      <c r="N245" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O245" t="n">
+        <v>4</v>
+      </c>
+      <c r="P245" t="n">
+        <v>2522000</v>
+      </c>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>245</v>
+      </c>
+      <c r="B246" t="inlineStr"/>
+      <c r="C246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>656553</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr"/>
+      <c r="H246" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr"/>
+      <c r="M246" t="n">
+        <v>1990000</v>
+      </c>
+      <c r="N246" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O246" t="n">
+        <v>4</v>
+      </c>
+      <c r="P246" t="n">
+        <v>1990000</v>
+      </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>246</v>
+      </c>
+      <c r="B247" t="inlineStr"/>
+      <c r="C247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>656560</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr"/>
+      <c r="G247" t="inlineStr"/>
+      <c r="H247" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr"/>
+      <c r="M247" t="n">
+        <v>2256300</v>
+      </c>
+      <c r="N247" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O247" t="n">
+        <v>4</v>
+      </c>
+      <c r="P247" t="n">
+        <v>2256300</v>
+      </c>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>247</v>
+      </c>
+      <c r="B248" t="inlineStr"/>
+      <c r="C248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>656560</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr"/>
+      <c r="G248" t="inlineStr"/>
+      <c r="H248" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr"/>
+      <c r="M248" t="n">
+        <v>423000</v>
+      </c>
+      <c r="N248" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O248" t="n">
+        <v>4</v>
+      </c>
+      <c r="P248" t="n">
+        <v>423000</v>
+      </c>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>248</v>
+      </c>
+      <c r="B249" t="inlineStr"/>
+      <c r="C249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>424245</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr"/>
+      <c r="G249" t="inlineStr"/>
+      <c r="H249" t="n">
+        <v>8800000</v>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr"/>
+      <c r="M249" t="n">
+        <v>1067000</v>
+      </c>
+      <c r="N249" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O249" t="n">
+        <v>4</v>
+      </c>
+      <c r="P249" t="n">
+        <v>1067000</v>
+      </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>249</v>
+      </c>
+      <c r="B250" t="inlineStr"/>
+      <c r="C250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>692339</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>RUTAN KELAS II B BATURAJA</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr"/>
+      <c r="G250" t="inlineStr"/>
+      <c r="H250" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr"/>
+      <c r="M250" t="n">
+        <v>2526125</v>
+      </c>
+      <c r="N250" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O250" t="n">
+        <v>4</v>
+      </c>
+      <c r="P250" t="n">
+        <v>2526125</v>
+      </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>250</v>
+      </c>
+      <c r="B251" t="inlineStr"/>
+      <c r="C251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>692339</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>RUTAN KELAS II B BATURAJA</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr"/>
+      <c r="G251" t="inlineStr"/>
+      <c r="H251" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr"/>
+      <c r="M251" t="n">
+        <v>4225000</v>
+      </c>
+      <c r="N251" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O251" t="n">
+        <v>4</v>
+      </c>
+      <c r="P251" t="n">
+        <v>4225000</v>
+      </c>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>251</v>
+      </c>
+      <c r="B252" t="inlineStr"/>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr"/>
+      <c r="G252" t="inlineStr"/>
+      <c r="H252" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr"/>
+      <c r="M252" t="n">
+        <v>10000</v>
+      </c>
+      <c r="N252" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O252" t="n">
+        <v>4</v>
+      </c>
+      <c r="P252" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>252</v>
+      </c>
+      <c r="B253" t="inlineStr"/>
+      <c r="C253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr"/>
+      <c r="G253" t="inlineStr"/>
+      <c r="H253" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr"/>
+      <c r="M253" t="n">
+        <v>82960</v>
+      </c>
+      <c r="N253" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O253" t="n">
+        <v>4</v>
+      </c>
+      <c r="P253" t="n">
+        <v>82960</v>
+      </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>253</v>
+      </c>
+      <c r="B254" t="inlineStr"/>
+      <c r="C254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr"/>
+      <c r="G254" t="inlineStr"/>
+      <c r="H254" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr"/>
+      <c r="M254" t="n">
+        <v>650000</v>
+      </c>
+      <c r="N254" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O254" t="n">
+        <v>4</v>
+      </c>
+      <c r="P254" t="n">
+        <v>650000</v>
+      </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>254</v>
+      </c>
+      <c r="B255" t="inlineStr"/>
+      <c r="C255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr"/>
+      <c r="G255" t="inlineStr"/>
+      <c r="H255" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr"/>
+      <c r="M255" t="n">
+        <v>850000</v>
+      </c>
+      <c r="N255" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O255" t="n">
+        <v>4</v>
+      </c>
+      <c r="P255" t="n">
+        <v>850000</v>
+      </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>255</v>
+      </c>
+      <c r="B256" t="inlineStr"/>
+      <c r="C256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr"/>
+      <c r="G256" t="inlineStr"/>
+      <c r="H256" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr"/>
+      <c r="M256" t="n">
+        <v>400000</v>
+      </c>
+      <c r="N256" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O256" t="n">
+        <v>4</v>
+      </c>
+      <c r="P256" t="n">
+        <v>400000</v>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>256</v>
+      </c>
+      <c r="B257" t="inlineStr"/>
+      <c r="C257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr"/>
+      <c r="G257" t="inlineStr"/>
+      <c r="H257" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr"/>
+      <c r="M257" t="n">
+        <v>4395000</v>
+      </c>
+      <c r="N257" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O257" t="n">
+        <v>4</v>
+      </c>
+      <c r="P257" t="n">
+        <v>4395000</v>
+      </c>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>257</v>
+      </c>
+      <c r="B258" t="inlineStr"/>
+      <c r="C258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>410574</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr"/>
+      <c r="G258" t="inlineStr"/>
+      <c r="H258" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr"/>
+      <c r="M258" t="n">
+        <v>4849486</v>
+      </c>
+      <c r="N258" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O258" t="n">
+        <v>4</v>
+      </c>
+      <c r="P258" t="n">
+        <v>4849486</v>
+      </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>258</v>
+      </c>
+      <c r="B259" t="inlineStr"/>
+      <c r="C259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>401944</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr"/>
+      <c r="G259" t="inlineStr"/>
+      <c r="H259" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr"/>
+      <c r="M259" t="n">
+        <v>2574000</v>
+      </c>
+      <c r="N259" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O259" t="n">
+        <v>4</v>
+      </c>
+      <c r="P259" t="n">
+        <v>2574000</v>
+      </c>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>259</v>
+      </c>
+      <c r="B260" t="inlineStr"/>
+      <c r="C260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>401944</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr"/>
+      <c r="G260" t="inlineStr"/>
+      <c r="H260" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr"/>
+      <c r="M260" t="n">
+        <v>498320</v>
+      </c>
+      <c r="N260" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O260" t="n">
+        <v>4</v>
+      </c>
+      <c r="P260" t="n">
+        <v>498320</v>
+      </c>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>260</v>
+      </c>
+      <c r="B261" t="inlineStr"/>
+      <c r="C261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>401944</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="inlineStr"/>
+      <c r="H261" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr"/>
+      <c r="M261" t="n">
+        <v>78000</v>
+      </c>
+      <c r="N261" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O261" t="n">
+        <v>4</v>
+      </c>
+      <c r="P261" t="n">
+        <v>78000</v>
+      </c>
+      <c r="Q261" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>261</v>
+      </c>
+      <c r="B262" t="inlineStr"/>
+      <c r="C262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>401944</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr"/>
+      <c r="G262" t="inlineStr"/>
+      <c r="H262" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>KKP</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr"/>
+      <c r="M262" t="n">
+        <v>1874700</v>
+      </c>
+      <c r="N262" t="n">
+        <v>2026</v>
+      </c>
+      <c r="O262" t="n">
+        <v>4</v>
+      </c>
+      <c r="P262" t="n">
+        <v>1874700</v>
+      </c>
+      <c r="Q262" t="inlineStr">
+        <is>
+          <t>BARU</t>
         </is>
       </c>
     </row>

--- a/data_kkp/KKP_MASTER.xlsx
+++ b/data_kkp/KKP_MASTER.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K108"/>
+  <dimension ref="A1:K156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,157 +489,125 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>MAHKAMAH AGUNG</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>007130</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>24000000</v>
+        <v>8000000</v>
       </c>
       <c r="K2" t="n">
-        <v>11321000</v>
+        <v>145429</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>MAHKAMAH AGUNG</t>
-        </is>
-      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>007130</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>24000000</v>
+        <v>8000000</v>
       </c>
       <c r="K3" t="n">
-        <v>17922000</v>
+        <v>198180</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>MAHKAMAH AGUNG</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>24000000</v>
       </c>
       <c r="K4" t="n">
-        <v>2650000</v>
+        <v>19336463</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>MAHKAMAH AGUNG</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>098963</t>
@@ -652,41 +620,33 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>24000000</v>
+        <v>43200000</v>
       </c>
       <c r="K5" t="n">
-        <v>3905000</v>
+        <v>10861535</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>MAHKAMAH AGUNG</t>
-        </is>
-      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>098963</t>
@@ -699,229 +659,189 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>24000000</v>
+        <v>43200000</v>
       </c>
       <c r="K6" t="n">
-        <v>3500000</v>
+        <v>3980879</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>MAHKAMAH AGUNG</t>
-        </is>
-      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>24000000</v>
       </c>
       <c r="K7" t="n">
-        <v>13874500</v>
+        <v>11031747</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>MAHKAMAH AGUNG</t>
-        </is>
-      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H8" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>24000000</v>
+        <v>12000000</v>
       </c>
       <c r="K8" t="n">
-        <v>3897000</v>
+        <v>2695000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>MAHKAMAH AGUNG</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>24000000</v>
       </c>
       <c r="K9" t="n">
-        <v>13995500</v>
+        <v>5926136</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>MAHKAMAH AGUNG</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H10" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>24000000</v>
       </c>
       <c r="K10" t="n">
-        <v>9151500</v>
+        <v>5142960</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>MAHKAMAH AGUNG</t>
-        </is>
-      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>401944</t>
@@ -934,41 +854,33 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>16000000</v>
+        <v>40000000</v>
       </c>
       <c r="K11" t="n">
-        <v>3618000</v>
+        <v>7850987</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>MAHKAMAH AGUNG</t>
-        </is>
-      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>401944</t>
@@ -981,1764 +893,1468 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>10000000</v>
+        <v>32000000</v>
       </c>
       <c r="K12" t="n">
-        <v>212017</v>
+        <v>5025020</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>MAHKAMAH AGUNG</t>
-        </is>
-      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>16000000</v>
+        <v>72000000</v>
       </c>
       <c r="K13" t="n">
-        <v>1362070</v>
+        <v>9817209</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>MAHKAMAH AGUNG</t>
-        </is>
-      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>16000000</v>
+        <v>56000000</v>
       </c>
       <c r="K14" t="n">
-        <v>2800570</v>
+        <v>14099104</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>MAHKAMAH AGUNG</t>
-        </is>
-      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>16000000</v>
+        <v>48000000</v>
       </c>
       <c r="K15" t="n">
-        <v>4221853</v>
+        <v>10919258</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>MAHKAMAH AGUNG</t>
-        </is>
-      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>16000000</v>
+        <v>24000000</v>
       </c>
       <c r="K16" t="n">
-        <v>4371470</v>
+        <v>7257331</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>MAHKAMAH AGUNG</t>
-        </is>
-      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H17" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>10000000</v>
+        <v>40000000</v>
       </c>
       <c r="K17" t="n">
-        <v>1933320</v>
+        <v>12334663</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>MAHKAMAH AGUNG</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H18" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>16000000</v>
+        <v>120000000</v>
       </c>
       <c r="K18" t="n">
-        <v>5285170</v>
+        <v>8053774</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>MAHKAMAH AGUNG</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H19" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>16000000</v>
+        <v>40000000</v>
       </c>
       <c r="K19" t="n">
-        <v>7754710</v>
+        <v>4849486</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>MAHKAMAH AGUNG</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>424245</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H20" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>16000000</v>
+        <v>17600000</v>
       </c>
       <c r="K20" t="n">
-        <v>10124059</v>
+        <v>3273950</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>MAHKAMAH AGUNG</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>424245</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H21" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>10000000</v>
+        <v>8800000</v>
       </c>
       <c r="K21" t="n">
-        <v>3348270</v>
+        <v>2223600</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>MAHKAMAH AGUNG</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>424245</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>10000000</v>
+        <v>8800000</v>
       </c>
       <c r="K22" t="n">
-        <v>1168200</v>
+        <v>1067000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>MAHKAMAH AGUNG</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H23" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>10000000</v>
+        <v>40000000</v>
       </c>
       <c r="K23" t="n">
-        <v>9026788</v>
+        <v>5055500</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>23</v>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>MAHKAMAH AGUNG</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H24" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>10000000</v>
+        <v>100000000</v>
       </c>
       <c r="K24" t="n">
-        <v>1068054</v>
+        <v>12720428</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>MAHKAMAH AGUNG</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>10000000</v>
+        <v>120000000</v>
       </c>
       <c r="K25" t="n">
-        <v>7992275</v>
+        <v>6387960</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>25</v>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>MAHKAMAH AGUNG</t>
-        </is>
-      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>641681</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>POLRES OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H26" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>10000000</v>
+        <v>360000000</v>
       </c>
       <c r="K26" t="n">
-        <v>8596433</v>
+        <v>61610000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>26</v>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>MAHKAMAH AGUNG</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>641681</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>POLRES OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H27" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>10000000</v>
+        <v>360000000</v>
       </c>
       <c r="K27" t="n">
-        <v>10000</v>
+        <v>54210000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>27</v>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>MAHKAMAH AGUNG</t>
-        </is>
-      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>656553</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H28" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>10000000</v>
+        <v>2000000</v>
       </c>
       <c r="K28" t="n">
-        <v>14785443</v>
+        <v>1721500</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>28</v>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>MAHKAMAH AGUNG</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>656553</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H29" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>10000000</v>
+        <v>6000000</v>
       </c>
       <c r="K29" t="n">
-        <v>10000</v>
+        <v>5455000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>29</v>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>006</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>KEJAKSAAN REPUBLIK INDONESIA</t>
-        </is>
-      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>007130</t>
+          <t>656553</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H30" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>6000000</v>
+        <v>2000000</v>
       </c>
       <c r="K30" t="n">
-        <v>770670</v>
+        <v>1995000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>30</v>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>006</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>KEJAKSAAN REPUBLIK INDONESIA</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>007130</t>
+          <t>656553</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H31" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>6000000</v>
+        <v>2000000</v>
       </c>
       <c r="K31" t="n">
-        <v>160005</v>
+        <v>1990000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>31</v>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>006</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>KEJAKSAAN REPUBLIK INDONESIA</t>
-        </is>
-      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>007130</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H32" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>6000000</v>
+        <v>30000000</v>
       </c>
       <c r="K32" t="n">
-        <v>1160190</v>
+        <v>6034789</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>32</v>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>006</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>KEJAKSAAN REPUBLIK INDONESIA</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>40000000</v>
+        <v>20000000</v>
       </c>
       <c r="K33" t="n">
-        <v>9180565</v>
+        <v>2679300</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
         <v>33</v>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>006</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>KEJAKSAAN REPUBLIK INDONESIA</t>
-        </is>
-      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>656574</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>40000000</v>
+        <v>4000000</v>
       </c>
       <c r="K34" t="n">
-        <v>8752087</v>
+        <v>1216870</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>34</v>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>006</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>KEJAKSAAN REPUBLIK INDONESIA</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>656574</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>40000000</v>
+        <v>4000000</v>
       </c>
       <c r="K35" t="n">
-        <v>16690098</v>
+        <v>350550</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
         <v>35</v>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>006</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>KEJAKSAAN REPUBLIK INDONESIA</t>
-        </is>
-      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>665292</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>POLRES OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H36" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>40000000</v>
+        <v>80000000</v>
       </c>
       <c r="K36" t="n">
-        <v>26763409</v>
+        <v>16512000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
         <v>36</v>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>006</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>KEJAKSAAN REPUBLIK INDONESIA</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>665292</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>POLRES OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H37" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>40000000</v>
+        <v>80000000</v>
       </c>
       <c r="K37" t="n">
-        <v>22446603</v>
+        <v>16512000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
         <v>37</v>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>012</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>KEMENTERIAN PERTAHANAN</t>
-        </is>
-      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>685001</t>
+          <t>665307</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>PUSLATPUR KODIKLATAD</t>
+          <t>POLRES OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H38" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>3000000</v>
+        <v>120000000</v>
       </c>
       <c r="K38" t="n">
-        <v>1500000</v>
+        <v>59780000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
         <v>38</v>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>015</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>KEMENTERIAN KEUANGAN</t>
-        </is>
-      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>665307</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>POLRES OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H39" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>40000000</v>
+        <v>120000000</v>
       </c>
       <c r="K39" t="n">
-        <v>19651577</v>
+        <v>24770827</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
         <v>39</v>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>015</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>KEMENTERIAN KEUANGAN</t>
-        </is>
-      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>665307</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>POLRES OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H40" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>40000000</v>
+        <v>240000000</v>
       </c>
       <c r="K40" t="n">
-        <v>9670989</v>
+        <v>37398067</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
         <v>40</v>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>015</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>KEMENTERIAN KEUANGAN</t>
-        </is>
-      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H41" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>40000000</v>
+        <v>36000000</v>
       </c>
       <c r="K41" t="n">
-        <v>6743111</v>
+        <v>8638865</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
         <v>41</v>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>015</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>KEMENTERIAN KEUANGAN</t>
-        </is>
-      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H42" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>40000000</v>
+        <v>30000000</v>
       </c>
       <c r="K42" t="n">
-        <v>9978760</v>
+        <v>13630532</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
         <v>42</v>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>015</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>KEMENTERIAN KEUANGAN</t>
-        </is>
-      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>685001</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>PUSLATPUR KODIKLATAD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H43" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>40000000</v>
+        <v>2400000</v>
       </c>
       <c r="K43" t="n">
-        <v>22314667</v>
+        <v>2400000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
         <v>43</v>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>015</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>KEMENTERIAN KEUANGAN</t>
-        </is>
-      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>685001</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>PUSLATPUR KODIKLATAD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H44" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>40000000</v>
+        <v>7200000</v>
       </c>
       <c r="K44" t="n">
-        <v>8400111</v>
+        <v>2850000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
         <v>44</v>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>015</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>KEMENTERIAN KEUANGAN</t>
-        </is>
-      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>692339</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H45" t="n">
         <v>2</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>70000000</v>
+        <v>40000000</v>
       </c>
       <c r="K45" t="n">
-        <v>1489998</v>
+        <v>30090000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>45</v>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>015</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>KEMENTERIAN KEUANGAN</t>
-        </is>
-      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>692339</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>10000000</v>
+        <v>40000000</v>
       </c>
       <c r="K46" t="n">
-        <v>3211146</v>
+        <v>16654072</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
         <v>46</v>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>015</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>KEMENTERIAN KEUANGAN</t>
-        </is>
-      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>692339</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H47" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>10000000</v>
+        <v>40000000</v>
       </c>
       <c r="K47" t="n">
-        <v>5902139</v>
+        <v>12828042</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
         <v>47</v>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>015</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>KEMENTERIAN KEUANGAN</t>
-        </is>
-      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>692625</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>BAPAS KELAS II OKU INDUK</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H48" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>10000000</v>
+        <v>6000000</v>
       </c>
       <c r="K48" t="n">
-        <v>6077473</v>
+        <v>2550000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
         <v>48</v>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>015</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>KEMENTERIAN KEUANGAN</t>
-        </is>
-      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>692625</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>BAPAS KELAS II OKU INDUK</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="H49" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>10000000</v>
+        <v>6000000</v>
       </c>
       <c r="K49" t="n">
-        <v>7744485</v>
+        <v>2500000</v>
       </c>
     </row>
     <row r="50">
@@ -2747,34 +2363,34 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>KEMENTERIAN KEUANGAN</t>
+          <t>MAHKAMAH AGUNG</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G50" t="n">
         <v>2025</v>
       </c>
       <c r="H50" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2782,10 +2398,10 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>10000000</v>
+        <v>24000000</v>
       </c>
       <c r="K50" t="n">
-        <v>2241786</v>
+        <v>11321000</v>
       </c>
     </row>
     <row r="51">
@@ -2794,34 +2410,34 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>KEMENTERIAN KEUANGAN</t>
+          <t>MAHKAMAH AGUNG</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="G51" t="n">
         <v>2025</v>
       </c>
       <c r="H51" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2829,10 +2445,10 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>16000000</v>
+        <v>24000000</v>
       </c>
       <c r="K51" t="n">
-        <v>3889590</v>
+        <v>17922000</v>
       </c>
     </row>
     <row r="52">
@@ -2841,34 +2457,34 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>KEMENTERIAN KEUANGAN</t>
+          <t>MAHKAMAH AGUNG</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="G52" t="n">
         <v>2025</v>
       </c>
       <c r="H52" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -2876,10 +2492,10 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>16000000</v>
+        <v>24000000</v>
       </c>
       <c r="K52" t="n">
-        <v>68700000</v>
+        <v>2650000</v>
       </c>
     </row>
     <row r="53">
@@ -2888,34 +2504,34 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>KEMENTERIAN KEUANGAN</t>
+          <t>MAHKAMAH AGUNG</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G53" t="n">
         <v>2025</v>
       </c>
       <c r="H53" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -2923,10 +2539,10 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>16000000</v>
+        <v>24000000</v>
       </c>
       <c r="K53" t="n">
-        <v>33307620</v>
+        <v>3905000</v>
       </c>
     </row>
     <row r="54">
@@ -2935,34 +2551,34 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>KEMENTERIAN KEUANGAN</t>
+          <t>MAHKAMAH AGUNG</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="G54" t="n">
         <v>2025</v>
       </c>
       <c r="H54" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -2970,10 +2586,10 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>6000000</v>
+        <v>24000000</v>
       </c>
       <c r="K54" t="n">
-        <v>259000</v>
+        <v>3500000</v>
       </c>
     </row>
     <row r="55">
@@ -2982,34 +2598,34 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>024</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>KEMENTERIAN KESEHATAN</t>
+          <t>MAHKAMAH AGUNG</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>690801</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="G55" t="n">
         <v>2025</v>
       </c>
       <c r="H55" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3017,10 +2633,10 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>22000000</v>
+        <v>24000000</v>
       </c>
       <c r="K55" t="n">
-        <v>1865319</v>
+        <v>13874500</v>
       </c>
     </row>
     <row r="56">
@@ -3029,34 +2645,34 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>024</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>KEMENTERIAN KESEHATAN</t>
+          <t>MAHKAMAH AGUNG</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>690801</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="G56" t="n">
         <v>2025</v>
       </c>
       <c r="H56" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3064,10 +2680,10 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>22000000</v>
+        <v>24000000</v>
       </c>
       <c r="K56" t="n">
-        <v>2717905</v>
+        <v>3897000</v>
       </c>
     </row>
     <row r="57">
@@ -3076,22 +2692,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>KEMENTERIAN AGAMA</t>
+          <t>MAHKAMAH AGUNG</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>424245</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3111,10 +2727,10 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>10000000</v>
+        <v>24000000</v>
       </c>
       <c r="K57" t="n">
-        <v>568000</v>
+        <v>13995500</v>
       </c>
     </row>
     <row r="58">
@@ -3123,22 +2739,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>KEMENTERIAN AGAMA</t>
+          <t>MAHKAMAH AGUNG</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>553099</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3158,10 +2774,10 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>6000000</v>
+        <v>24000000</v>
       </c>
       <c r="K58" t="n">
-        <v>2911500</v>
+        <v>9151500</v>
       </c>
     </row>
     <row r="59">
@@ -3170,22 +2786,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK</t>
+          <t>MAHKAMAH AGUNG</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3205,10 +2821,10 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>28000000</v>
+        <v>16000000</v>
       </c>
       <c r="K59" t="n">
-        <v>19420000</v>
+        <v>3618000</v>
       </c>
     </row>
     <row r="60">
@@ -3217,22 +2833,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK</t>
+          <t>MAHKAMAH AGUNG</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3252,10 +2868,10 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>18000000</v>
+        <v>10000000</v>
       </c>
       <c r="K60" t="n">
-        <v>6523503</v>
+        <v>212017</v>
       </c>
     </row>
     <row r="61">
@@ -3264,22 +2880,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK</t>
+          <t>MAHKAMAH AGUNG</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3299,10 +2915,10 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>18000000</v>
+        <v>16000000</v>
       </c>
       <c r="K61" t="n">
-        <v>905070</v>
+        <v>1362070</v>
       </c>
     </row>
     <row r="62">
@@ -3311,22 +2927,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK</t>
+          <t>MAHKAMAH AGUNG</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3346,10 +2962,10 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>18000000</v>
+        <v>16000000</v>
       </c>
       <c r="K62" t="n">
-        <v>3822990</v>
+        <v>2800570</v>
       </c>
     </row>
     <row r="63">
@@ -3358,22 +2974,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK</t>
+          <t>MAHKAMAH AGUNG</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3393,10 +3009,10 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>18000000</v>
+        <v>16000000</v>
       </c>
       <c r="K63" t="n">
-        <v>1290545</v>
+        <v>4221853</v>
       </c>
     </row>
     <row r="64">
@@ -3405,22 +3021,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK</t>
+          <t>MAHKAMAH AGUNG</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3440,10 +3056,10 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>18000000</v>
+        <v>16000000</v>
       </c>
       <c r="K64" t="n">
-        <v>1517640</v>
+        <v>4371470</v>
       </c>
     </row>
     <row r="65">
@@ -3452,22 +3068,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK</t>
+          <t>MAHKAMAH AGUNG</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3487,10 +3103,10 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>18000000</v>
+        <v>10000000</v>
       </c>
       <c r="K65" t="n">
-        <v>8875815</v>
+        <v>1933320</v>
       </c>
     </row>
     <row r="66">
@@ -3499,22 +3115,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK</t>
+          <t>MAHKAMAH AGUNG</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3534,10 +3150,10 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>18000000</v>
+        <v>16000000</v>
       </c>
       <c r="K66" t="n">
-        <v>15951110</v>
+        <v>5285170</v>
       </c>
     </row>
     <row r="67">
@@ -3546,22 +3162,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK</t>
+          <t>MAHKAMAH AGUNG</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3581,10 +3197,10 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>18000000</v>
+        <v>16000000</v>
       </c>
       <c r="K67" t="n">
-        <v>17150045</v>
+        <v>7754710</v>
       </c>
     </row>
     <row r="68">
@@ -3593,22 +3209,22 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK</t>
+          <t>MAHKAMAH AGUNG</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3628,10 +3244,10 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>18000000</v>
+        <v>16000000</v>
       </c>
       <c r="K68" t="n">
-        <v>17095326</v>
+        <v>10124059</v>
       </c>
     </row>
     <row r="69">
@@ -3640,22 +3256,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK</t>
+          <t>MAHKAMAH AGUNG</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3675,10 +3291,10 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>18000000</v>
+        <v>10000000</v>
       </c>
       <c r="K69" t="n">
-        <v>1074070</v>
+        <v>3348270</v>
       </c>
     </row>
     <row r="70">
@@ -3687,34 +3303,34 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK</t>
+          <t>MAHKAMAH AGUNG</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="G70" t="n">
         <v>2025</v>
       </c>
       <c r="H70" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3722,10 +3338,10 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>11000000</v>
+        <v>10000000</v>
       </c>
       <c r="K70" t="n">
-        <v>2868489</v>
+        <v>1168200</v>
       </c>
     </row>
     <row r="71">
@@ -3734,34 +3350,34 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK</t>
+          <t>MAHKAMAH AGUNG</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G71" t="n">
         <v>2025</v>
       </c>
       <c r="H71" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3769,10 +3385,10 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>5000000</v>
+        <v>10000000</v>
       </c>
       <c r="K71" t="n">
-        <v>2115768</v>
+        <v>9026788</v>
       </c>
     </row>
     <row r="72">
@@ -3781,34 +3397,34 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK</t>
+          <t>MAHKAMAH AGUNG</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="G72" t="n">
         <v>2025</v>
       </c>
       <c r="H72" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -3816,10 +3432,10 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>5000000</v>
+        <v>10000000</v>
       </c>
       <c r="K72" t="n">
-        <v>2111897</v>
+        <v>1068054</v>
       </c>
     </row>
     <row r="73">
@@ -3828,34 +3444,34 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK</t>
+          <t>MAHKAMAH AGUNG</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="G73" t="n">
         <v>2025</v>
       </c>
       <c r="H73" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -3863,10 +3479,10 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>11000000</v>
+        <v>10000000</v>
       </c>
       <c r="K73" t="n">
-        <v>4914266</v>
+        <v>7992275</v>
       </c>
     </row>
     <row r="74">
@@ -3875,34 +3491,34 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK</t>
+          <t>MAHKAMAH AGUNG</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="G74" t="n">
         <v>2025</v>
       </c>
       <c r="H74" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -3910,10 +3526,10 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>5000000</v>
+        <v>10000000</v>
       </c>
       <c r="K74" t="n">
-        <v>3017400</v>
+        <v>8596433</v>
       </c>
     </row>
     <row r="75">
@@ -3922,34 +3538,34 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK</t>
+          <t>MAHKAMAH AGUNG</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="G75" t="n">
         <v>2025</v>
       </c>
       <c r="H75" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -3957,10 +3573,10 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>5000000</v>
+        <v>10000000</v>
       </c>
       <c r="K75" t="n">
-        <v>5939307</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="76">
@@ -3969,34 +3585,34 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK</t>
+          <t>MAHKAMAH AGUNG</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="G76" t="n">
         <v>2025</v>
       </c>
       <c r="H76" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -4004,10 +3620,10 @@
         </is>
       </c>
       <c r="J76" t="n">
-        <v>5000000</v>
+        <v>10000000</v>
       </c>
       <c r="K76" t="n">
-        <v>3240885</v>
+        <v>14785443</v>
       </c>
     </row>
     <row r="77">
@@ -4016,34 +3632,34 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK</t>
+          <t>MAHKAMAH AGUNG</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="G77" t="n">
         <v>2025</v>
       </c>
       <c r="H77" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -4051,10 +3667,10 @@
         </is>
       </c>
       <c r="J77" t="n">
-        <v>11000000</v>
+        <v>10000000</v>
       </c>
       <c r="K77" t="n">
-        <v>10681290</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="78">
@@ -4063,22 +3679,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>006</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK</t>
+          <t>KEJAKSAAN REPUBLIK INDONESIA</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>007130</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4098,10 +3714,10 @@
         </is>
       </c>
       <c r="J78" t="n">
-        <v>11000000</v>
+        <v>6000000</v>
       </c>
       <c r="K78" t="n">
-        <v>4634266</v>
+        <v>770670</v>
       </c>
     </row>
     <row r="79">
@@ -4110,22 +3726,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>006</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK</t>
+          <t>KEJAKSAAN REPUBLIK INDONESIA</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>007130</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4145,10 +3761,10 @@
         </is>
       </c>
       <c r="J79" t="n">
-        <v>11000000</v>
+        <v>6000000</v>
       </c>
       <c r="K79" t="n">
-        <v>7207769</v>
+        <v>160005</v>
       </c>
     </row>
     <row r="80">
@@ -4157,22 +3773,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>006</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK</t>
+          <t>KEJAKSAAN REPUBLIK INDONESIA</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>007130</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4192,10 +3808,10 @@
         </is>
       </c>
       <c r="J80" t="n">
-        <v>5000000</v>
+        <v>6000000</v>
       </c>
       <c r="K80" t="n">
-        <v>5716521</v>
+        <v>1160190</v>
       </c>
     </row>
     <row r="81">
@@ -4204,34 +3820,34 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>006</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK</t>
+          <t>KEJAKSAAN REPUBLIK INDONESIA</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="G81" t="n">
         <v>2025</v>
       </c>
       <c r="H81" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4239,10 +3855,10 @@
         </is>
       </c>
       <c r="J81" t="n">
-        <v>24000000</v>
+        <v>40000000</v>
       </c>
       <c r="K81" t="n">
-        <v>14859000</v>
+        <v>9180565</v>
       </c>
     </row>
     <row r="82">
@@ -4251,34 +3867,34 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>006</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK</t>
+          <t>KEJAKSAAN REPUBLIK INDONESIA</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="G82" t="n">
         <v>2025</v>
       </c>
       <c r="H82" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4286,10 +3902,10 @@
         </is>
       </c>
       <c r="J82" t="n">
-        <v>14000000</v>
+        <v>40000000</v>
       </c>
       <c r="K82" t="n">
-        <v>1392000</v>
+        <v>8752087</v>
       </c>
     </row>
     <row r="83">
@@ -4298,34 +3914,34 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>006</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK</t>
+          <t>KEJAKSAAN REPUBLIK INDONESIA</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="G83" t="n">
         <v>2025</v>
       </c>
       <c r="H83" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -4333,10 +3949,10 @@
         </is>
       </c>
       <c r="J83" t="n">
-        <v>14000000</v>
+        <v>40000000</v>
       </c>
       <c r="K83" t="n">
-        <v>1722276</v>
+        <v>16690098</v>
       </c>
     </row>
     <row r="84">
@@ -4345,34 +3961,34 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>006</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK</t>
+          <t>KEJAKSAAN REPUBLIK INDONESIA</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="G84" t="n">
         <v>2025</v>
       </c>
       <c r="H84" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -4380,10 +3996,10 @@
         </is>
       </c>
       <c r="J84" t="n">
-        <v>14000000</v>
+        <v>40000000</v>
       </c>
       <c r="K84" t="n">
-        <v>689000</v>
+        <v>26763409</v>
       </c>
     </row>
     <row r="85">
@@ -4392,34 +4008,34 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>066</t>
+          <t>006</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL (BNN)</t>
+          <t>KEJAKSAAN REPUBLIK INDONESIA</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="G85" t="n">
         <v>2025</v>
       </c>
       <c r="H85" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4430,7 +4046,7 @@
         <v>40000000</v>
       </c>
       <c r="K85" t="n">
-        <v>4043518</v>
+        <v>22446603</v>
       </c>
     </row>
     <row r="86">
@@ -4439,34 +4055,34 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>066</t>
+          <t>012</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL (BNN)</t>
+          <t>KEMENTERIAN PERTAHANAN</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>685001</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>PUSLATPUR KODIKLATAD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="G86" t="n">
         <v>2025</v>
       </c>
       <c r="H86" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -4474,10 +4090,10 @@
         </is>
       </c>
       <c r="J86" t="n">
-        <v>40000000</v>
+        <v>3000000</v>
       </c>
       <c r="K86" t="n">
-        <v>37740000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="87">
@@ -4486,22 +4102,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>066</t>
+          <t>015</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL (BNN)</t>
+          <t>KEMENTERIAN KEUANGAN</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4524,7 +4140,7 @@
         <v>40000000</v>
       </c>
       <c r="K87" t="n">
-        <v>12365000</v>
+        <v>19651577</v>
       </c>
     </row>
     <row r="88">
@@ -4533,34 +4149,34 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>066</t>
+          <t>015</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL (BNN)</t>
+          <t>KEMENTERIAN KEUANGAN</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="G88" t="n">
         <v>2025</v>
       </c>
       <c r="H88" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -4571,7 +4187,7 @@
         <v>40000000</v>
       </c>
       <c r="K88" t="n">
-        <v>9286864</v>
+        <v>9670989</v>
       </c>
     </row>
     <row r="89">
@@ -4580,34 +4196,34 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>015</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>KOMISI PEMILIHAN UMUM</t>
+          <t>KEMENTERIAN KEUANGAN</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>656553</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="G89" t="n">
         <v>2025</v>
       </c>
       <c r="H89" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4615,10 +4231,10 @@
         </is>
       </c>
       <c r="J89" t="n">
-        <v>50000000</v>
+        <v>40000000</v>
       </c>
       <c r="K89" t="n">
-        <v>775000</v>
+        <v>6743111</v>
       </c>
     </row>
     <row r="90">
@@ -4627,34 +4243,34 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>015</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>KOMISI PEMILIHAN UMUM</t>
+          <t>KEMENTERIAN KEUANGAN</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="G90" t="n">
         <v>2025</v>
       </c>
       <c r="H90" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4662,10 +4278,10 @@
         </is>
       </c>
       <c r="J90" t="n">
-        <v>16000000</v>
+        <v>40000000</v>
       </c>
       <c r="K90" t="n">
-        <v>2289406</v>
+        <v>9978760</v>
       </c>
     </row>
     <row r="91">
@@ -4674,34 +4290,34 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>015</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>KOMISI PEMILIHAN UMUM</t>
+          <t>KEMENTERIAN KEUANGAN</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="G91" t="n">
         <v>2025</v>
       </c>
       <c r="H91" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -4709,10 +4325,10 @@
         </is>
       </c>
       <c r="J91" t="n">
-        <v>16000000</v>
+        <v>40000000</v>
       </c>
       <c r="K91" t="n">
-        <v>3668591</v>
+        <v>22314667</v>
       </c>
     </row>
     <row r="92">
@@ -4721,34 +4337,34 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>015</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>KOMISI PEMILIHAN UMUM</t>
+          <t>KEMENTERIAN KEUANGAN</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="G92" t="n">
         <v>2025</v>
       </c>
       <c r="H92" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -4756,10 +4372,10 @@
         </is>
       </c>
       <c r="J92" t="n">
-        <v>16000000</v>
+        <v>40000000</v>
       </c>
       <c r="K92" t="n">
-        <v>2283305</v>
+        <v>8400111</v>
       </c>
     </row>
     <row r="93">
@@ -4768,34 +4384,34 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>015</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>KOMISI PEMILIHAN UMUM</t>
+          <t>KEMENTERIAN KEUANGAN</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="G93" t="n">
         <v>2025</v>
       </c>
       <c r="H93" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -4803,10 +4419,10 @@
         </is>
       </c>
       <c r="J93" t="n">
-        <v>32000000</v>
+        <v>70000000</v>
       </c>
       <c r="K93" t="n">
-        <v>7554670</v>
+        <v>1489998</v>
       </c>
     </row>
     <row r="94">
@@ -4815,34 +4431,34 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>015</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>KOMISI PEMILIHAN UMUM</t>
+          <t>KEMENTERIAN KEUANGAN</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="G94" t="n">
         <v>2025</v>
       </c>
       <c r="H94" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -4850,10 +4466,10 @@
         </is>
       </c>
       <c r="J94" t="n">
-        <v>32000000</v>
+        <v>10000000</v>
       </c>
       <c r="K94" t="n">
-        <v>2727445</v>
+        <v>3211146</v>
       </c>
     </row>
     <row r="95">
@@ -4862,34 +4478,34 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>015</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>KOMISI PEMILIHAN UMUM</t>
+          <t>KEMENTERIAN KEUANGAN</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="G95" t="n">
         <v>2025</v>
       </c>
       <c r="H95" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -4897,10 +4513,10 @@
         </is>
       </c>
       <c r="J95" t="n">
-        <v>16000000</v>
+        <v>10000000</v>
       </c>
       <c r="K95" t="n">
-        <v>7326664</v>
+        <v>5902139</v>
       </c>
     </row>
     <row r="96">
@@ -4909,34 +4525,34 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>015</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>KOMISI PEMILIHAN UMUM</t>
+          <t>KEMENTERIAN KEUANGAN</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="G96" t="n">
         <v>2025</v>
       </c>
       <c r="H96" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -4944,10 +4560,10 @@
         </is>
       </c>
       <c r="J96" t="n">
-        <v>16000000</v>
+        <v>10000000</v>
       </c>
       <c r="K96" t="n">
-        <v>3185388</v>
+        <v>6077473</v>
       </c>
     </row>
     <row r="97">
@@ -4956,34 +4572,34 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>015</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>KOMISI PEMILIHAN UMUM</t>
+          <t>KEMENTERIAN KEUANGAN</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="G97" t="n">
         <v>2025</v>
       </c>
       <c r="H97" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -4991,10 +4607,10 @@
         </is>
       </c>
       <c r="J97" t="n">
-        <v>16000000</v>
+        <v>10000000</v>
       </c>
       <c r="K97" t="n">
-        <v>4151070</v>
+        <v>7744485</v>
       </c>
     </row>
     <row r="98">
@@ -5003,34 +4619,34 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>015</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>KOMISI PEMILIHAN UMUM</t>
+          <t>KEMENTERIAN KEUANGAN</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="G98" t="n">
         <v>2025</v>
       </c>
       <c r="H98" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -5038,10 +4654,10 @@
         </is>
       </c>
       <c r="J98" t="n">
-        <v>1900000</v>
+        <v>10000000</v>
       </c>
       <c r="K98" t="n">
-        <v>1904397</v>
+        <v>2241786</v>
       </c>
     </row>
     <row r="99">
@@ -5050,34 +4666,34 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>015</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>KOMISI PEMILIHAN UMUM</t>
+          <t>KEMENTERIAN KEUANGAN</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="G99" t="n">
         <v>2025</v>
       </c>
       <c r="H99" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -5085,10 +4701,10 @@
         </is>
       </c>
       <c r="J99" t="n">
-        <v>1900000</v>
+        <v>16000000</v>
       </c>
       <c r="K99" t="n">
-        <v>640133</v>
+        <v>3889590</v>
       </c>
     </row>
     <row r="100">
@@ -5097,34 +4713,34 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>015</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>KOMISI PEMILIHAN UMUM</t>
+          <t>KEMENTERIAN KEUANGAN</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="G100" t="n">
         <v>2025</v>
       </c>
       <c r="H100" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -5132,10 +4748,10 @@
         </is>
       </c>
       <c r="J100" t="n">
-        <v>1900000</v>
+        <v>16000000</v>
       </c>
       <c r="K100" t="n">
-        <v>1720000</v>
+        <v>68700000</v>
       </c>
     </row>
     <row r="101">
@@ -5144,34 +4760,34 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>015</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>KOMISI PEMILIHAN UMUM</t>
+          <t>KEMENTERIAN KEUANGAN</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="G101" t="n">
         <v>2025</v>
       </c>
       <c r="H101" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -5179,10 +4795,10 @@
         </is>
       </c>
       <c r="J101" t="n">
-        <v>1900000</v>
+        <v>16000000</v>
       </c>
       <c r="K101" t="n">
-        <v>128530</v>
+        <v>33307620</v>
       </c>
     </row>
     <row r="102">
@@ -5191,34 +4807,34 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>015</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>KOMISI PEMILIHAN UMUM</t>
+          <t>KEMENTERIAN KEUANGAN</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="G102" t="n">
         <v>2025</v>
       </c>
       <c r="H102" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -5226,10 +4842,10 @@
         </is>
       </c>
       <c r="J102" t="n">
-        <v>1900000</v>
+        <v>6000000</v>
       </c>
       <c r="K102" t="n">
-        <v>401000</v>
+        <v>259000</v>
       </c>
     </row>
     <row r="103">
@@ -5238,34 +4854,34 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>024</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>KEMENTERIAN IMIGRASI DAN PEMASYARAKATAN</t>
+          <t>KEMENTERIAN KESEHATAN</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>690801</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA</t>
+          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="G103" t="n">
         <v>2025</v>
       </c>
       <c r="H103" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -5273,10 +4889,10 @@
         </is>
       </c>
       <c r="J103" t="n">
-        <v>40000000</v>
+        <v>22000000</v>
       </c>
       <c r="K103" t="n">
-        <v>1082700</v>
+        <v>1865319</v>
       </c>
     </row>
     <row r="104">
@@ -5285,34 +4901,34 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>024</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>KEMENTERIAN IMIGRASI DAN PEMASYARAKATAN</t>
+          <t>KEMENTERIAN KESEHATAN</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>690801</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA</t>
+          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="G104" t="n">
         <v>2025</v>
       </c>
       <c r="H104" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -5320,10 +4936,10 @@
         </is>
       </c>
       <c r="J104" t="n">
-        <v>40000000</v>
+        <v>22000000</v>
       </c>
       <c r="K104" t="n">
-        <v>2260122</v>
+        <v>2717905</v>
       </c>
     </row>
     <row r="105">
@@ -5332,22 +4948,22 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>025</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>KEMENTERIAN IMIGRASI DAN PEMASYARAKATAN</t>
+          <t>KEMENTERIAN AGAMA</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>424245</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5367,10 +4983,10 @@
         </is>
       </c>
       <c r="J105" t="n">
-        <v>40000000</v>
+        <v>10000000</v>
       </c>
       <c r="K105" t="n">
-        <v>2806886</v>
+        <v>568000</v>
       </c>
     </row>
     <row r="106">
@@ -5379,34 +4995,34 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>025</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>KEMENTERIAN IMIGRASI DAN PEMASYARAKATAN</t>
+          <t>KEMENTERIAN AGAMA</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>553099</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="G106" t="n">
         <v>2025</v>
       </c>
       <c r="H106" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -5414,10 +5030,10 @@
         </is>
       </c>
       <c r="J106" t="n">
-        <v>40000000</v>
+        <v>6000000</v>
       </c>
       <c r="K106" t="n">
-        <v>1082700</v>
+        <v>2911500</v>
       </c>
     </row>
     <row r="107">
@@ -5426,34 +5042,34 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>054</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>KEMENTERIAN IMIGRASI DAN PEMASYARAKATAN</t>
+          <t>BADAN PUSAT STATISTIK</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>692339</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RUTAN KELAS II B BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="G107" t="n">
         <v>2025</v>
       </c>
       <c r="H107" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
@@ -5461,10 +5077,10 @@
         </is>
       </c>
       <c r="J107" t="n">
-        <v>6800000</v>
+        <v>28000000</v>
       </c>
       <c r="K107" t="n">
-        <v>1386000</v>
+        <v>19420000</v>
       </c>
     </row>
     <row r="108">
@@ -5473,44 +5089,2300 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H108" t="n">
+        <v>2</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="K108" t="n">
+        <v>6523503</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H109" t="n">
+        <v>3</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="K109" t="n">
+        <v>905070</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H110" t="n">
+        <v>4</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="K110" t="n">
+        <v>3822990</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H111" t="n">
+        <v>5</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="K111" t="n">
+        <v>1290545</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H112" t="n">
+        <v>6</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="K112" t="n">
+        <v>1517640</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H113" t="n">
+        <v>7</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="K113" t="n">
+        <v>8875815</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H114" t="n">
+        <v>8</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="K114" t="n">
+        <v>15951110</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H115" t="n">
+        <v>9</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="K115" t="n">
+        <v>17150045</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H116" t="n">
+        <v>10</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="K116" t="n">
+        <v>17095326</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H117" t="n">
+        <v>11</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="K117" t="n">
+        <v>1074070</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H118" t="n">
+        <v>2</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J118" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="K118" t="n">
+        <v>2868489</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H119" t="n">
+        <v>3</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="K119" t="n">
+        <v>2115768</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H120" t="n">
+        <v>4</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="K120" t="n">
+        <v>2111897</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H121" t="n">
+        <v>5</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="K121" t="n">
+        <v>4914266</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H122" t="n">
+        <v>6</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J122" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="K122" t="n">
+        <v>3017400</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H123" t="n">
+        <v>7</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J123" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="K123" t="n">
+        <v>5939307</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H124" t="n">
+        <v>8</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J124" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="K124" t="n">
+        <v>3240885</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H125" t="n">
+        <v>9</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J125" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="K125" t="n">
+        <v>10681290</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H126" t="n">
+        <v>10</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="K126" t="n">
+        <v>4634266</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H127" t="n">
+        <v>11</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J127" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="K127" t="n">
+        <v>7207769</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H128" t="n">
+        <v>12</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J128" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="K128" t="n">
+        <v>5716521</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>668529</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H129" t="n">
+        <v>7</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J129" t="n">
+        <v>24000000</v>
+      </c>
+      <c r="K129" t="n">
+        <v>14859000</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>668529</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H130" t="n">
+        <v>8</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J130" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="K130" t="n">
+        <v>1392000</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>668529</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H131" t="n">
+        <v>9</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J131" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="K131" t="n">
+        <v>1722276</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>668529</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H132" t="n">
+        <v>10</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J132" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="K132" t="n">
+        <v>689000</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>066</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>BADAN NARKOTIKA NASIONAL (BNN)</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>111079</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H133" t="n">
+        <v>2</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J133" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="K133" t="n">
+        <v>4043518</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>066</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>BADAN NARKOTIKA NASIONAL (BNN)</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>111079</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H134" t="n">
+        <v>6</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J134" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="K134" t="n">
+        <v>37740000</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>066</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>BADAN NARKOTIKA NASIONAL (BNN)</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>111079</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H135" t="n">
+        <v>7</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J135" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="K135" t="n">
+        <v>12365000</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>066</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>BADAN NARKOTIKA NASIONAL (BNN)</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>111079</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H136" t="n">
+        <v>10</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J136" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="K136" t="n">
+        <v>9286864</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>076</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>KOMISI PEMILIHAN UMUM</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>656553</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H137" t="n">
+        <v>10</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J137" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="K137" t="n">
+        <v>775000</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>076</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>KOMISI PEMILIHAN UMUM</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>656560</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H138" t="n">
+        <v>2</v>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J138" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="K138" t="n">
+        <v>2289406</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>076</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>KOMISI PEMILIHAN UMUM</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>656560</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H139" t="n">
+        <v>4</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J139" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="K139" t="n">
+        <v>3668591</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>076</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>KOMISI PEMILIHAN UMUM</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>656560</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H140" t="n">
+        <v>6</v>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J140" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="K140" t="n">
+        <v>2283305</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>076</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>KOMISI PEMILIHAN UMUM</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>656560</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H141" t="n">
+        <v>8</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J141" t="n">
+        <v>32000000</v>
+      </c>
+      <c r="K141" t="n">
+        <v>7554670</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>076</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>KOMISI PEMILIHAN UMUM</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>656560</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H142" t="n">
+        <v>9</v>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J142" t="n">
+        <v>32000000</v>
+      </c>
+      <c r="K142" t="n">
+        <v>2727445</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>076</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>KOMISI PEMILIHAN UMUM</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>656560</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H143" t="n">
+        <v>10</v>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J143" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="K143" t="n">
+        <v>7326664</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>076</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>KOMISI PEMILIHAN UMUM</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>656560</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H144" t="n">
+        <v>11</v>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J144" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="K144" t="n">
+        <v>3185388</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>076</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>KOMISI PEMILIHAN UMUM</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>656560</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H145" t="n">
+        <v>12</v>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J145" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="K145" t="n">
+        <v>4151070</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>076</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>KOMISI PEMILIHAN UMUM</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>656574</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H146" t="n">
+        <v>2</v>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J146" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="K146" t="n">
+        <v>1904397</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>076</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>KOMISI PEMILIHAN UMUM</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>656574</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H147" t="n">
+        <v>3</v>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J147" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="K147" t="n">
+        <v>640133</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>076</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>KOMISI PEMILIHAN UMUM</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>656574</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H148" t="n">
+        <v>5</v>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J148" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="K148" t="n">
+        <v>1720000</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>076</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>KOMISI PEMILIHAN UMUM</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>656574</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H149" t="n">
+        <v>10</v>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J149" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="K149" t="n">
+        <v>128530</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>076</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>KOMISI PEMILIHAN UMUM</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>656574</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H150" t="n">
+        <v>11</v>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J150" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="K150" t="n">
+        <v>401000</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
           <t>137</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C151" t="inlineStr">
         <is>
           <t>KEMENTERIAN IMIGRASI DAN PEMASYARAKATAN</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>692334</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>LAPAS KELAS II B MUARA DUA</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H151" t="n">
+        <v>8</v>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J151" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="K151" t="n">
+        <v>1082700</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>KEMENTERIAN IMIGRASI DAN PEMASYARAKATAN</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>692334</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>LAPAS KELAS II B MUARA DUA</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H152" t="n">
+        <v>9</v>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J152" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="K152" t="n">
+        <v>2260122</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>KEMENTERIAN IMIGRASI DAN PEMASYARAKATAN</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>692334</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>LAPAS KELAS II B MUARA DUA</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H153" t="n">
+        <v>10</v>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J153" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="K153" t="n">
+        <v>2806886</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>KEMENTERIAN IMIGRASI DAN PEMASYARAKATAN</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>692334</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>LAPAS KELAS II B MUARA DUA</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H154" t="n">
+        <v>12</v>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J154" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="K154" t="n">
+        <v>1082700</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>KEMENTERIAN IMIGRASI DAN PEMASYARAKATAN</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
         <is>
           <t>692339</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
+      <c r="E155" t="inlineStr">
         <is>
           <t>RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H155" t="n">
+        <v>11</v>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J155" t="n">
+        <v>6800000</v>
+      </c>
+      <c r="K155" t="n">
+        <v>1386000</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>KEMENTERIAN IMIGRASI DAN PEMASYARAKATAN</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>692339</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>RUTAN KELAS II B BATURAJA</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
         <is>
           <t>2025-12</t>
         </is>
       </c>
-      <c r="G108" t="n">
-        <v>2025</v>
-      </c>
-      <c r="H108" t="n">
+      <c r="G156" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H156" t="n">
         <v>12</v>
       </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>LAMA</t>
-        </is>
-      </c>
-      <c r="J108" t="n">
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="J156" t="n">
         <v>6800000</v>
       </c>
-      <c r="K108" t="n">
+      <c r="K156" t="n">
         <v>3465000</v>
       </c>
     </row>

--- a/data_kkp/KKP_MASTER.xlsx
+++ b/data_kkp/KKP_MASTER.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J108"/>
+  <dimension ref="A1:J156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,137 +484,121 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>007130</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>24000000</v>
+        <v>8000000</v>
       </c>
       <c r="J2" t="n">
-        <v>11321000</v>
+        <v>145429</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>007130</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>24000000</v>
+        <v>8000000</v>
       </c>
       <c r="J3" t="n">
-        <v>17922000</v>
+        <v>198180</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>24000000</v>
       </c>
       <c r="J4" t="n">
-        <v>2650000</v>
+        <v>19336463</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>098963</t>
@@ -627,36 +611,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>24000000</v>
+        <v>43200000</v>
       </c>
       <c r="J5" t="n">
-        <v>3905000</v>
+        <v>10861535</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>098963</t>
@@ -669,204 +649,184 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>24000000</v>
+        <v>43200000</v>
       </c>
       <c r="J6" t="n">
-        <v>3500000</v>
+        <v>3980879</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>24000000</v>
       </c>
       <c r="J7" t="n">
-        <v>13874500</v>
+        <v>11031747</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G8" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>24000000</v>
+        <v>12000000</v>
       </c>
       <c r="J8" t="n">
-        <v>3897000</v>
+        <v>2695000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>24000000</v>
       </c>
       <c r="J9" t="n">
-        <v>13995500</v>
+        <v>5926136</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G10" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>24000000</v>
       </c>
       <c r="J10" t="n">
-        <v>9151500</v>
+        <v>5142960</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>401944</t>
@@ -879,36 +839,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>16000000</v>
+        <v>40000000</v>
       </c>
       <c r="J11" t="n">
-        <v>3618000</v>
+        <v>7850987</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>401944</t>
@@ -921,1579 +877,1431 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>10000000</v>
+        <v>32000000</v>
       </c>
       <c r="J12" t="n">
-        <v>212017</v>
+        <v>5025020</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>16000000</v>
+        <v>72000000</v>
       </c>
       <c r="J13" t="n">
-        <v>1362070</v>
+        <v>9817209</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>16000000</v>
+        <v>56000000</v>
       </c>
       <c r="J14" t="n">
-        <v>2800570</v>
+        <v>14099104</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>16000000</v>
+        <v>48000000</v>
       </c>
       <c r="J15" t="n">
-        <v>4221853</v>
+        <v>10919258</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>16000000</v>
+        <v>24000000</v>
       </c>
       <c r="J16" t="n">
-        <v>4371470</v>
+        <v>7257331</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G17" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>10000000</v>
+        <v>40000000</v>
       </c>
       <c r="J17" t="n">
-        <v>1933320</v>
+        <v>12334663</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G18" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>16000000</v>
+        <v>120000000</v>
       </c>
       <c r="J18" t="n">
-        <v>5285170</v>
+        <v>8053774</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G19" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>16000000</v>
+        <v>40000000</v>
       </c>
       <c r="J19" t="n">
-        <v>7754710</v>
+        <v>4849486</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>424245</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G20" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>16000000</v>
+        <v>17600000</v>
       </c>
       <c r="J20" t="n">
-        <v>10124059</v>
+        <v>3273950</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>424245</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G21" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>10000000</v>
+        <v>8800000</v>
       </c>
       <c r="J21" t="n">
-        <v>3348270</v>
+        <v>2223600</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>424245</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>10000000</v>
+        <v>8800000</v>
       </c>
       <c r="J22" t="n">
-        <v>1168200</v>
+        <v>1067000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G23" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>10000000</v>
+        <v>40000000</v>
       </c>
       <c r="J23" t="n">
-        <v>9026788</v>
+        <v>5055500</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>23</v>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G24" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>10000000</v>
+        <v>100000000</v>
       </c>
       <c r="J24" t="n">
-        <v>1068054</v>
+        <v>12720428</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>10000000</v>
+        <v>120000000</v>
       </c>
       <c r="J25" t="n">
-        <v>7992275</v>
+        <v>6387960</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>25</v>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>641681</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>POLRES OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G26" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>10000000</v>
+        <v>360000000</v>
       </c>
       <c r="J26" t="n">
-        <v>8596433</v>
+        <v>61610000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>26</v>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>641681</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>POLRES OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G27" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>10000000</v>
+        <v>360000000</v>
       </c>
       <c r="J27" t="n">
-        <v>10000</v>
+        <v>54210000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>27</v>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>656553</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G28" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>10000000</v>
+        <v>2000000</v>
       </c>
       <c r="J28" t="n">
-        <v>14785443</v>
+        <v>1721500</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>28</v>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>005</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>656553</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G29" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>10000000</v>
+        <v>6000000</v>
       </c>
       <c r="J29" t="n">
-        <v>10000</v>
+        <v>5455000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>29</v>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>006</t>
-        </is>
-      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>007130</t>
+          <t>656553</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G30" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>6000000</v>
+        <v>2000000</v>
       </c>
       <c r="J30" t="n">
-        <v>770670</v>
+        <v>1995000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>30</v>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>006</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>007130</t>
+          <t>656553</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G31" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>6000000</v>
+        <v>2000000</v>
       </c>
       <c r="J31" t="n">
-        <v>160005</v>
+        <v>1990000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>31</v>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>006</t>
-        </is>
-      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>007130</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G32" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>6000000</v>
+        <v>30000000</v>
       </c>
       <c r="J32" t="n">
-        <v>1160190</v>
+        <v>6034789</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>32</v>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>006</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>40000000</v>
+        <v>20000000</v>
       </c>
       <c r="J33" t="n">
-        <v>9180565</v>
+        <v>2679300</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
         <v>33</v>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>006</t>
-        </is>
-      </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>656574</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>40000000</v>
+        <v>4000000</v>
       </c>
       <c r="J34" t="n">
-        <v>8752087</v>
+        <v>1216870</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>34</v>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>006</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>656574</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>40000000</v>
+        <v>4000000</v>
       </c>
       <c r="J35" t="n">
-        <v>16690098</v>
+        <v>350550</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
         <v>35</v>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>006</t>
-        </is>
-      </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>665292</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>POLRES OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G36" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>40000000</v>
+        <v>80000000</v>
       </c>
       <c r="J36" t="n">
-        <v>26763409</v>
+        <v>16512000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
         <v>36</v>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>006</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>665292</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>POLRES OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G37" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>40000000</v>
+        <v>80000000</v>
       </c>
       <c r="J37" t="n">
-        <v>22446603</v>
+        <v>16512000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
         <v>37</v>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>012</t>
-        </is>
-      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>685001</t>
+          <t>665307</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>PUSLATPUR KODIKLATAD</t>
+          <t>POLRES OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G38" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3000000</v>
+        <v>120000000</v>
       </c>
       <c r="J38" t="n">
-        <v>1500000</v>
+        <v>59780000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
         <v>38</v>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>015</t>
-        </is>
-      </c>
+      <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>665307</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>POLRES OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G39" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>40000000</v>
+        <v>120000000</v>
       </c>
       <c r="J39" t="n">
-        <v>19651577</v>
+        <v>24770827</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
         <v>39</v>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>015</t>
-        </is>
-      </c>
+      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>665307</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>POLRES OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G40" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>40000000</v>
+        <v>240000000</v>
       </c>
       <c r="J40" t="n">
-        <v>9670989</v>
+        <v>37398067</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
         <v>40</v>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>015</t>
-        </is>
-      </c>
+      <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G41" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>40000000</v>
+        <v>36000000</v>
       </c>
       <c r="J41" t="n">
-        <v>6743111</v>
+        <v>8638865</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
         <v>41</v>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>015</t>
-        </is>
-      </c>
+      <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>667215</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G42" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>40000000</v>
+        <v>30000000</v>
       </c>
       <c r="J42" t="n">
-        <v>9978760</v>
+        <v>13630532</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
         <v>42</v>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>015</t>
-        </is>
-      </c>
+      <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>685001</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>PUSLATPUR KODIKLATAD</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G43" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>40000000</v>
+        <v>2400000</v>
       </c>
       <c r="J43" t="n">
-        <v>22314667</v>
+        <v>2400000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
         <v>43</v>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>015</t>
-        </is>
-      </c>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>685001</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>PUSLATPUR KODIKLATAD</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G44" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>40000000</v>
+        <v>7200000</v>
       </c>
       <c r="J44" t="n">
-        <v>8400111</v>
+        <v>2850000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
         <v>44</v>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>015</t>
-        </is>
-      </c>
+      <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>692339</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G45" t="n">
         <v>2</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>70000000</v>
+        <v>40000000</v>
       </c>
       <c r="J45" t="n">
-        <v>1489998</v>
+        <v>30090000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>45</v>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>015</t>
-        </is>
-      </c>
+      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>692339</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>10000000</v>
+        <v>40000000</v>
       </c>
       <c r="J46" t="n">
-        <v>3211146</v>
+        <v>16654072</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
         <v>46</v>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>015</t>
-        </is>
-      </c>
+      <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>692339</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G47" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>10000000</v>
+        <v>40000000</v>
       </c>
       <c r="J47" t="n">
-        <v>5902139</v>
+        <v>12828042</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
         <v>47</v>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>015</t>
-        </is>
-      </c>
+      <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>692625</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>BAPAS KELAS II OKU INDUK</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G48" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>10000000</v>
+        <v>6000000</v>
       </c>
       <c r="J48" t="n">
-        <v>6077473</v>
+        <v>2550000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
         <v>48</v>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>015</t>
-        </is>
-      </c>
+      <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>692625</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>BAPAS KELAS II OKU INDUK</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G49" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>10000000</v>
+        <v>6000000</v>
       </c>
       <c r="J49" t="n">
-        <v>7744485</v>
+        <v>2500000</v>
       </c>
     </row>
     <row r="50">
@@ -2502,29 +2310,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="F50" t="n">
         <v>2025</v>
       </c>
       <c r="G50" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2532,10 +2340,10 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>10000000</v>
+        <v>24000000</v>
       </c>
       <c r="J50" t="n">
-        <v>2241786</v>
+        <v>11321000</v>
       </c>
     </row>
     <row r="51">
@@ -2544,29 +2352,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="F51" t="n">
         <v>2025</v>
       </c>
       <c r="G51" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2574,10 +2382,10 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>16000000</v>
+        <v>24000000</v>
       </c>
       <c r="J51" t="n">
-        <v>3889590</v>
+        <v>17922000</v>
       </c>
     </row>
     <row r="52">
@@ -2586,29 +2394,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="F52" t="n">
         <v>2025</v>
       </c>
       <c r="G52" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2616,10 +2424,10 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>16000000</v>
+        <v>24000000</v>
       </c>
       <c r="J52" t="n">
-        <v>68700000</v>
+        <v>2650000</v>
       </c>
     </row>
     <row r="53">
@@ -2628,29 +2436,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="F53" t="n">
         <v>2025</v>
       </c>
       <c r="G53" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2658,10 +2466,10 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>16000000</v>
+        <v>24000000</v>
       </c>
       <c r="J53" t="n">
-        <v>33307620</v>
+        <v>3905000</v>
       </c>
     </row>
     <row r="54">
@@ -2670,29 +2478,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>015</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="F54" t="n">
         <v>2025</v>
       </c>
       <c r="G54" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -2700,10 +2508,10 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>6000000</v>
+        <v>24000000</v>
       </c>
       <c r="J54" t="n">
-        <v>259000</v>
+        <v>3500000</v>
       </c>
     </row>
     <row r="55">
@@ -2712,29 +2520,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>024</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>690801</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="F55" t="n">
         <v>2025</v>
       </c>
       <c r="G55" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -2742,10 +2550,10 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>22000000</v>
+        <v>24000000</v>
       </c>
       <c r="J55" t="n">
-        <v>1865319</v>
+        <v>13874500</v>
       </c>
     </row>
     <row r="56">
@@ -2754,29 +2562,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>024</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>690801</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="F56" t="n">
         <v>2025</v>
       </c>
       <c r="G56" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2784,10 +2592,10 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>22000000</v>
+        <v>24000000</v>
       </c>
       <c r="J56" t="n">
-        <v>2717905</v>
+        <v>3897000</v>
       </c>
     </row>
     <row r="57">
@@ -2796,17 +2604,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>424245</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2826,10 +2634,10 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>10000000</v>
+        <v>24000000</v>
       </c>
       <c r="J57" t="n">
-        <v>568000</v>
+        <v>13995500</v>
       </c>
     </row>
     <row r="58">
@@ -2838,17 +2646,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>025</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>553099</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2868,10 +2676,10 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>6000000</v>
+        <v>24000000</v>
       </c>
       <c r="J58" t="n">
-        <v>2911500</v>
+        <v>9151500</v>
       </c>
     </row>
     <row r="59">
@@ -2880,17 +2688,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2910,10 +2718,10 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>28000000</v>
+        <v>16000000</v>
       </c>
       <c r="J59" t="n">
-        <v>19420000</v>
+        <v>3618000</v>
       </c>
     </row>
     <row r="60">
@@ -2922,17 +2730,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2952,10 +2760,10 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>18000000</v>
+        <v>10000000</v>
       </c>
       <c r="J60" t="n">
-        <v>6523503</v>
+        <v>212017</v>
       </c>
     </row>
     <row r="61">
@@ -2964,17 +2772,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2994,10 +2802,10 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>18000000</v>
+        <v>16000000</v>
       </c>
       <c r="J61" t="n">
-        <v>905070</v>
+        <v>1362070</v>
       </c>
     </row>
     <row r="62">
@@ -3006,17 +2814,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3036,10 +2844,10 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>18000000</v>
+        <v>16000000</v>
       </c>
       <c r="J62" t="n">
-        <v>3822990</v>
+        <v>2800570</v>
       </c>
     </row>
     <row r="63">
@@ -3048,17 +2856,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3078,10 +2886,10 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>18000000</v>
+        <v>16000000</v>
       </c>
       <c r="J63" t="n">
-        <v>1290545</v>
+        <v>4221853</v>
       </c>
     </row>
     <row r="64">
@@ -3090,17 +2898,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3120,10 +2928,10 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>18000000</v>
+        <v>16000000</v>
       </c>
       <c r="J64" t="n">
-        <v>1517640</v>
+        <v>4371470</v>
       </c>
     </row>
     <row r="65">
@@ -3132,17 +2940,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3162,10 +2970,10 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>18000000</v>
+        <v>10000000</v>
       </c>
       <c r="J65" t="n">
-        <v>8875815</v>
+        <v>1933320</v>
       </c>
     </row>
     <row r="66">
@@ -3174,17 +2982,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3204,10 +3012,10 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>18000000</v>
+        <v>16000000</v>
       </c>
       <c r="J66" t="n">
-        <v>15951110</v>
+        <v>5285170</v>
       </c>
     </row>
     <row r="67">
@@ -3216,17 +3024,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3246,10 +3054,10 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>18000000</v>
+        <v>16000000</v>
       </c>
       <c r="J67" t="n">
-        <v>17150045</v>
+        <v>7754710</v>
       </c>
     </row>
     <row r="68">
@@ -3258,17 +3066,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3288,10 +3096,10 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>18000000</v>
+        <v>16000000</v>
       </c>
       <c r="J68" t="n">
-        <v>17095326</v>
+        <v>10124059</v>
       </c>
     </row>
     <row r="69">
@@ -3300,17 +3108,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3330,10 +3138,10 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>18000000</v>
+        <v>10000000</v>
       </c>
       <c r="J69" t="n">
-        <v>1074070</v>
+        <v>3348270</v>
       </c>
     </row>
     <row r="70">
@@ -3342,29 +3150,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="F70" t="n">
         <v>2025</v>
       </c>
       <c r="G70" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -3372,10 +3180,10 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>11000000</v>
+        <v>10000000</v>
       </c>
       <c r="J70" t="n">
-        <v>2868489</v>
+        <v>1168200</v>
       </c>
     </row>
     <row r="71">
@@ -3384,29 +3192,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="F71" t="n">
         <v>2025</v>
       </c>
       <c r="G71" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -3414,10 +3222,10 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>5000000</v>
+        <v>10000000</v>
       </c>
       <c r="J71" t="n">
-        <v>2115768</v>
+        <v>9026788</v>
       </c>
     </row>
     <row r="72">
@@ -3426,29 +3234,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="F72" t="n">
         <v>2025</v>
       </c>
       <c r="G72" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -3456,10 +3264,10 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>5000000</v>
+        <v>10000000</v>
       </c>
       <c r="J72" t="n">
-        <v>2111897</v>
+        <v>1068054</v>
       </c>
     </row>
     <row r="73">
@@ -3468,29 +3276,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="F73" t="n">
         <v>2025</v>
       </c>
       <c r="G73" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -3498,10 +3306,10 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>11000000</v>
+        <v>10000000</v>
       </c>
       <c r="J73" t="n">
-        <v>4914266</v>
+        <v>7992275</v>
       </c>
     </row>
     <row r="74">
@@ -3510,29 +3318,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="F74" t="n">
         <v>2025</v>
       </c>
       <c r="G74" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -3540,10 +3348,10 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>5000000</v>
+        <v>10000000</v>
       </c>
       <c r="J74" t="n">
-        <v>3017400</v>
+        <v>8596433</v>
       </c>
     </row>
     <row r="75">
@@ -3552,29 +3360,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="F75" t="n">
         <v>2025</v>
       </c>
       <c r="G75" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -3582,10 +3390,10 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>5000000</v>
+        <v>10000000</v>
       </c>
       <c r="J75" t="n">
-        <v>5939307</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="76">
@@ -3594,29 +3402,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="F76" t="n">
         <v>2025</v>
       </c>
       <c r="G76" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -3624,10 +3432,10 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>5000000</v>
+        <v>10000000</v>
       </c>
       <c r="J76" t="n">
-        <v>3240885</v>
+        <v>14785443</v>
       </c>
     </row>
     <row r="77">
@@ -3636,29 +3444,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="F77" t="n">
         <v>2025</v>
       </c>
       <c r="G77" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -3666,10 +3474,10 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>11000000</v>
+        <v>10000000</v>
       </c>
       <c r="J77" t="n">
-        <v>10681290</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="78">
@@ -3678,17 +3486,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>006</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>007130</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3708,10 +3516,10 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>11000000</v>
+        <v>6000000</v>
       </c>
       <c r="J78" t="n">
-        <v>4634266</v>
+        <v>770670</v>
       </c>
     </row>
     <row r="79">
@@ -3720,17 +3528,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>006</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>007130</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3750,10 +3558,10 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>11000000</v>
+        <v>6000000</v>
       </c>
       <c r="J79" t="n">
-        <v>7207769</v>
+        <v>160005</v>
       </c>
     </row>
     <row r="80">
@@ -3762,17 +3570,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>006</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>007130</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3792,10 +3600,10 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>5000000</v>
+        <v>6000000</v>
       </c>
       <c r="J80" t="n">
-        <v>5716521</v>
+        <v>1160190</v>
       </c>
     </row>
     <row r="81">
@@ -3804,29 +3612,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>006</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="F81" t="n">
         <v>2025</v>
       </c>
       <c r="G81" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -3834,10 +3642,10 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>24000000</v>
+        <v>40000000</v>
       </c>
       <c r="J81" t="n">
-        <v>14859000</v>
+        <v>9180565</v>
       </c>
     </row>
     <row r="82">
@@ -3846,29 +3654,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>006</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="F82" t="n">
         <v>2025</v>
       </c>
       <c r="G82" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -3876,10 +3684,10 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>14000000</v>
+        <v>40000000</v>
       </c>
       <c r="J82" t="n">
-        <v>1392000</v>
+        <v>8752087</v>
       </c>
     </row>
     <row r="83">
@@ -3888,29 +3696,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>006</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="F83" t="n">
         <v>2025</v>
       </c>
       <c r="G83" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -3918,10 +3726,10 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>14000000</v>
+        <v>40000000</v>
       </c>
       <c r="J83" t="n">
-        <v>1722276</v>
+        <v>16690098</v>
       </c>
     </row>
     <row r="84">
@@ -3930,29 +3738,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>054</t>
+          <t>006</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="F84" t="n">
         <v>2025</v>
       </c>
       <c r="G84" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -3960,10 +3768,10 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>14000000</v>
+        <v>40000000</v>
       </c>
       <c r="J84" t="n">
-        <v>689000</v>
+        <v>26763409</v>
       </c>
     </row>
     <row r="85">
@@ -3972,29 +3780,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>066</t>
+          <t>006</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="F85" t="n">
         <v>2025</v>
       </c>
       <c r="G85" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -4005,7 +3813,7 @@
         <v>40000000</v>
       </c>
       <c r="J85" t="n">
-        <v>4043518</v>
+        <v>22446603</v>
       </c>
     </row>
     <row r="86">
@@ -4014,29 +3822,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>066</t>
+          <t>012</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>685001</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>PUSLATPUR KODIKLATAD</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="F86" t="n">
         <v>2025</v>
       </c>
       <c r="G86" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -4044,10 +3852,10 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>40000000</v>
+        <v>3000000</v>
       </c>
       <c r="J86" t="n">
-        <v>37740000</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="87">
@@ -4056,17 +3864,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>066</t>
+          <t>015</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4089,7 +3897,7 @@
         <v>40000000</v>
       </c>
       <c r="J87" t="n">
-        <v>12365000</v>
+        <v>19651577</v>
       </c>
     </row>
     <row r="88">
@@ -4098,29 +3906,29 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>066</t>
+          <t>015</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="F88" t="n">
         <v>2025</v>
       </c>
       <c r="G88" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -4131,7 +3939,7 @@
         <v>40000000</v>
       </c>
       <c r="J88" t="n">
-        <v>9286864</v>
+        <v>9670989</v>
       </c>
     </row>
     <row r="89">
@@ -4140,29 +3948,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>015</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>656553</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="F89" t="n">
         <v>2025</v>
       </c>
       <c r="G89" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -4170,10 +3978,10 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>50000000</v>
+        <v>40000000</v>
       </c>
       <c r="J89" t="n">
-        <v>775000</v>
+        <v>6743111</v>
       </c>
     </row>
     <row r="90">
@@ -4182,29 +3990,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>015</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="F90" t="n">
         <v>2025</v>
       </c>
       <c r="G90" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -4212,10 +4020,10 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>16000000</v>
+        <v>40000000</v>
       </c>
       <c r="J90" t="n">
-        <v>2289406</v>
+        <v>9978760</v>
       </c>
     </row>
     <row r="91">
@@ -4224,29 +4032,29 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>015</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="F91" t="n">
         <v>2025</v>
       </c>
       <c r="G91" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -4254,10 +4062,10 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>16000000</v>
+        <v>40000000</v>
       </c>
       <c r="J91" t="n">
-        <v>3668591</v>
+        <v>22314667</v>
       </c>
     </row>
     <row r="92">
@@ -4266,29 +4074,29 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>015</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="F92" t="n">
         <v>2025</v>
       </c>
       <c r="G92" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -4296,10 +4104,10 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>16000000</v>
+        <v>40000000</v>
       </c>
       <c r="J92" t="n">
-        <v>2283305</v>
+        <v>8400111</v>
       </c>
     </row>
     <row r="93">
@@ -4308,29 +4116,29 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>015</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="F93" t="n">
         <v>2025</v>
       </c>
       <c r="G93" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -4338,10 +4146,10 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>32000000</v>
+        <v>70000000</v>
       </c>
       <c r="J93" t="n">
-        <v>7554670</v>
+        <v>1489998</v>
       </c>
     </row>
     <row r="94">
@@ -4350,29 +4158,29 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>015</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="F94" t="n">
         <v>2025</v>
       </c>
       <c r="G94" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -4380,10 +4188,10 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>32000000</v>
+        <v>10000000</v>
       </c>
       <c r="J94" t="n">
-        <v>2727445</v>
+        <v>3211146</v>
       </c>
     </row>
     <row r="95">
@@ -4392,29 +4200,29 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>015</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="F95" t="n">
         <v>2025</v>
       </c>
       <c r="G95" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -4422,10 +4230,10 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>16000000</v>
+        <v>10000000</v>
       </c>
       <c r="J95" t="n">
-        <v>7326664</v>
+        <v>5902139</v>
       </c>
     </row>
     <row r="96">
@@ -4434,29 +4242,29 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>015</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="F96" t="n">
         <v>2025</v>
       </c>
       <c r="G96" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -4464,10 +4272,10 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>16000000</v>
+        <v>10000000</v>
       </c>
       <c r="J96" t="n">
-        <v>3185388</v>
+        <v>6077473</v>
       </c>
     </row>
     <row r="97">
@@ -4476,29 +4284,29 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>015</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="F97" t="n">
         <v>2025</v>
       </c>
       <c r="G97" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -4506,10 +4314,10 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>16000000</v>
+        <v>10000000</v>
       </c>
       <c r="J97" t="n">
-        <v>4151070</v>
+        <v>7744485</v>
       </c>
     </row>
     <row r="98">
@@ -4518,29 +4326,29 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>015</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="F98" t="n">
         <v>2025</v>
       </c>
       <c r="G98" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -4548,10 +4356,10 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1900000</v>
+        <v>10000000</v>
       </c>
       <c r="J98" t="n">
-        <v>1904397</v>
+        <v>2241786</v>
       </c>
     </row>
     <row r="99">
@@ -4560,29 +4368,29 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>015</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="F99" t="n">
         <v>2025</v>
       </c>
       <c r="G99" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -4590,10 +4398,10 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1900000</v>
+        <v>16000000</v>
       </c>
       <c r="J99" t="n">
-        <v>640133</v>
+        <v>3889590</v>
       </c>
     </row>
     <row r="100">
@@ -4602,29 +4410,29 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>015</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="F100" t="n">
         <v>2025</v>
       </c>
       <c r="G100" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -4632,10 +4440,10 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1900000</v>
+        <v>16000000</v>
       </c>
       <c r="J100" t="n">
-        <v>1720000</v>
+        <v>68700000</v>
       </c>
     </row>
     <row r="101">
@@ -4644,29 +4452,29 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>015</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="F101" t="n">
         <v>2025</v>
       </c>
       <c r="G101" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -4674,10 +4482,10 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1900000</v>
+        <v>16000000</v>
       </c>
       <c r="J101" t="n">
-        <v>128530</v>
+        <v>33307620</v>
       </c>
     </row>
     <row r="102">
@@ -4686,29 +4494,29 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>076</t>
+          <t>015</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="F102" t="n">
         <v>2025</v>
       </c>
       <c r="G102" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -4716,10 +4524,10 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1900000</v>
+        <v>6000000</v>
       </c>
       <c r="J102" t="n">
-        <v>401000</v>
+        <v>259000</v>
       </c>
     </row>
     <row r="103">
@@ -4728,29 +4536,29 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>024</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>690801</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA</t>
+          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="F103" t="n">
         <v>2025</v>
       </c>
       <c r="G103" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -4758,10 +4566,10 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>40000000</v>
+        <v>22000000</v>
       </c>
       <c r="J103" t="n">
-        <v>1082700</v>
+        <v>1865319</v>
       </c>
     </row>
     <row r="104">
@@ -4770,29 +4578,29 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>024</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>690801</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA</t>
+          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="F104" t="n">
         <v>2025</v>
       </c>
       <c r="G104" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -4800,10 +4608,10 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>40000000</v>
+        <v>22000000</v>
       </c>
       <c r="J104" t="n">
-        <v>2260122</v>
+        <v>2717905</v>
       </c>
     </row>
     <row r="105">
@@ -4812,17 +4620,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>025</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>424245</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4842,10 +4650,10 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>40000000</v>
+        <v>10000000</v>
       </c>
       <c r="J105" t="n">
-        <v>2806886</v>
+        <v>568000</v>
       </c>
     </row>
     <row r="106">
@@ -4854,29 +4662,29 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>025</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>553099</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="F106" t="n">
         <v>2025</v>
       </c>
       <c r="G106" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -4884,10 +4692,10 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>40000000</v>
+        <v>6000000</v>
       </c>
       <c r="J106" t="n">
-        <v>1082700</v>
+        <v>2911500</v>
       </c>
     </row>
     <row r="107">
@@ -4896,29 +4704,29 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>054</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>692339</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>RUTAN KELAS II B BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="F107" t="n">
         <v>2025</v>
       </c>
       <c r="G107" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -4926,10 +4734,10 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>6800000</v>
+        <v>28000000</v>
       </c>
       <c r="J107" t="n">
-        <v>1386000</v>
+        <v>19420000</v>
       </c>
     </row>
     <row r="108">
@@ -4938,39 +4746,2055 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G108" t="n">
+        <v>2</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="J108" t="n">
+        <v>6523503</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G109" t="n">
+        <v>3</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I109" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="J109" t="n">
+        <v>905070</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G110" t="n">
+        <v>4</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I110" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="J110" t="n">
+        <v>3822990</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G111" t="n">
+        <v>5</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I111" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="J111" t="n">
+        <v>1290545</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G112" t="n">
+        <v>6</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I112" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="J112" t="n">
+        <v>1517640</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G113" t="n">
+        <v>7</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I113" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="J113" t="n">
+        <v>8875815</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G114" t="n">
+        <v>8</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I114" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="J114" t="n">
+        <v>15951110</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G115" t="n">
+        <v>9</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="J115" t="n">
+        <v>17150045</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G116" t="n">
+        <v>10</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="J116" t="n">
+        <v>17095326</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>428258</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G117" t="n">
+        <v>11</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I117" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="J117" t="n">
+        <v>1074070</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G118" t="n">
+        <v>2</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="J118" t="n">
+        <v>2868489</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G119" t="n">
+        <v>3</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I119" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="J119" t="n">
+        <v>2115768</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G120" t="n">
+        <v>4</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="J120" t="n">
+        <v>2111897</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G121" t="n">
+        <v>5</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="J121" t="n">
+        <v>4914266</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G122" t="n">
+        <v>6</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="J122" t="n">
+        <v>3017400</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G123" t="n">
+        <v>7</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="J123" t="n">
+        <v>5939307</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G124" t="n">
+        <v>8</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="J124" t="n">
+        <v>3240885</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G125" t="n">
+        <v>9</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="J125" t="n">
+        <v>10681290</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G126" t="n">
+        <v>10</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="J126" t="n">
+        <v>4634266</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G127" t="n">
+        <v>11</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="J127" t="n">
+        <v>7207769</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G128" t="n">
+        <v>12</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="J128" t="n">
+        <v>5716521</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>668529</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G129" t="n">
+        <v>7</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I129" t="n">
+        <v>24000000</v>
+      </c>
+      <c r="J129" t="n">
+        <v>14859000</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>668529</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G130" t="n">
+        <v>8</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="J130" t="n">
+        <v>1392000</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>668529</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G131" t="n">
+        <v>9</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="J131" t="n">
+        <v>1722276</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>668529</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G132" t="n">
+        <v>10</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="J132" t="n">
+        <v>689000</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>066</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>111079</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G133" t="n">
+        <v>2</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="J133" t="n">
+        <v>4043518</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>066</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>111079</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G134" t="n">
+        <v>6</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="J134" t="n">
+        <v>37740000</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>066</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>111079</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G135" t="n">
+        <v>7</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="J135" t="n">
+        <v>12365000</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>066</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>111079</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G136" t="n">
+        <v>10</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="J136" t="n">
+        <v>9286864</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>076</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>656553</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G137" t="n">
+        <v>10</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="J137" t="n">
+        <v>775000</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>076</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>656560</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G138" t="n">
+        <v>2</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="J138" t="n">
+        <v>2289406</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>076</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>656560</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G139" t="n">
+        <v>4</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="J139" t="n">
+        <v>3668591</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>076</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>656560</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G140" t="n">
+        <v>6</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="J140" t="n">
+        <v>2283305</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>076</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>656560</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G141" t="n">
+        <v>8</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I141" t="n">
+        <v>32000000</v>
+      </c>
+      <c r="J141" t="n">
+        <v>7554670</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>076</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>656560</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G142" t="n">
+        <v>9</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I142" t="n">
+        <v>32000000</v>
+      </c>
+      <c r="J142" t="n">
+        <v>2727445</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>076</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>656560</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G143" t="n">
+        <v>10</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I143" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="J143" t="n">
+        <v>7326664</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>076</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>656560</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G144" t="n">
+        <v>11</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I144" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="J144" t="n">
+        <v>3185388</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>076</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>656560</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G145" t="n">
+        <v>12</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I145" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="J145" t="n">
+        <v>4151070</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>076</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>656574</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G146" t="n">
+        <v>2</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I146" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="J146" t="n">
+        <v>1904397</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>076</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>656574</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G147" t="n">
+        <v>3</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="J147" t="n">
+        <v>640133</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>076</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>656574</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G148" t="n">
+        <v>5</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I148" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="J148" t="n">
+        <v>1720000</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>076</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>656574</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G149" t="n">
+        <v>10</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I149" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="J149" t="n">
+        <v>128530</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>076</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>656574</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G150" t="n">
+        <v>11</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I150" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="J150" t="n">
+        <v>401000</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
           <t>137</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>692334</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>LAPAS KELAS II B MUARA DUA</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G151" t="n">
+        <v>8</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I151" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="J151" t="n">
+        <v>1082700</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>692334</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>LAPAS KELAS II B MUARA DUA</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G152" t="n">
+        <v>9</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I152" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="J152" t="n">
+        <v>2260122</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>692334</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>LAPAS KELAS II B MUARA DUA</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G153" t="n">
+        <v>10</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I153" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="J153" t="n">
+        <v>2806886</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>692334</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>LAPAS KELAS II B MUARA DUA</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G154" t="n">
+        <v>12</v>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I154" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="J154" t="n">
+        <v>1082700</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
         <is>
           <t>692339</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
+      <c r="D155" t="inlineStr">
         <is>
           <t>RUTAN KELAS II B BATURAJA</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G155" t="n">
+        <v>11</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I155" t="n">
+        <v>6800000</v>
+      </c>
+      <c r="J155" t="n">
+        <v>1386000</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>692339</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>RUTAN KELAS II B BATURAJA</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
         <is>
           <t>2025-12</t>
         </is>
       </c>
-      <c r="F108" t="n">
-        <v>2025</v>
-      </c>
-      <c r="G108" t="n">
+      <c r="F156" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G156" t="n">
         <v>12</v>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>LAMA</t>
-        </is>
-      </c>
-      <c r="I108" t="n">
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="I156" t="n">
         <v>6800000</v>
       </c>
-      <c r="J108" t="n">
+      <c r="J156" t="n">
         <v>3465000</v>
       </c>
     </row>

--- a/data_kkp/KKP_MASTER.xlsx
+++ b/data_kkp/KKP_MASTER.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I156"/>
+  <dimension ref="A1:I218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>8000000</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>145429</v>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>8000000</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>198180</v>
@@ -666,35 +666,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>007130</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>40000000</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>9180565</v>
+        <v>722230</v>
       </c>
     </row>
     <row r="8">
@@ -703,35 +703,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>007208</t>
+          <t>007130</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>40000000</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>8752087</v>
+        <v>2846077</v>
       </c>
     </row>
     <row r="9">
@@ -750,14 +750,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>2025</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -768,7 +768,7 @@
         <v>40000000</v>
       </c>
       <c r="I9" t="n">
-        <v>16690098</v>
+        <v>9180565</v>
       </c>
     </row>
     <row r="10">
@@ -787,14 +787,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="E10" t="n">
         <v>2025</v>
       </c>
       <c r="F10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>40000000</v>
       </c>
       <c r="I10" t="n">
-        <v>26763409</v>
+        <v>8752087</v>
       </c>
     </row>
     <row r="11">
@@ -824,14 +824,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>2025</v>
       </c>
       <c r="F11" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         <v>40000000</v>
       </c>
       <c r="I11" t="n">
-        <v>22446603</v>
+        <v>16690098</v>
       </c>
     </row>
     <row r="12">
@@ -861,25 +861,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>LAMA</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>24000000</v>
+        <v>40000000</v>
       </c>
       <c r="I12" t="n">
-        <v>19336463</v>
+        <v>26763409</v>
       </c>
     </row>
     <row r="13">
@@ -888,24 +888,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="E13" t="n">
         <v>2025</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>24000000</v>
+        <v>40000000</v>
       </c>
       <c r="I13" t="n">
-        <v>11321000</v>
+        <v>22446603</v>
       </c>
     </row>
     <row r="14">
@@ -925,35 +925,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F14" t="n">
         <v>2</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>24000000</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>17922000</v>
+        <v>19336463</v>
       </c>
     </row>
     <row r="15">
@@ -962,35 +962,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>098963</t>
+          <t>007208</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PENGADILAN NEGERI BATURAJA</t>
+          <t>KEJAKSAAN NEGERI OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>24000000</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>2650000</v>
+        <v>3451103</v>
       </c>
     </row>
     <row r="16">
@@ -1009,14 +1009,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>2025</v>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
         <v>24000000</v>
       </c>
       <c r="I16" t="n">
-        <v>3905000</v>
+        <v>11321000</v>
       </c>
     </row>
     <row r="17">
@@ -1046,14 +1046,14 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="E17" t="n">
         <v>2025</v>
       </c>
       <c r="F17" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         <v>24000000</v>
       </c>
       <c r="I17" t="n">
-        <v>3500000</v>
+        <v>17922000</v>
       </c>
     </row>
     <row r="18">
@@ -1083,14 +1083,14 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="E18" t="n">
         <v>2025</v>
       </c>
       <c r="F18" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>24000000</v>
       </c>
       <c r="I18" t="n">
-        <v>13874500</v>
+        <v>2650000</v>
       </c>
     </row>
     <row r="19">
@@ -1120,14 +1120,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="E19" t="n">
         <v>2025</v>
       </c>
       <c r="F19" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>24000000</v>
       </c>
       <c r="I19" t="n">
-        <v>3897000</v>
+        <v>3905000</v>
       </c>
     </row>
     <row r="20">
@@ -1157,14 +1157,14 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="E20" t="n">
         <v>2025</v>
       </c>
       <c r="F20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>24000000</v>
       </c>
       <c r="I20" t="n">
-        <v>13995500</v>
+        <v>3500000</v>
       </c>
     </row>
     <row r="21">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="E21" t="n">
         <v>2025</v>
       </c>
       <c r="F21" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>24000000</v>
       </c>
       <c r="I21" t="n">
-        <v>9151500</v>
+        <v>13874500</v>
       </c>
     </row>
     <row r="22">
@@ -1231,25 +1231,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>LAMA</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>43200000</v>
+        <v>24000000</v>
       </c>
       <c r="I22" t="n">
-        <v>10861535</v>
+        <v>3897000</v>
       </c>
     </row>
     <row r="23">
@@ -1268,25 +1268,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>LAMA</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>43200000</v>
+        <v>24000000</v>
       </c>
       <c r="I23" t="n">
-        <v>3980879</v>
+        <v>13995500</v>
       </c>
     </row>
     <row r="24">
@@ -1295,24 +1295,24 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="E24" t="n">
         <v>2025</v>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>40000000</v>
+        <v>24000000</v>
       </c>
       <c r="I24" t="n">
-        <v>4043518</v>
+        <v>9151500</v>
       </c>
     </row>
     <row r="25">
@@ -1332,35 +1332,35 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F25" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>40000000</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>37740000</v>
+        <v>10861535</v>
       </c>
     </row>
     <row r="26">
@@ -1369,35 +1369,35 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F26" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>40000000</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>12365000</v>
+        <v>3980879</v>
       </c>
     </row>
     <row r="27">
@@ -1406,35 +1406,35 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F27" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>40000000</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>9286864</v>
+        <v>15195074</v>
       </c>
     </row>
     <row r="28">
@@ -1443,24 +1443,24 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="E28" t="n">
         <v>2026</v>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1468,10 +1468,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>24000000</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>11031747</v>
+        <v>13990728</v>
       </c>
     </row>
     <row r="29">
@@ -1480,24 +1480,24 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>111079</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="E29" t="n">
         <v>2026</v>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>12000000</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>2695000</v>
+        <v>697080</v>
       </c>
     </row>
     <row r="30">
@@ -1517,35 +1517,35 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>098963</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>PENGADILAN NEGERI BATURAJA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>16000000</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>3618000</v>
+        <v>8735000</v>
       </c>
     </row>
     <row r="31">
@@ -1554,12 +1554,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1579,10 +1579,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>10000000</v>
+        <v>40000000</v>
       </c>
       <c r="I31" t="n">
-        <v>212017</v>
+        <v>4043518</v>
       </c>
     </row>
     <row r="32">
@@ -1591,24 +1591,24 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="E32" t="n">
         <v>2025</v>
       </c>
       <c r="F32" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>16000000</v>
+        <v>40000000</v>
       </c>
       <c r="I32" t="n">
-        <v>1362070</v>
+        <v>37740000</v>
       </c>
     </row>
     <row r="33">
@@ -1628,24 +1628,24 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="E33" t="n">
         <v>2025</v>
       </c>
       <c r="F33" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>16000000</v>
+        <v>40000000</v>
       </c>
       <c r="I33" t="n">
-        <v>2800570</v>
+        <v>12365000</v>
       </c>
     </row>
     <row r="34">
@@ -1665,24 +1665,24 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="E34" t="n">
         <v>2025</v>
       </c>
       <c r="F34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>16000000</v>
+        <v>40000000</v>
       </c>
       <c r="I34" t="n">
-        <v>4221853</v>
+        <v>9286864</v>
       </c>
     </row>
     <row r="35">
@@ -1702,35 +1702,35 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F35" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>16000000</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>4371470</v>
+        <v>11031747</v>
       </c>
     </row>
     <row r="36">
@@ -1739,35 +1739,35 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>401944</t>
+          <t>111079</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA MARTAPURA</t>
+          <t>BADAN NARKOTIKA NASIONAL KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F36" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>10000000</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>1933320</v>
+        <v>2695000</v>
       </c>
     </row>
     <row r="37">
@@ -1786,14 +1786,14 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="E37" t="n">
         <v>2025</v>
       </c>
       <c r="F37" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>16000000</v>
       </c>
       <c r="I37" t="n">
-        <v>5285170</v>
+        <v>3618000</v>
       </c>
     </row>
     <row r="38">
@@ -1823,14 +1823,14 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="E38" t="n">
         <v>2025</v>
       </c>
       <c r="F38" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1838,10 +1838,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>16000000</v>
+        <v>10000000</v>
       </c>
       <c r="I38" t="n">
-        <v>7754710</v>
+        <v>212017</v>
       </c>
     </row>
     <row r="39">
@@ -1860,14 +1860,14 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="E39" t="n">
         <v>2025</v>
       </c>
       <c r="F39" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>16000000</v>
       </c>
       <c r="I39" t="n">
-        <v>10124059</v>
+        <v>1362070</v>
       </c>
     </row>
     <row r="40">
@@ -1897,14 +1897,14 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="E40" t="n">
         <v>2025</v>
       </c>
       <c r="F40" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>10000000</v>
+        <v>16000000</v>
       </c>
       <c r="I40" t="n">
-        <v>3348270</v>
+        <v>2800570</v>
       </c>
     </row>
     <row r="41">
@@ -1934,25 +1934,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>LAMA</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>24000000</v>
+        <v>16000000</v>
       </c>
       <c r="I41" t="n">
-        <v>5926136</v>
+        <v>4221853</v>
       </c>
     </row>
     <row r="42">
@@ -1971,25 +1971,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>LAMA</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>24000000</v>
+        <v>16000000</v>
       </c>
       <c r="I42" t="n">
-        <v>5142960</v>
+        <v>4371470</v>
       </c>
     </row>
     <row r="43">
@@ -2008,25 +2008,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="F43" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>LAMA</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>40000000</v>
+        <v>10000000</v>
       </c>
       <c r="I43" t="n">
-        <v>7850987</v>
+        <v>1933320</v>
       </c>
     </row>
     <row r="44">
@@ -2045,25 +2045,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="F44" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>LAMA</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>32000000</v>
+        <v>16000000</v>
       </c>
       <c r="I44" t="n">
-        <v>5025020</v>
+        <v>5285170</v>
       </c>
     </row>
     <row r="45">
@@ -2072,24 +2072,24 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="E45" t="n">
         <v>2025</v>
       </c>
       <c r="F45" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>10000000</v>
+        <v>16000000</v>
       </c>
       <c r="I45" t="n">
-        <v>1168200</v>
+        <v>7754710</v>
       </c>
     </row>
     <row r="46">
@@ -2109,24 +2109,24 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="E46" t="n">
         <v>2025</v>
       </c>
       <c r="F46" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>10000000</v>
+        <v>16000000</v>
       </c>
       <c r="I46" t="n">
-        <v>9026788</v>
+        <v>10124059</v>
       </c>
     </row>
     <row r="47">
@@ -2146,24 +2146,24 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="E47" t="n">
         <v>2025</v>
       </c>
       <c r="F47" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>10000000</v>
       </c>
       <c r="I47" t="n">
-        <v>1068054</v>
+        <v>3348270</v>
       </c>
     </row>
     <row r="48">
@@ -2183,35 +2183,35 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F48" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>10000000</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>7992275</v>
+        <v>5926136</v>
       </c>
     </row>
     <row r="49">
@@ -2220,35 +2220,35 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F49" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>10000000</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>8596433</v>
+        <v>5142960</v>
       </c>
     </row>
     <row r="50">
@@ -2257,35 +2257,35 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F50" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>10000000</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>10000</v>
+        <v>7850987</v>
       </c>
     </row>
     <row r="51">
@@ -2294,35 +2294,35 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F51" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>10000000</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>14785443</v>
+        <v>5025020</v>
       </c>
     </row>
     <row r="52">
@@ -2331,35 +2331,35 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F52" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>10000000</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>10000</v>
+        <v>9364058</v>
       </c>
     </row>
     <row r="53">
@@ -2368,24 +2368,24 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="E53" t="n">
         <v>2026</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>72000000</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>9817209</v>
+        <v>9684986</v>
       </c>
     </row>
     <row r="54">
@@ -2405,24 +2405,24 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>402267</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>PENGADILAN AGAMA BATURAJA</t>
+          <t>PENGADILAN AGAMA MARTAPURA</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="E54" t="n">
         <v>2026</v>
       </c>
       <c r="F54" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2430,10 +2430,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>56000000</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>14099104</v>
+        <v>9857297</v>
       </c>
     </row>
     <row r="55">
@@ -2452,25 +2452,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="F55" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>LAMA</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>48000000</v>
+        <v>10000000</v>
       </c>
       <c r="I55" t="n">
-        <v>10919258</v>
+        <v>1168200</v>
       </c>
     </row>
     <row r="56">
@@ -2489,25 +2489,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="F56" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>LAMA</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>24000000</v>
+        <v>10000000</v>
       </c>
       <c r="I56" t="n">
-        <v>7257331</v>
+        <v>9026788</v>
       </c>
     </row>
     <row r="57">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2541,10 +2541,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>40000000</v>
+        <v>10000000</v>
       </c>
       <c r="I57" t="n">
-        <v>19651577</v>
+        <v>1068054</v>
       </c>
     </row>
     <row r="58">
@@ -2553,12 +2553,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2578,10 +2578,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>40000000</v>
+        <v>10000000</v>
       </c>
       <c r="I58" t="n">
-        <v>9670989</v>
+        <v>7992275</v>
       </c>
     </row>
     <row r="59">
@@ -2590,12 +2590,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2615,10 +2615,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>40000000</v>
+        <v>10000000</v>
       </c>
       <c r="I59" t="n">
-        <v>6743111</v>
+        <v>8596433</v>
       </c>
     </row>
     <row r="60">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>40000000</v>
+        <v>10000000</v>
       </c>
       <c r="I60" t="n">
-        <v>9978760</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="61">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>40000000</v>
+        <v>10000000</v>
       </c>
       <c r="I61" t="n">
-        <v>22314667</v>
+        <v>14785443</v>
       </c>
     </row>
     <row r="62">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>40000000</v>
+        <v>10000000</v>
       </c>
       <c r="I62" t="n">
-        <v>8400111</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="63">
@@ -2738,24 +2738,24 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="E63" t="n">
         <v>2026</v>
       </c>
       <c r="F63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>40000000</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>12334663</v>
+        <v>9817209</v>
       </c>
     </row>
     <row r="64">
@@ -2775,24 +2775,24 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="E64" t="n">
         <v>2026</v>
       </c>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>120000000</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>8053774</v>
+        <v>14099104</v>
       </c>
     </row>
     <row r="65">
@@ -2812,24 +2812,24 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>410574</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="E65" t="n">
         <v>2026</v>
       </c>
       <c r="F65" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2837,10 +2837,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>40000000</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>4849486</v>
+        <v>10919258</v>
       </c>
     </row>
     <row r="66">
@@ -2849,35 +2849,35 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>424245</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F66" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>10000000</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>568000</v>
+        <v>30736359</v>
       </c>
     </row>
     <row r="67">
@@ -2886,24 +2886,24 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>424245</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="E67" t="n">
         <v>2026</v>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2911,10 +2911,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>17600000</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>3273950</v>
+        <v>6614010</v>
       </c>
     </row>
     <row r="68">
@@ -2923,24 +2923,24 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>424245</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="E68" t="n">
         <v>2026</v>
       </c>
       <c r="F68" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2948,10 +2948,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>8800000</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>2223600</v>
+        <v>5502100</v>
       </c>
     </row>
     <row r="69">
@@ -2960,24 +2960,24 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>424245</t>
+          <t>402267</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
+          <t>PENGADILAN AGAMA BATURAJA</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="E69" t="n">
         <v>2026</v>
       </c>
       <c r="F69" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>8800000</v>
+        <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>1067000</v>
+        <v>14306400</v>
       </c>
     </row>
     <row r="70">
@@ -2997,24 +2997,24 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="E70" t="n">
         <v>2025</v>
       </c>
       <c r="F70" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3022,10 +3022,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>28000000</v>
+        <v>40000000</v>
       </c>
       <c r="I70" t="n">
-        <v>19420000</v>
+        <v>19651577</v>
       </c>
     </row>
     <row r="71">
@@ -3034,24 +3034,24 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="E71" t="n">
         <v>2025</v>
       </c>
       <c r="F71" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>18000000</v>
+        <v>40000000</v>
       </c>
       <c r="I71" t="n">
-        <v>6523503</v>
+        <v>9670989</v>
       </c>
     </row>
     <row r="72">
@@ -3071,24 +3071,24 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="E72" t="n">
         <v>2025</v>
       </c>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>18000000</v>
+        <v>40000000</v>
       </c>
       <c r="I72" t="n">
-        <v>905070</v>
+        <v>6743111</v>
       </c>
     </row>
     <row r="73">
@@ -3108,24 +3108,24 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="E73" t="n">
         <v>2025</v>
       </c>
       <c r="F73" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>18000000</v>
+        <v>40000000</v>
       </c>
       <c r="I73" t="n">
-        <v>3822990</v>
+        <v>9978760</v>
       </c>
     </row>
     <row r="74">
@@ -3145,24 +3145,24 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="E74" t="n">
         <v>2025</v>
       </c>
       <c r="F74" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>18000000</v>
+        <v>40000000</v>
       </c>
       <c r="I74" t="n">
-        <v>1290545</v>
+        <v>22314667</v>
       </c>
     </row>
     <row r="75">
@@ -3182,24 +3182,24 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="E75" t="n">
         <v>2025</v>
       </c>
       <c r="F75" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3207,10 +3207,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>18000000</v>
+        <v>40000000</v>
       </c>
       <c r="I75" t="n">
-        <v>1517640</v>
+        <v>8400111</v>
       </c>
     </row>
     <row r="76">
@@ -3219,35 +3219,35 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F76" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>18000000</v>
+        <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>8875815</v>
+        <v>12334663</v>
       </c>
     </row>
     <row r="77">
@@ -3256,35 +3256,35 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F77" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>18000000</v>
+        <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>15951110</v>
+        <v>8053774</v>
       </c>
     </row>
     <row r="78">
@@ -3293,35 +3293,35 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F78" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>18000000</v>
+        <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>17150045</v>
+        <v>4849486</v>
       </c>
     </row>
     <row r="79">
@@ -3330,35 +3330,35 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>18000000</v>
+        <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>17095326</v>
+        <v>17655648</v>
       </c>
     </row>
     <row r="80">
@@ -3367,35 +3367,35 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F80" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>18000000</v>
+        <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>1074070</v>
+        <v>1496690</v>
       </c>
     </row>
     <row r="81">
@@ -3404,24 +3404,24 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>410574</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>KANTOR PELAYANAN PAJAK PRATAMA BATURAJA</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="E81" t="n">
         <v>2026</v>
       </c>
       <c r="F81" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3429,10 +3429,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>40000000</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>5055500</v>
+        <v>9007192</v>
       </c>
     </row>
     <row r="82">
@@ -3441,35 +3441,35 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>424245</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>LAMA</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>100000000</v>
+        <v>10000000</v>
       </c>
       <c r="I82" t="n">
-        <v>12720428</v>
+        <v>568000</v>
       </c>
     </row>
     <row r="83">
@@ -3478,24 +3478,24 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>428258</t>
+          <t>424245</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="E83" t="n">
         <v>2026</v>
       </c>
       <c r="F83" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3503,10 +3503,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>120000000</v>
+        <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>6387960</v>
+        <v>3273950</v>
       </c>
     </row>
     <row r="84">
@@ -3515,35 +3515,35 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>424245</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>70000000</v>
+        <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>1489998</v>
+        <v>2223600</v>
       </c>
     </row>
     <row r="85">
@@ -3552,35 +3552,35 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>424245</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F85" t="n">
         <v>4</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>10000000</v>
+        <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>3211146</v>
+        <v>1067000</v>
       </c>
     </row>
     <row r="86">
@@ -3589,35 +3589,35 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>424245</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F86" t="n">
         <v>5</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>10000000</v>
+        <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>5902139</v>
+        <v>1562500</v>
       </c>
     </row>
     <row r="87">
@@ -3626,35 +3626,35 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>424245</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F87" t="n">
         <v>6</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>10000000</v>
+        <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>6077473</v>
+        <v>5585000</v>
       </c>
     </row>
     <row r="88">
@@ -3663,35 +3663,35 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>424245</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>MADRASAH ALIYAH NEGERI 1 OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F88" t="n">
         <v>7</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>10000000</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>7744485</v>
+        <v>1300000</v>
       </c>
     </row>
     <row r="89">
@@ -3700,24 +3700,24 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="E89" t="n">
         <v>2025</v>
       </c>
       <c r="F89" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -3725,10 +3725,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>10000000</v>
+        <v>28000000</v>
       </c>
       <c r="I89" t="n">
-        <v>2241786</v>
+        <v>19420000</v>
       </c>
     </row>
     <row r="90">
@@ -3737,24 +3737,24 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="E90" t="n">
         <v>2025</v>
       </c>
       <c r="F90" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -3762,10 +3762,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>16000000</v>
+        <v>18000000</v>
       </c>
       <c r="I90" t="n">
-        <v>3889590</v>
+        <v>6523503</v>
       </c>
     </row>
     <row r="91">
@@ -3774,24 +3774,24 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="E91" t="n">
         <v>2025</v>
       </c>
       <c r="F91" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -3799,10 +3799,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>16000000</v>
+        <v>18000000</v>
       </c>
       <c r="I91" t="n">
-        <v>68700000</v>
+        <v>905070</v>
       </c>
     </row>
     <row r="92">
@@ -3811,24 +3811,24 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="E92" t="n">
         <v>2025</v>
       </c>
       <c r="F92" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>16000000</v>
+        <v>18000000</v>
       </c>
       <c r="I92" t="n">
-        <v>33307620</v>
+        <v>3822990</v>
       </c>
     </row>
     <row r="93">
@@ -3848,24 +3848,24 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>527975</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="E93" t="n">
         <v>2025</v>
       </c>
       <c r="F93" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -3873,10 +3873,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>6000000</v>
+        <v>18000000</v>
       </c>
       <c r="I93" t="n">
-        <v>259000</v>
+        <v>1290545</v>
       </c>
     </row>
     <row r="94">
@@ -3885,24 +3885,24 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>553099</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="E94" t="n">
         <v>2025</v>
       </c>
       <c r="F94" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -3910,10 +3910,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>6000000</v>
+        <v>18000000</v>
       </c>
       <c r="I94" t="n">
-        <v>2911500</v>
+        <v>1517640</v>
       </c>
     </row>
     <row r="95">
@@ -3922,35 +3922,35 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>641681</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="F95" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>LAMA</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>360000000</v>
+        <v>18000000</v>
       </c>
       <c r="I95" t="n">
-        <v>61610000</v>
+        <v>8875815</v>
       </c>
     </row>
     <row r="96">
@@ -3959,35 +3959,35 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>641681</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="F96" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>LAMA</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>360000000</v>
+        <v>18000000</v>
       </c>
       <c r="I96" t="n">
-        <v>54210000</v>
+        <v>15951110</v>
       </c>
     </row>
     <row r="97">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>656553</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="E97" t="n">
         <v>2025</v>
       </c>
       <c r="F97" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -4021,10 +4021,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>50000000</v>
+        <v>18000000</v>
       </c>
       <c r="I97" t="n">
-        <v>775000</v>
+        <v>17150045</v>
       </c>
     </row>
     <row r="98">
@@ -4033,35 +4033,35 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>656553</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="F98" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>LAMA</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>2000000</v>
+        <v>18000000</v>
       </c>
       <c r="I98" t="n">
-        <v>1721500</v>
+        <v>17095326</v>
       </c>
     </row>
     <row r="99">
@@ -4070,35 +4070,35 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>656553</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="F99" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>LAMA</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>6000000</v>
+        <v>18000000</v>
       </c>
       <c r="I99" t="n">
-        <v>5455000</v>
+        <v>1074070</v>
       </c>
     </row>
     <row r="100">
@@ -4107,24 +4107,24 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>656553</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="E100" t="n">
         <v>2026</v>
       </c>
       <c r="F100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>1995000</v>
+        <v>5055500</v>
       </c>
     </row>
     <row r="101">
@@ -4144,24 +4144,24 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>656553</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="E101" t="n">
         <v>2026</v>
       </c>
       <c r="F101" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -4169,10 +4169,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>1990000</v>
+        <v>12720428</v>
       </c>
     </row>
     <row r="102">
@@ -4181,35 +4181,35 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F102" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>16000000</v>
+        <v>0</v>
       </c>
       <c r="I102" t="n">
-        <v>2289406</v>
+        <v>6387960</v>
       </c>
     </row>
     <row r="103">
@@ -4218,35 +4218,35 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F103" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>16000000</v>
+        <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>3668591</v>
+        <v>3002960</v>
       </c>
     </row>
     <row r="104">
@@ -4255,35 +4255,35 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F104" t="n">
         <v>6</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>16000000</v>
+        <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>2283305</v>
+        <v>5400960</v>
       </c>
     </row>
     <row r="105">
@@ -4292,35 +4292,35 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>428258</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F105" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>32000000</v>
+        <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>7554670</v>
+        <v>8636460</v>
       </c>
     </row>
     <row r="106">
@@ -4329,24 +4329,24 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="E106" t="n">
         <v>2025</v>
       </c>
       <c r="F106" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -4354,10 +4354,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>32000000</v>
+        <v>70000000</v>
       </c>
       <c r="I106" t="n">
-        <v>2727445</v>
+        <v>1489998</v>
       </c>
     </row>
     <row r="107">
@@ -4366,24 +4366,24 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="E107" t="n">
         <v>2025</v>
       </c>
       <c r="F107" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -4391,10 +4391,10 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>16000000</v>
+        <v>10000000</v>
       </c>
       <c r="I107" t="n">
-        <v>7326664</v>
+        <v>3211146</v>
       </c>
     </row>
     <row r="108">
@@ -4403,24 +4403,24 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="E108" t="n">
         <v>2025</v>
       </c>
       <c r="F108" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -4428,10 +4428,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>16000000</v>
+        <v>10000000</v>
       </c>
       <c r="I108" t="n">
-        <v>3185388</v>
+        <v>5902139</v>
       </c>
     </row>
     <row r="109">
@@ -4440,24 +4440,24 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="E109" t="n">
         <v>2025</v>
       </c>
       <c r="F109" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -4465,10 +4465,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>16000000</v>
+        <v>10000000</v>
       </c>
       <c r="I109" t="n">
-        <v>4151070</v>
+        <v>6077473</v>
       </c>
     </row>
     <row r="110">
@@ -4477,35 +4477,35 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="F110" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>LAMA</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>30000000</v>
+        <v>10000000</v>
       </c>
       <c r="I110" t="n">
-        <v>6034789</v>
+        <v>7744485</v>
       </c>
     </row>
     <row r="111">
@@ -4514,35 +4514,35 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>656560</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="F111" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>LAMA</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>20000000</v>
+        <v>10000000</v>
       </c>
       <c r="I111" t="n">
-        <v>2679300</v>
+        <v>2241786</v>
       </c>
     </row>
     <row r="112">
@@ -4551,24 +4551,24 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="E112" t="n">
         <v>2025</v>
       </c>
       <c r="F112" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -4576,10 +4576,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>1900000</v>
+        <v>16000000</v>
       </c>
       <c r="I112" t="n">
-        <v>1904397</v>
+        <v>3889590</v>
       </c>
     </row>
     <row r="113">
@@ -4588,24 +4588,24 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="E113" t="n">
         <v>2025</v>
       </c>
       <c r="F113" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>1900000</v>
+        <v>16000000</v>
       </c>
       <c r="I113" t="n">
-        <v>640133</v>
+        <v>68700000</v>
       </c>
     </row>
     <row r="114">
@@ -4625,24 +4625,24 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="E114" t="n">
         <v>2025</v>
       </c>
       <c r="F114" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -4650,10 +4650,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>1900000</v>
+        <v>16000000</v>
       </c>
       <c r="I114" t="n">
-        <v>1720000</v>
+        <v>33307620</v>
       </c>
     </row>
     <row r="115">
@@ -4662,24 +4662,24 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="E115" t="n">
         <v>2025</v>
       </c>
       <c r="F115" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -4687,10 +4687,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>1900000</v>
+        <v>6000000</v>
       </c>
       <c r="I115" t="n">
-        <v>128530</v>
+        <v>259000</v>
       </c>
     </row>
     <row r="116">
@@ -4699,35 +4699,35 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F116" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>1900000</v>
+        <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>401000</v>
+        <v>12332819</v>
       </c>
     </row>
     <row r="117">
@@ -4736,24 +4736,24 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="E117" t="n">
         <v>2026</v>
       </c>
       <c r="F117" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -4761,10 +4761,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>4000000</v>
+        <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>1216870</v>
+        <v>31243134</v>
       </c>
     </row>
     <row r="118">
@@ -4773,24 +4773,24 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>656574</t>
+          <t>527975</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
+          <t>KANTOR PELAYANAN PERBENDAHARAAN NEGARA BATURAJA</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="E118" t="n">
         <v>2026</v>
       </c>
       <c r="F118" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -4798,10 +4798,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>4000000</v>
+        <v>0</v>
       </c>
       <c r="I118" t="n">
-        <v>350550</v>
+        <v>17970000</v>
       </c>
     </row>
     <row r="119">
@@ -4810,35 +4810,35 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>665292</t>
+          <t>553099</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU TIMUR</t>
+          <t>MADRASAH TSANAWIYAH NEGERI 3 OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="F119" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>LAMA</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>80000000</v>
+        <v>6000000</v>
       </c>
       <c r="I119" t="n">
-        <v>16512000</v>
+        <v>2911500</v>
       </c>
     </row>
     <row r="120">
@@ -4847,24 +4847,24 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>665292</t>
+          <t>641681</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU TIMUR</t>
+          <t>POLRES OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="E120" t="n">
         <v>2026</v>
       </c>
       <c r="F120" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -4872,10 +4872,10 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>80000000</v>
+        <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>16512000</v>
+        <v>61610000</v>
       </c>
     </row>
     <row r="121">
@@ -4884,24 +4884,24 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>665307</t>
+          <t>641681</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU SELATAN</t>
+          <t>POLRES OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="E121" t="n">
         <v>2026</v>
       </c>
       <c r="F121" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -4909,10 +4909,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>120000000</v>
+        <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>59780000</v>
+        <v>54210000</v>
       </c>
     </row>
     <row r="122">
@@ -4921,24 +4921,24 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>665307</t>
+          <t>641681</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU SELATAN</t>
+          <t>POLRES OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="E122" t="n">
         <v>2026</v>
       </c>
       <c r="F122" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -4946,10 +4946,10 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>120000000</v>
+        <v>0</v>
       </c>
       <c r="I122" t="n">
-        <v>24770827</v>
+        <v>30805000</v>
       </c>
     </row>
     <row r="123">
@@ -4958,24 +4958,24 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>665307</t>
+          <t>641681</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>POLRES OGAN KOMERING ULU SELATAN</t>
+          <t>POLRES OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="E123" t="n">
         <v>2026</v>
       </c>
       <c r="F123" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -4983,10 +4983,10 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>240000000</v>
+        <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>37398067</v>
+        <v>30805000</v>
       </c>
     </row>
     <row r="124">
@@ -4995,35 +4995,35 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>641681</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>POLRES OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F124" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>11000000</v>
+        <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>2868489</v>
+        <v>11500000</v>
       </c>
     </row>
     <row r="125">
@@ -5032,24 +5032,24 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>656553</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="E125" t="n">
         <v>2025</v>
       </c>
       <c r="F125" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -5057,10 +5057,10 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>5000000</v>
+        <v>50000000</v>
       </c>
       <c r="I125" t="n">
-        <v>2115768</v>
+        <v>775000</v>
       </c>
     </row>
     <row r="126">
@@ -5069,35 +5069,35 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>656553</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>KPU KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F126" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>2111897</v>
+        <v>1721500</v>
       </c>
     </row>
     <row r="127">
@@ -5106,35 +5106,35 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>656553</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>KPU KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F127" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>11000000</v>
+        <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>4914266</v>
+        <v>5455000</v>
       </c>
     </row>
     <row r="128">
@@ -5143,35 +5143,35 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>656553</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>KPU KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F128" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>3017400</v>
+        <v>1995000</v>
       </c>
     </row>
     <row r="129">
@@ -5180,35 +5180,35 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>656553</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>KPU KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F129" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>5939307</v>
+        <v>3985000</v>
       </c>
     </row>
     <row r="130">
@@ -5217,35 +5217,35 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>656553</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>KPU KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F130" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>3240885</v>
+        <v>1720000</v>
       </c>
     </row>
     <row r="131">
@@ -5254,35 +5254,35 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>656553</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>KPU KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F131" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>11000000</v>
+        <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>10681290</v>
+        <v>3165505</v>
       </c>
     </row>
     <row r="132">
@@ -5291,35 +5291,35 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>656553</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>KPU KABUPATEN OGAN KOMERING ULU</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F132" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>11000000</v>
+        <v>0</v>
       </c>
       <c r="I132" t="n">
-        <v>4634266</v>
+        <v>1418516</v>
       </c>
     </row>
     <row r="133">
@@ -5328,24 +5328,24 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="E133" t="n">
         <v>2025</v>
       </c>
       <c r="F133" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -5353,10 +5353,10 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>11000000</v>
+        <v>16000000</v>
       </c>
       <c r="I133" t="n">
-        <v>7207769</v>
+        <v>2289406</v>
       </c>
     </row>
     <row r="134">
@@ -5365,24 +5365,24 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="E134" t="n">
         <v>2025</v>
       </c>
       <c r="F134" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>5000000</v>
+        <v>16000000</v>
       </c>
       <c r="I134" t="n">
-        <v>5716521</v>
+        <v>3668591</v>
       </c>
     </row>
     <row r="135">
@@ -5402,35 +5402,35 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="F135" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>LAMA</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>36000000</v>
+        <v>16000000</v>
       </c>
       <c r="I135" t="n">
-        <v>8638865</v>
+        <v>2283305</v>
       </c>
     </row>
     <row r="136">
@@ -5439,35 +5439,35 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>667215</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="F136" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>LAMA</t>
         </is>
       </c>
       <c r="H136" t="n">
-        <v>30000000</v>
+        <v>32000000</v>
       </c>
       <c r="I136" t="n">
-        <v>13630532</v>
+        <v>7554670</v>
       </c>
     </row>
     <row r="137">
@@ -5476,24 +5476,24 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="E137" t="n">
         <v>2025</v>
       </c>
       <c r="F137" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>24000000</v>
+        <v>32000000</v>
       </c>
       <c r="I137" t="n">
-        <v>14859000</v>
+        <v>2727445</v>
       </c>
     </row>
     <row r="138">
@@ -5513,24 +5513,24 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="E138" t="n">
         <v>2025</v>
       </c>
       <c r="F138" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -5538,10 +5538,10 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>14000000</v>
+        <v>16000000</v>
       </c>
       <c r="I138" t="n">
-        <v>1392000</v>
+        <v>7326664</v>
       </c>
     </row>
     <row r="139">
@@ -5550,24 +5550,24 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="E139" t="n">
         <v>2025</v>
       </c>
       <c r="F139" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>14000000</v>
+        <v>16000000</v>
       </c>
       <c r="I139" t="n">
-        <v>1722276</v>
+        <v>3185388</v>
       </c>
     </row>
     <row r="140">
@@ -5587,24 +5587,24 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>668529</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="E140" t="n">
         <v>2025</v>
       </c>
       <c r="F140" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -5612,10 +5612,10 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>14000000</v>
+        <v>16000000</v>
       </c>
       <c r="I140" t="n">
-        <v>689000</v>
+        <v>4151070</v>
       </c>
     </row>
     <row r="141">
@@ -5624,35 +5624,35 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>685001</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>PUSLATPUR KODIKLATAD</t>
+          <t>KPU KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F141" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>1500000</v>
+        <v>6034789</v>
       </c>
     </row>
     <row r="142">
@@ -5661,24 +5661,24 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>685001</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>PUSLATPUR KODIKLATAD</t>
+          <t>KPU KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="E142" t="n">
         <v>2026</v>
       </c>
       <c r="F142" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -5686,10 +5686,10 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>2400000</v>
+        <v>0</v>
       </c>
       <c r="I142" t="n">
-        <v>2400000</v>
+        <v>2679300</v>
       </c>
     </row>
     <row r="143">
@@ -5698,24 +5698,24 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>685001</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>PUSLATPUR KODIKLATAD</t>
+          <t>KPU KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="E143" t="n">
         <v>2026</v>
       </c>
       <c r="F143" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -5723,10 +5723,10 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>7200000</v>
+        <v>0</v>
       </c>
       <c r="I143" t="n">
-        <v>2850000</v>
+        <v>17453340</v>
       </c>
     </row>
     <row r="144">
@@ -5735,35 +5735,35 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>690801</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
+          <t>KPU KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F144" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H144" t="n">
-        <v>22000000</v>
+        <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>1865319</v>
+        <v>10105310</v>
       </c>
     </row>
     <row r="145">
@@ -5772,35 +5772,35 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>690801</t>
+          <t>656560</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
+          <t>KPU KABUPATEN OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F145" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H145" t="n">
-        <v>22000000</v>
+        <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>2717905</v>
+        <v>6104000</v>
       </c>
     </row>
     <row r="146">
@@ -5809,24 +5809,24 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>656574</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="E146" t="n">
         <v>2025</v>
       </c>
       <c r="F146" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>40000000</v>
+        <v>1900000</v>
       </c>
       <c r="I146" t="n">
-        <v>1082700</v>
+        <v>1904397</v>
       </c>
     </row>
     <row r="147">
@@ -5846,24 +5846,24 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>656574</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="E147" t="n">
         <v>2025</v>
       </c>
       <c r="F147" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -5871,10 +5871,10 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>40000000</v>
+        <v>1900000</v>
       </c>
       <c r="I147" t="n">
-        <v>2260122</v>
+        <v>640133</v>
       </c>
     </row>
     <row r="148">
@@ -5883,24 +5883,24 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>656574</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="E148" t="n">
         <v>2025</v>
       </c>
       <c r="F148" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -5908,10 +5908,10 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>40000000</v>
+        <v>1900000</v>
       </c>
       <c r="I148" t="n">
-        <v>2806886</v>
+        <v>1720000</v>
       </c>
     </row>
     <row r="149">
@@ -5920,24 +5920,24 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>692334</t>
+          <t>656574</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>LAPAS KELAS II B MUARA DUA</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="E149" t="n">
         <v>2025</v>
       </c>
       <c r="F149" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -5945,10 +5945,10 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>40000000</v>
+        <v>1900000</v>
       </c>
       <c r="I149" t="n">
-        <v>1082700</v>
+        <v>128530</v>
       </c>
     </row>
     <row r="150">
@@ -5957,12 +5957,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>692339</t>
+          <t>656574</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>RUTAN KELAS II B BATURAJA</t>
+          <t>KPU  KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -5982,10 +5982,10 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>6800000</v>
+        <v>1900000</v>
       </c>
       <c r="I150" t="n">
-        <v>1386000</v>
+        <v>401000</v>
       </c>
     </row>
     <row r="151">
@@ -5994,35 +5994,35 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>692339</t>
+          <t>656574</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>RUTAN KELAS II B BATURAJA</t>
+          <t>KPU KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F151" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>LAMA</t>
+          <t>BARU</t>
         </is>
       </c>
       <c r="H151" t="n">
-        <v>6800000</v>
+        <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>3465000</v>
+        <v>1216870</v>
       </c>
     </row>
     <row r="152">
@@ -6031,24 +6031,24 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>692339</t>
+          <t>656574</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>RUTAN KELAS II B BATURAJA</t>
+          <t>KPU KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="E152" t="n">
         <v>2026</v>
       </c>
       <c r="F152" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -6056,10 +6056,10 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>40000000</v>
+        <v>0</v>
       </c>
       <c r="I152" t="n">
-        <v>30090000</v>
+        <v>350550</v>
       </c>
     </row>
     <row r="153">
@@ -6068,24 +6068,24 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>692339</t>
+          <t>656574</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>RUTAN KELAS II B BATURAJA</t>
+          <t>KPU KABUPATEN OGAN KOMERING ULU SELATAN</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="E153" t="n">
         <v>2026</v>
       </c>
       <c r="F153" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -6093,10 +6093,10 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>40000000</v>
+        <v>0</v>
       </c>
       <c r="I153" t="n">
-        <v>16654072</v>
+        <v>2039995</v>
       </c>
     </row>
     <row r="154">
@@ -6105,24 +6105,24 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>692339</t>
+          <t>665292</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>RUTAN KELAS II B BATURAJA</t>
+          <t>POLRES OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="E154" t="n">
         <v>2026</v>
       </c>
       <c r="F154" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -6130,10 +6130,10 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>40000000</v>
+        <v>0</v>
       </c>
       <c r="I154" t="n">
-        <v>12828042</v>
+        <v>16512000</v>
       </c>
     </row>
     <row r="155">
@@ -6142,24 +6142,24 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>692625</t>
+          <t>665292</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>BAPAS KELAS II OKU INDUK</t>
+          <t>POLRES OGAN KOMERING ULU TIMUR</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="E155" t="n">
         <v>2026</v>
       </c>
       <c r="F155" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -6167,10 +6167,10 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>6000000</v>
+        <v>0</v>
       </c>
       <c r="I155" t="n">
-        <v>2550000</v>
+        <v>16512000</v>
       </c>
     </row>
     <row r="156">
@@ -6179,34 +6179,2328 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
+          <t>665292</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>POLRES OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F156" t="n">
+        <v>4</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+      <c r="H156" t="n">
+        <v>0</v>
+      </c>
+      <c r="I156" t="n">
+        <v>16522000</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>665292</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>POLRES OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F157" t="n">
+        <v>5</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+      <c r="H157" t="n">
+        <v>0</v>
+      </c>
+      <c r="I157" t="n">
+        <v>16522000</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>665292</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>POLRES OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F158" t="n">
+        <v>6</v>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+      <c r="H158" t="n">
+        <v>0</v>
+      </c>
+      <c r="I158" t="n">
+        <v>33044000</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>665307</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>POLRES OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F159" t="n">
+        <v>1</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+      <c r="H159" t="n">
+        <v>0</v>
+      </c>
+      <c r="I159" t="n">
+        <v>59780000</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>665307</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>POLRES OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F160" t="n">
+        <v>2</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+      <c r="H160" t="n">
+        <v>0</v>
+      </c>
+      <c r="I160" t="n">
+        <v>24770827</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>665307</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>POLRES OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F161" t="n">
+        <v>3</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+      <c r="H161" t="n">
+        <v>0</v>
+      </c>
+      <c r="I161" t="n">
+        <v>37398067</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>665307</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>POLRES OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F162" t="n">
+        <v>4</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+      <c r="H162" t="n">
+        <v>0</v>
+      </c>
+      <c r="I162" t="n">
+        <v>69316624</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>665307</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>POLRES OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F163" t="n">
+        <v>5</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+      <c r="H163" t="n">
+        <v>0</v>
+      </c>
+      <c r="I163" t="n">
+        <v>87477232</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>665307</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>POLRES OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F164" t="n">
+        <v>6</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+      <c r="H164" t="n">
+        <v>0</v>
+      </c>
+      <c r="I164" t="n">
+        <v>65137181</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>665307</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>POLRES OGAN KOMERING ULU SELATAN</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F165" t="n">
+        <v>7</v>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+      <c r="H165" t="n">
+        <v>0</v>
+      </c>
+      <c r="I165" t="n">
+        <v>33359790</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F166" t="n">
+        <v>2</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="H166" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="I166" t="n">
+        <v>2868489</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F167" t="n">
+        <v>3</v>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="H167" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="I167" t="n">
+        <v>2115768</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F168" t="n">
+        <v>4</v>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="H168" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="I168" t="n">
+        <v>2111897</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F169" t="n">
+        <v>5</v>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="H169" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="I169" t="n">
+        <v>4914266</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F170" t="n">
+        <v>6</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="H170" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="I170" t="n">
+        <v>3017400</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F171" t="n">
+        <v>7</v>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="H171" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="I171" t="n">
+        <v>5939307</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F172" t="n">
+        <v>8</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="H172" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="I172" t="n">
+        <v>3240885</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F173" t="n">
+        <v>9</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="H173" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="I173" t="n">
+        <v>10681290</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F174" t="n">
+        <v>10</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="H174" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="I174" t="n">
+        <v>4634266</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F175" t="n">
+        <v>11</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="H175" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="I175" t="n">
+        <v>7207769</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F176" t="n">
+        <v>12</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="H176" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="I176" t="n">
+        <v>5716521</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F177" t="n">
+        <v>2</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+      <c r="H177" t="n">
+        <v>0</v>
+      </c>
+      <c r="I177" t="n">
+        <v>8638865</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F178" t="n">
+        <v>3</v>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+      <c r="H178" t="n">
+        <v>0</v>
+      </c>
+      <c r="I178" t="n">
+        <v>13630532</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F179" t="n">
+        <v>4</v>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+      <c r="H179" t="n">
+        <v>0</v>
+      </c>
+      <c r="I179" t="n">
+        <v>230040</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F180" t="n">
+        <v>5</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+      <c r="H180" t="n">
+        <v>0</v>
+      </c>
+      <c r="I180" t="n">
+        <v>3173547</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F181" t="n">
+        <v>6</v>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+      <c r="H181" t="n">
+        <v>0</v>
+      </c>
+      <c r="I181" t="n">
+        <v>3569566</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>667215</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OKU SELATAN</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F182" t="n">
+        <v>7</v>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+      <c r="H182" t="n">
+        <v>0</v>
+      </c>
+      <c r="I182" t="n">
+        <v>2164321</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>668529</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F183" t="n">
+        <v>7</v>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="H183" t="n">
+        <v>24000000</v>
+      </c>
+      <c r="I183" t="n">
+        <v>14859000</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>668529</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F184" t="n">
+        <v>8</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="H184" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="I184" t="n">
+        <v>1392000</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>668529</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F185" t="n">
+        <v>9</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="H185" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="I185" t="n">
+        <v>1722276</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>668529</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F186" t="n">
+        <v>10</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="H186" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="I186" t="n">
+        <v>689000</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>668529</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F187" t="n">
+        <v>5</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+      <c r="H187" t="n">
+        <v>0</v>
+      </c>
+      <c r="I187" t="n">
+        <v>2904000</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>668529</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F188" t="n">
+        <v>6</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+      <c r="H188" t="n">
+        <v>0</v>
+      </c>
+      <c r="I188" t="n">
+        <v>524600</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>668529</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>BADAN PUSAT STATISTIK KAB. OGAN KOMERING ULU TIMUR</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F189" t="n">
+        <v>7</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+      <c r="H189" t="n">
+        <v>0</v>
+      </c>
+      <c r="I189" t="n">
+        <v>7975500</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>685001</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>PUSLATPUR KODIKLATAD</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F190" t="n">
+        <v>11</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="H190" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="I190" t="n">
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>685001</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>PUSLATPUR KODIKLATAD</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F191" t="n">
+        <v>2</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+      <c r="H191" t="n">
+        <v>0</v>
+      </c>
+      <c r="I191" t="n">
+        <v>2400000</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>685001</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>PUSLATPUR KODIKLATAD</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F192" t="n">
+        <v>3</v>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+      <c r="H192" t="n">
+        <v>0</v>
+      </c>
+      <c r="I192" t="n">
+        <v>2850000</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>685001</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>PUSLATPUR KODIKLATAD</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F193" t="n">
+        <v>4</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+      <c r="H193" t="n">
+        <v>0</v>
+      </c>
+      <c r="I193" t="n">
+        <v>2625000</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>685001</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>PUSLATPUR KODIKLATAD</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F194" t="n">
+        <v>5</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+      <c r="H194" t="n">
+        <v>0</v>
+      </c>
+      <c r="I194" t="n">
+        <v>2625000</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>685001</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>PUSLATPUR KODIKLATAD</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F195" t="n">
+        <v>6</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+      <c r="H195" t="n">
+        <v>0</v>
+      </c>
+      <c r="I195" t="n">
+        <v>2625000</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>690801</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F196" t="n">
+        <v>11</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="H196" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="I196" t="n">
+        <v>1865319</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>690801</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F197" t="n">
+        <v>12</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="H197" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="I197" t="n">
+        <v>2717905</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>690801</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F198" t="n">
+        <v>4</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+      <c r="H198" t="n">
+        <v>0</v>
+      </c>
+      <c r="I198" t="n">
+        <v>381136</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>690801</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>LOKA LABORATORIUM KESEHATAN MASYARAKAT BATURAJA</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F199" t="n">
+        <v>6</v>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+      <c r="H199" t="n">
+        <v>0</v>
+      </c>
+      <c r="I199" t="n">
+        <v>609215</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>692334</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>LAPAS KELAS II B MUARA DUA</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F200" t="n">
+        <v>8</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="H200" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="I200" t="n">
+        <v>1082700</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>692334</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>LAPAS KELAS II B MUARA DUA</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F201" t="n">
+        <v>9</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="H201" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="I201" t="n">
+        <v>2260122</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>692334</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>LAPAS KELAS II B MUARA DUA</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F202" t="n">
+        <v>10</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="H202" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="I202" t="n">
+        <v>2806886</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>692334</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>LAPAS KELAS II B MUARA DUA</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F203" t="n">
+        <v>12</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="H203" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="I203" t="n">
+        <v>1082700</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>692334</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>LAPAS KELAS II B MUARA DUA</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F204" t="n">
+        <v>5</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+      <c r="H204" t="n">
+        <v>0</v>
+      </c>
+      <c r="I204" t="n">
+        <v>2159400</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>692334</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>LAPAS KELAS II B MUARA DUA</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F205" t="n">
+        <v>6</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+      <c r="H205" t="n">
+        <v>0</v>
+      </c>
+      <c r="I205" t="n">
+        <v>1082700</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>692334</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>LAPAS KELAS II B MUARA DUA</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F206" t="n">
+        <v>7</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+      <c r="H206" t="n">
+        <v>0</v>
+      </c>
+      <c r="I206" t="n">
+        <v>1082700</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>692339</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>RUTAN KELAS II B BATURAJA</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F207" t="n">
+        <v>11</v>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="H207" t="n">
+        <v>6800000</v>
+      </c>
+      <c r="I207" t="n">
+        <v>1386000</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>692339</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>RUTAN KELAS II B BATURAJA</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F208" t="n">
+        <v>12</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>LAMA</t>
+        </is>
+      </c>
+      <c r="H208" t="n">
+        <v>6800000</v>
+      </c>
+      <c r="I208" t="n">
+        <v>3465000</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>692339</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>RUTAN KELAS II B BATURAJA</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F209" t="n">
+        <v>2</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+      <c r="H209" t="n">
+        <v>0</v>
+      </c>
+      <c r="I209" t="n">
+        <v>30090000</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>692339</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>RUTAN KELAS II B BATURAJA</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F210" t="n">
+        <v>3</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+      <c r="H210" t="n">
+        <v>0</v>
+      </c>
+      <c r="I210" t="n">
+        <v>16654072</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>692339</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>RUTAN KELAS II B BATURAJA</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F211" t="n">
+        <v>4</v>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+      <c r="H211" t="n">
+        <v>0</v>
+      </c>
+      <c r="I211" t="n">
+        <v>20831840</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>692339</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>RUTAN KELAS II B BATURAJA</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F212" t="n">
+        <v>5</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+      <c r="H212" t="n">
+        <v>0</v>
+      </c>
+      <c r="I212" t="n">
+        <v>4159000</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>692339</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>RUTAN KELAS II B BATURAJA</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F213" t="n">
+        <v>6</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+      <c r="H213" t="n">
+        <v>0</v>
+      </c>
+      <c r="I213" t="n">
+        <v>5200000</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
           <t>692625</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr">
+      <c r="C214" t="inlineStr">
         <is>
           <t>BAPAS KELAS II OKU INDUK</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr">
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F214" t="n">
+        <v>2</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+      <c r="H214" t="n">
+        <v>0</v>
+      </c>
+      <c r="I214" t="n">
+        <v>2550000</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>692625</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>BAPAS KELAS II OKU INDUK</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="E156" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F156" t="n">
+      <c r="E215" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F215" t="n">
         <v>3</v>
       </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>BARU</t>
-        </is>
-      </c>
-      <c r="H156" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="I156" t="n">
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+      <c r="H215" t="n">
+        <v>0</v>
+      </c>
+      <c r="I215" t="n">
+        <v>2500000</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>692625</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>BAPAS KELAS II OKU INDUK</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F216" t="n">
+        <v>5</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+      <c r="H216" t="n">
+        <v>0</v>
+      </c>
+      <c r="I216" t="n">
+        <v>2500000</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>692625</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>BAPAS KELAS II OKU INDUK</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F217" t="n">
+        <v>6</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+      <c r="H217" t="n">
+        <v>0</v>
+      </c>
+      <c r="I217" t="n">
+        <v>2500000</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>692625</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>BAPAS KELAS II OKU INDUK</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F218" t="n">
+        <v>7</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+      <c r="H218" t="n">
+        <v>0</v>
+      </c>
+      <c r="I218" t="n">
         <v>2500000</v>
       </c>
     </row>
